--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -2,101 +2,101 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R2cb2431e482740cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R422b127241634dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Rcc385e50b0064664"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="R888f7eeb0b8149d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R44db06b46b344d1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="Ra555501e9fef46bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R81007e29bce440a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R6c205f087d044a4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R6cfa5e21500c47ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="Rb36be03cc39949a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="Re413363f460641df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R7a602e4ecac94c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R3d849265e8a348ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Re387bae5e75d42a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="R38e5e968629c46e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="Rd55bce03db1f4c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R5235c8eb42764934"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R40ee2929e9684499"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="Rc49b80b767cb4576"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R17a5d13203c34081"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="Re875d924b28e4064"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="R355bcb9f55ed4a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R7eda2b70f3d447d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="Rc674199300074ad8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="Rdabbb8eb91874096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="Re9ba1d1beaa9419d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="Re7721cccd32543e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="R9c74a564ccc64c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R6386ae9b1ab64d6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R2707a2fb96c24b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="R5e06070611d44087"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Rbbd96c8f47af453e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="Ra4bc68e9bed74137"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R5ad03aa28bca4253"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Rf77e7ca3b3b6459b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="R5d4af7ccc15847e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="Rfd8c2617b3b94795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="Rd68cad1eea73498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="Rba014e021c3747ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R659fb3cc111b490f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="R62904e1e541246ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R404aa5354c7548ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R39a80b4320514176"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="R697f44a5ba974214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="R91af0324fa954ab5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="Rff6ddff73e1042ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R3ec59a397f9a4086"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R2f1733cdb6524795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R809fac24df114d64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="R7da0812af1534859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="Refa38fe34441455c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="R1e35e96751eb4638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="R0648f0991b544085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R00ffe5afcdb8474e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="Rd947bc45d5c9430c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R465c40d8b9b145ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="R184f55570b244939"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="Rff39691f4c384681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R18aef53c34664bbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R30d3165f692642f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R8317d9c6fbf54681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="Rabbc3ea507854802"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R506f49149b884a50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R6ff5664a735745c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R5edb7ec40b2c4fcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R5bca6e6aef21456a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R08386466c54f4362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="Re6a9bc934ad84b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="Ra2581805f7934e46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="Rd93d74a5a3c04f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Rb2cf3fce17614975"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R2c0651a5abe5455b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R5f89191d31d6425f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Rac7675c1fdf74566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="Rfa7d243a104f4eea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="R588597188e8e4d19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Raf20f0f2a3c54e28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="R3dee7a024cb74a79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="Ra858e81de1df4448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="R853589996df9422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R8896a66f406943f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R1fd2903fac484d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="R79720e6dddf64c98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R0f3c7ecb9cbb46ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="R39abbbbed1fd44e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="Rc0f430eba3374808"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="Rab116a69588043bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="R0fe887affac14c77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="R396c21b4b8304661"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R956b4d519e324175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R956c6bbfbb994313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R895095e64c974268"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R93b330999643404e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="R2d4b1ed4eb5449bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Rdc26707630784943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="Rbdf70b79fec44565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R2088ed7995fd4a8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Rc775655d5403498d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rd8404d4b00c94ff7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R6f402b1a714e454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="Rcaf9c1cc88b94d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="Rdf36fbfb77534b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R3d06ff6fad07494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="Rc9ec98efe3bb4faa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R153480a3da3e414a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="Rd7c2049bac9c40cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R69871b5690484a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="Rf5b5dff5158a4d73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="R1ce97b6bb53f4313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="Ra1f6b251841d47c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="R214347ec00af4d90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R593b8013feb44072"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R6355ba7e6d254b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R3aea60d047fe4679"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="Rd87c35135a854cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R03100569061848d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="R4cff77b702374c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="Raf553d146747486c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R6abcbb27514748f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="R2c85a8f517b14a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="Re280aa4dc4a94b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="Ra3653140d49544cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="R1035cd74aed74d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R1f497dd8e7fb4dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R94b824cd40a448c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="Rc5cb630979504a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Rdda15d8c22b442e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R12496005af5148ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R1f411d5f1acc44ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Rc215350b2b694376"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="R1c79c863fbe343be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R3c6d61a035f141da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R1df4c2f3c02b4200"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R1d38c773199148ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R7017c99fe89040c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="Rbaa7da4c5bed41ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R6cf83b10dc9e4e73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R69a9707e3b924440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="R05b2ba39906c4848"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="Rccd9686aa54c4665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="Rd159b95775e348b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R93d33d68aded474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R4db0debc89b547b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R4acd0aabee1040c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="R74705c858d084434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R08b58bb6774b4815"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="Re11b533a369441a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="R482669573c2d4e48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R75e44b08a386414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R624d784ef9de497d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="Rc663f60fabd646f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="R683c2ca51f404baa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R84fba967d966469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R0470478a42cf459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R6a4f3a7b9a6b496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R2acea644a20a4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R9538a1f8e70f459f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="Re51afb557b5944ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="Rf32a66514967464f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R18fe4041f2954def"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="Re7e0952902fd4085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R87e5a8c393e644c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="R59f3f5e28fb64ca9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="Rb2b97610903d4e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="Rffc539c21e3c439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="R11310e371c424259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R31921dd5c5344093"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R650a7ad770ee4102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Raa338800d5b34a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R6cd1a395107949ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="Re0510237b2d74b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="R5ac00f23812943f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="Rc71360fe95b24340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="Re3fb7704c3f64a72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="Rd619005f457a4af7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R2b5de855caef4e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R41af45ebbc414524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Ra29f865fc5634f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R64e2acca77e34f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="R088a5e0dc85846c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R77ab2160f60441b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="Refe0730c63bf4ee2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="Recc9203d2c654561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="R4610a18ee03c4c4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R22495ba073a745c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R683bc9a8b449411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="Rb522c2160c374fb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R20249e1196f846c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="Rc6dbb2614a5a4816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Rf26bee975af84b05"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44963,16 +44963,16 @@
         <x:v>first_loop_closed_development</x:v>
       </x:c>
       <x:c r="C4" s="17" t="str">
-        <x:v>{"rule_version":2,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_range_minus_defence","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。","player_stats_source":"../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600","damage_scope_notice":"仅验证无幸运/命中/元素/Buff的源物理区间减固定防御子集。不是完整1.80伤害管线。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]}}</x:v>
+        <x:v>{"rule_version":3,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"skills":[{"learn_level":7,"learned_level":0,"mp_base_cost":3,"mp_level_cost":2,"cooldown_base_ms":1800,"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"range_cells":9,"delay_base_ms":500,"accuracy_per_level":0,"power_bonus":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"id":1,"name":"火球术","job_id":1,"book_item_id":7,"behavior":"fireball","projectile_ms_per_cell":50,"target_move_tolerance_cells":2,"power_base":2,"mpower_base":8},{"learn_level":7,"learned_level":0,"mp_base_cost":3,"mp_level_cost":2,"cooldown_base_ms":1800,"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"range_cells":9,"delay_base_ms":500,"accuracy_per_level":0,"power_bonus":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"id":2,"name":"治愈术","job_id":2,"book_item_id":21,"behavior":"healing","projectile_ms_per_cell":0,"target_move_tolerance_cells":0,"power_base":0,"mpower_base":14},{"learn_level":7,"learned_level":0,"mp_base_cost":0,"mp_level_cost":0,"cooldown_base_ms":1800,"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"range_cells":0,"delay_base_ms":0,"accuracy_per_level":3,"power_bonus":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"id":3,"name":"基本剑术","job_id":0,"book_item_id":1,"behavior":"fencing","projectile_ms_per_cell":0,"target_move_tolerance_cells":0,"power_base":0,"mpower_base":0}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}]}</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）</x:v>
+        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>仅development候选，正式发布仍禁用。红20/蓝30是跨来源开发测试量，不证明MYF Ac/Mac字段语义；Crystal普通药分跳/上限/满值清队列/死亡暂停；来源客户端300ms共享节流提升为服务器校验。详见docs/药品与技能实施边界.md。</x:v>
+        <x:v>仅development候选。红蓝药与首组三职业技能；完整技能、升级、1.80还原及正式发布仍待验收。来源与例外见技能/药品边界文档。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -2,101 +2,101 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="Rbdf70b79fec44565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R2088ed7995fd4a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Rc775655d5403498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rd8404d4b00c94ff7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R6f402b1a714e454e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="Rcaf9c1cc88b94d00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="Rdf36fbfb77534b9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R3d06ff6fad07494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="Rc9ec98efe3bb4faa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R153480a3da3e414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="Rd7c2049bac9c40cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R69871b5690484a65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="Rf5b5dff5158a4d73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="R1ce97b6bb53f4313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="Ra1f6b251841d47c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="R214347ec00af4d90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R593b8013feb44072"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R6355ba7e6d254b48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R3aea60d047fe4679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="Rd87c35135a854cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R03100569061848d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="R4cff77b702374c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="Raf553d146747486c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R6abcbb27514748f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="R2c85a8f517b14a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="Re280aa4dc4a94b6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="Ra3653140d49544cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="R1035cd74aed74d96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R1f497dd8e7fb4dc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R94b824cd40a448c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="Rc5cb630979504a8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Rdda15d8c22b442e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R12496005af5148ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R1f411d5f1acc44ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Rc215350b2b694376"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="R1c79c863fbe343be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R3c6d61a035f141da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R1df4c2f3c02b4200"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R1d38c773199148ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R7017c99fe89040c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="Rbaa7da4c5bed41ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R6cf83b10dc9e4e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R69a9707e3b924440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="R05b2ba39906c4848"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="Rccd9686aa54c4665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="Rd159b95775e348b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R93d33d68aded474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R4db0debc89b547b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R4acd0aabee1040c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="R74705c858d084434"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R08b58bb6774b4815"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="Re11b533a369441a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="R482669573c2d4e48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R75e44b08a386414f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R624d784ef9de497d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="Rc663f60fabd646f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="R683c2ca51f404baa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R84fba967d966469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R0470478a42cf459a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R6a4f3a7b9a6b496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R2acea644a20a4157"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R9538a1f8e70f459f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="Re51afb557b5944ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="Rf32a66514967464f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R18fe4041f2954def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="Re7e0952902fd4085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R87e5a8c393e644c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="R59f3f5e28fb64ca9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="Rb2b97610903d4e9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="Rffc539c21e3c439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="R11310e371c424259"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R31921dd5c5344093"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R650a7ad770ee4102"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Raa338800d5b34a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R6cd1a395107949ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="Re0510237b2d74b0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="R5ac00f23812943f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="Rc71360fe95b24340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="Re3fb7704c3f64a72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="Rd619005f457a4af7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R2b5de855caef4e1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R41af45ebbc414524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Ra29f865fc5634f43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R64e2acca77e34f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="R088a5e0dc85846c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R77ab2160f60441b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="Refe0730c63bf4ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="Recc9203d2c654561"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="R4610a18ee03c4c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R22495ba073a745c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R683bc9a8b449411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="Rb522c2160c374fb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R20249e1196f846c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="Rc6dbb2614a5a4816"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Rf26bee975af84b05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R4a446053f0d445f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R9a68b6b3631f4457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Re3963f1b06fd42fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="R5199767e057e4193"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="Rb187396033d842db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="R7ce00b25f624475b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R84cf22d68f684b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R99e75a614a9147e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R42bfe4fe41d246ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="Rafd3659511a5496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="R5b4735e34b6c4dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R19488783206b4dfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R24b87d25257242e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Rfd3adc7253a74b85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="Rb4aea4f4656848a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="Rd479a0f12130459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R65a3c4e9f32b4c47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R658e43f2665c4676"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R18f5e61d87654271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R0a43034c71c74736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="Rf41f89b14a424b3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="Rac28d13ce501470f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R2138b25026994695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R47b14fdb43ef4703"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="R5e860261b1924b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="R75fe4b6f27344a19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="Rc741a8788e7d454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="Rdaeead3348c44e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="Ra1fd52784e4843d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R75ab300ad3bc471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="Re2431555b2da416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="R04a5963b72254f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R6ec5356c93e04191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R2c6bf35fc6a64715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Re175e5dc5fce4fb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="Rf4efd8f36f1744ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R6147c85dab7042ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R7adb023fca4243da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R48f839df00c04dcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="Rab16edb15f554909"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="Re339e8531199460e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R2cbc666458b04354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="Re0bc92ef6ab84520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="R12a2291fb44a476f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="Re0f5920ad98f42f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="R1e51525dc56d4728"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="Rc2f086b8365741bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R62bd1d0435254210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R4250fbe5a4854e2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="Rbd902b8c3d294828"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R5a8d17b6f2ae4934"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="R306cdbe523e64a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Ra3c5e96d716a4adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R25ec5d0e4ac04637"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="Rb6135214a8eb4e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R7218adc1798e45b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="Rfe98e538e58f47cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R0b18111adf054269"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="Rebfa4fffe9c741bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R7f3877472aac4dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="Rfe86f68e0f0b44de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="Ra21c0a56b5794a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R154b30958e544c71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R928bff76f5e3400b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R932d84cc64ae4769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="Rd08639de67c9475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R00e17b50e8fb4ecc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="R9ec044d49d334374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="R32e41d9ed3c8484f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R4dcb3ecb2e774334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Re7e0bf38509749c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R36f707e594c148c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R7e045910c8dc4c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Ra623b3348c574246"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R85905960f8044156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="R94437812f02f499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Ra6cfee0aa59f4e73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="Rc1410b7441c24520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R44c3add78bcc4e2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="R80fe5ed22b604518"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R3adfe257c87e44c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="Ra4fe03525ac74170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rfc4bb70541f74491"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="Re79b0315c9984dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="Rb3c3e8f7c1074c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R54ff0b1a7c284fcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="R3e76750798ff47e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="Rd067ecb7ae994da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Re222824bbf0d403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R06065ddc61b84938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R5cca22d53ab84fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R7848443fb8164174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="Ref7d114d823f483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="R532ecf91ebf04310"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="R81b287beee4d4dfa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8092,7 +8092,7 @@
       </x:c>
       <x:c r="C39" s="2" t="n">
         <x:f>COUNTA('商城商品候选'!$A$4:$A$10003)</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"confirmed")</x:f>
@@ -8100,7 +8100,7 @@
       </x:c>
       <x:c r="E39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"candidate")</x:f>
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"unverified")</x:f>
@@ -8588,7 +8588,7 @@
       </x:c>
       <x:c r="C55" s="2" t="n">
         <x:f>COUNTA('物品定义'!$A$4:$A$10003)</x:f>
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"confirmed")</x:f>
@@ -8596,7 +8596,7 @@
       </x:c>
       <x:c r="E55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"candidate")</x:f>
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"unverified")</x:f>
@@ -8867,7 +8867,7 @@
       </x:c>
       <x:c r="C64" s="2" t="n">
         <x:f>COUNTA('技能基础定义'!$A$4:$A$10003)</x:f>
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"confirmed")</x:f>
@@ -8875,7 +8875,7 @@
       </x:c>
       <x:c r="E64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"candidate")</x:f>
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"unverified")</x:f>
@@ -8898,7 +8898,7 @@
       </x:c>
       <x:c r="C65" s="2" t="n">
         <x:f>COUNTA('技能逐级扩展'!$A$4:$A$10003)</x:f>
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"confirmed")</x:f>
@@ -8906,7 +8906,7 @@
       </x:c>
       <x:c r="E65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"candidate")</x:f>
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"unverified")</x:f>
@@ -9177,7 +9177,7 @@
       </x:c>
       <x:c r="C74" s="2" t="n">
         <x:f>COUNTA('掉落条目'!$A$4:$A$10003)</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"confirmed")</x:f>
@@ -9185,7 +9185,7 @@
       </x:c>
       <x:c r="E74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"candidate")</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"unverified")</x:f>
@@ -22018,6 +22018,7 @@
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="48" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="70" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -22054,6 +22055,9 @@
       <x:c r="K1" s="7" t="str">
         <x:v>说明</x:v>
       </x:c>
+      <x:c r="L1" s="7" t="str">
+        <x:v>每件金币价格</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -22089,6 +22093,9 @@
       <x:c r="K2" s="12" t="str">
         <x:v>note</x:v>
       </x:c>
+      <x:c r="L2" s="12" t="str">
+        <x:v>price_gold</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="15" t="str">
@@ -22124,6 +22131,9 @@
       <x:c r="K3" s="15" t="str">
         <x:v>string / 可空 / none</x:v>
       </x:c>
+      <x:c r="L3" s="15" t="str">
+        <x:v>int / 可空 / both</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="19" t="n">
@@ -22157,6 +22167,7 @@
       <x:c r="K4" s="18" t="str">
         <x:v>限购/币种选择策略待定；报价必须明示选择币种，不能自动从100元宝换成200绑元。</x:v>
       </x:c>
+      <x:c r="L4" s="17"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="19" t="n">
@@ -22288,18 +22299,107 @@
         <x:v>正文明确价格待配置，禁止沿用旧20/100石价。</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="19"/>
-      <x:c r="B9" s="17"/>
-      <x:c r="C9" s="17"/>
-      <x:c r="D9" s="17"/>
+    <x:row r="9" ht="70" hidden="0" customHeight="1">
+      <x:c r="A9" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="17" t="str">
+        <x:v>skill_book_1</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>《火球术》</x:v>
+      </x:c>
+      <x:c r="D9" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
       <x:c r="E9" s="16"/>
-      <x:c r="F9" s="16"/>
-      <x:c r="G9" s="2"/>
+      <x:c r="F9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H9" s="16"/>
-      <x:c r="I9" s="17"/>
-      <x:c r="J9" s="18"/>
-      <x:c r="K9" s="18"/>
+      <x:c r="I9" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="str">
+        <x:v>MYF stditems源Price500；本项目development定价适配，非原NPC实际成交价核验</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L9" s="17" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="70" customHeight="1">
+      <x:c r="A10" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="17" t="str">
+        <x:v>skill_book_2</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="str">
+        <x:v>《治愈术》</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E10" s="16"/>
+      <x:c r="F10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="16"/>
+      <x:c r="I10" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="str">
+        <x:v>MYF stditems源Price500；本项目development定价适配，非原NPC实际成交价核验</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L10" s="17" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="70" customHeight="1">
+      <x:c r="A11" s="19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="str">
+        <x:v>skill_book_3</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="str">
+        <x:v>《基本剑术》</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E11" s="16"/>
+      <x:c r="F11" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="16"/>
+      <x:c r="I11" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="str">
+        <x:v>MYF stditems源Price500；本项目development定价适配，非原NPC实际成交价核验</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L11" s="17" t="n">
+        <x:v>500</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
@@ -29522,35 +29622,153 @@
         <x:v>正式堆叠与药效映射仍待核验；本轮仅development启用逐件消费候选，恢复量和时序由开发首循环夹具统一维护。原Looks/Shape不作为已核验图标或药效证据。</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="19"/>
-      <x:c r="B8" s="17"/>
-      <x:c r="C8" s="17"/>
-      <x:c r="D8" s="17"/>
-      <x:c r="E8" s="16"/>
+    <x:row r="8" ht="70" hidden="0" customHeight="1">
+      <x:c r="A8" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
+        <x:v>skill_book_1</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>《火球术》</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E8" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="F8" s="16"/>
-      <x:c r="G8" s="16"/>
-      <x:c r="H8" s="16"/>
-      <x:c r="I8" s="17"/>
+      <x:c r="G8" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
       <x:c r="J8" s="17"/>
-      <x:c r="K8" s="17"/>
-      <x:c r="L8" s="18"/>
-      <x:c r="M8" s="18"/>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="19"/>
-      <x:c r="B9" s="17"/>
-      <x:c r="C9" s="17"/>
-      <x:c r="D9" s="17"/>
-      <x:c r="E9" s="16"/>
+      <x:c r="K8" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L8" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv；显式书→技能映射见docs/技能获取与升级实施边界.md</x:v>
+      </x:c>
+      <x:c r="M8" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="70" hidden="0" customHeight="1">
+      <x:c r="A9" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B9" s="17" t="str">
+        <x:v>skill_book_2</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>《治愈术》</x:v>
+      </x:c>
+      <x:c r="D9" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="F9" s="16"/>
-      <x:c r="G9" s="16"/>
-      <x:c r="H9" s="16"/>
-      <x:c r="I9" s="17"/>
+      <x:c r="G9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
       <x:c r="J9" s="17"/>
-      <x:c r="K9" s="17"/>
-      <x:c r="L9" s="18"/>
-      <x:c r="M9" s="18"/>
+      <x:c r="K9" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L9" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv；显式书→技能映射见docs/技能获取与升级实施边界.md</x:v>
+      </x:c>
+      <x:c r="M9" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="70" customHeight="1">
+      <x:c r="A10" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B10" s="17" t="str">
+        <x:v>skill_book_3</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="str">
+        <x:v>《基本剑术》</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="16"/>
+      <x:c r="G10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J10" s="17"/>
+      <x:c r="K10" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L10" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv；显式书→技能映射见docs/技能获取与升级实施边界.md</x:v>
+      </x:c>
+      <x:c r="M10" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="70" customHeight="1">
+      <x:c r="A11" s="19" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="str">
+        <x:v>skill_page</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="str">
+        <x:v>书页</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="str">
+        <x:v>skill_page</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="n">
+        <x:v>65535</x:v>
+      </x:c>
+      <x:c r="F11" s="16"/>
+      <x:c r="G11" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="17" t="str">
+        <x:v>技能升级材料，分解产物继承原书绑定；商城书页绑定</x:v>
+      </x:c>
+      <x:c r="J11" s="17"/>
+      <x:c r="K11" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L11" s="18" t="str">
+        <x:v>最终策划4.8、5.8；项目自定义物品ID900001，非来源客户端物品编号</x:v>
+      </x:c>
+      <x:c r="M11" s="18" t="str">
+        <x:v>65535为本项目开发计数堆叠上限候选；不合并不同来源/绑定，图标尚待制作。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
@@ -32554,6 +32772,10 @@
     <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="48" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="70" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="25" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="25" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="25" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -32614,6 +32836,18 @@
       <x:c r="S1" s="7" t="str">
         <x:v>说明</x:v>
       </x:c>
+      <x:c r="T1" s="7" t="str">
+        <x:v>学习书物品ID</x:v>
+      </x:c>
+      <x:c r="U1" s="7" t="str">
+        <x:v>原生初学阶</x:v>
+      </x:c>
+      <x:c r="V1" s="7" t="str">
+        <x:v>原生开放最高阶</x:v>
+      </x:c>
+      <x:c r="W1" s="7" t="str">
+        <x:v>技能数值参数</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -32673,6 +32907,18 @@
       <x:c r="S2" s="12" t="str">
         <x:v>note</x:v>
       </x:c>
+      <x:c r="T2" s="12" t="str">
+        <x:v>book_item_id</x:v>
+      </x:c>
+      <x:c r="U2" s="12" t="str">
+        <x:v>native_start_level</x:v>
+      </x:c>
+      <x:c r="V2" s="12" t="str">
+        <x:v>native_max_level</x:v>
+      </x:c>
+      <x:c r="W2" s="12" t="str">
+        <x:v>damage_parameters</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="15" t="str">
@@ -32731,6 +32977,18 @@
       </x:c>
       <x:c r="S3" s="15" t="str">
         <x:v>string / 可空 / none</x:v>
+      </x:c>
+      <x:c r="T3" s="15" t="str">
+        <x:v>int / 可空 / both</x:v>
+      </x:c>
+      <x:c r="U3" s="15" t="str">
+        <x:v>int / 可空 / both</x:v>
+      </x:c>
+      <x:c r="V3" s="15" t="str">
+        <x:v>int / 可空 / both</x:v>
+      </x:c>
+      <x:c r="W3" s="15" t="str">
+        <x:v>json / 可空 / both</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -32785,69 +33043,217 @@
       <x:c r="S4" s="18" t="str">
         <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 普攻0为本项目开发消息标识，非来源技能ID；三职业共用近身普攻，职业专属施法仍禁用。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="19"/>
-      <x:c r="B5" s="17"/>
-      <x:c r="C5" s="17"/>
-      <x:c r="D5" s="16"/>
-      <x:c r="E5" s="16"/>
-      <x:c r="F5" s="17"/>
-      <x:c r="G5" s="17"/>
+      <x:c r="T4" s="17"/>
+      <x:c r="U4" s="17"/>
+      <x:c r="V4" s="17"/>
+      <x:c r="W4" s="17"/>
+    </x:row>
+    <x:row r="5" ht="70" hidden="0" customHeight="1">
+      <x:c r="A5" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="str">
+        <x:v>source_fireball</x:v>
+      </x:c>
+      <x:c r="C5" s="17" t="str">
+        <x:v>火球术</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F5" s="17" t="str">
+        <x:v>fireball</x:v>
+      </x:c>
+      <x:c r="G5" s="17" t="str">
+        <x:v>{"kind":"active_monster","range_cells":9,"target_move_tolerance_cells":2}</x:v>
+      </x:c>
       <x:c r="H5" s="16"/>
-      <x:c r="I5" s="16"/>
-      <x:c r="J5" s="17"/>
-      <x:c r="K5" s="17"/>
-      <x:c r="L5" s="17"/>
-      <x:c r="M5" s="17"/>
-      <x:c r="N5" s="17"/>
-      <x:c r="O5" s="17"/>
-      <x:c r="P5" s="2"/>
-      <x:c r="Q5" s="17"/>
-      <x:c r="R5" s="18"/>
-      <x:c r="S5" s="18"/>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="19"/>
-      <x:c r="B6" s="17"/>
-      <x:c r="C6" s="17"/>
-      <x:c r="D6" s="16"/>
-      <x:c r="E6" s="16"/>
-      <x:c r="F6" s="17"/>
-      <x:c r="G6" s="17"/>
+      <x:c r="I5" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J5" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50}</x:v>
+      </x:c>
+      <x:c r="K5" s="17" t="str">
+        <x:v>{"mp_base_cost":3,"mp_level_cost":2,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L5" s="17" t="str">
+        <x:v>fireball</x:v>
+      </x:c>
+      <x:c r="M5" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N5" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O5" s="17" t="str">
+        <x:v>development_source_fireball_v1</x:v>
+      </x:c>
+      <x:c r="P5" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R5" s="18" t="str">
+        <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
+      </x:c>
+      <x:c r="S5" s="18" t="str">
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。</x:v>
+      </x:c>
+      <x:c r="T5" s="17" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U5" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V5" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W5" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":2,"power_bonus":0,"mpower_base":8,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="70" hidden="0" customHeight="1">
+      <x:c r="A6" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="str">
+        <x:v>source_healing</x:v>
+      </x:c>
+      <x:c r="C6" s="17" t="str">
+        <x:v>治愈术</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F6" s="17" t="str">
+        <x:v>healing</x:v>
+      </x:c>
+      <x:c r="G6" s="17" t="str">
+        <x:v>{"kind":"friendly_self_pet","range_cells":9,"target_move_tolerance_cells":0}</x:v>
+      </x:c>
       <x:c r="H6" s="16"/>
-      <x:c r="I6" s="16"/>
-      <x:c r="J6" s="17"/>
-      <x:c r="K6" s="17"/>
-      <x:c r="L6" s="17"/>
-      <x:c r="M6" s="17"/>
-      <x:c r="N6" s="17"/>
-      <x:c r="O6" s="17"/>
-      <x:c r="P6" s="2"/>
-      <x:c r="Q6" s="17"/>
-      <x:c r="R6" s="18"/>
-      <x:c r="S6" s="18"/>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="19"/>
-      <x:c r="B7" s="17"/>
-      <x:c r="C7" s="17"/>
-      <x:c r="D7" s="16"/>
-      <x:c r="E7" s="16"/>
-      <x:c r="F7" s="17"/>
-      <x:c r="G7" s="17"/>
+      <x:c r="I6" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J6" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0}</x:v>
+      </x:c>
+      <x:c r="K6" s="17" t="str">
+        <x:v>{"mp_base_cost":3,"mp_level_cost":2,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L6" s="17" t="str">
+        <x:v>healing</x:v>
+      </x:c>
+      <x:c r="M6" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N6" s="17" t="str">
+        <x:v>player_male.casting</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="str">
+        <x:v>development_source_healing_v1</x:v>
+      </x:c>
+      <x:c r="P6" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R6" s="18" t="str">
+        <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
+      </x:c>
+      <x:c r="S6" s="18" t="str">
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。</x:v>
+      </x:c>
+      <x:c r="T6" s="17" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="U6" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V6" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W6" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":14,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="70" hidden="0" customHeight="1">
+      <x:c r="A7" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="str">
+        <x:v>source_fencing</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="str">
+        <x:v>基本剑术</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="str">
+        <x:v>fencing</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="str">
+        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0}</x:v>
+      </x:c>
       <x:c r="H7" s="16"/>
-      <x:c r="I7" s="16"/>
-      <x:c r="J7" s="17"/>
-      <x:c r="K7" s="17"/>
-      <x:c r="L7" s="17"/>
-      <x:c r="M7" s="17"/>
-      <x:c r="N7" s="17"/>
-      <x:c r="O7" s="17"/>
-      <x:c r="P7" s="2"/>
-      <x:c r="Q7" s="17"/>
-      <x:c r="R7" s="18"/>
-      <x:c r="S7" s="18"/>
+      <x:c r="I7" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0}</x:v>
+      </x:c>
+      <x:c r="K7" s="17" t="str">
+        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L7" s="17" t="str">
+        <x:v>fencing</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N7" s="17" t="str">
+        <x:v>passive</x:v>
+      </x:c>
+      <x:c r="O7" s="17" t="str">
+        <x:v>development_source_fencing_v1</x:v>
+      </x:c>
+      <x:c r="P7" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R7" s="18" t="str">
+        <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
+      </x:c>
+      <x:c r="S7" s="18" t="str">
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。</x:v>
+      </x:c>
+      <x:c r="T7" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U7" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V7" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W7" s="17" t="str">
+        <x:v>{"accuracy_per_level":3,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0}</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="19"/>
@@ -33000,6 +33406,8 @@
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="48" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="70" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="25" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -33033,6 +33441,12 @@
       <x:c r="J1" s="7" t="str">
         <x:v>说明</x:v>
       </x:c>
+      <x:c r="K1" s="7" t="str">
+        <x:v>所需角色等级</x:v>
+      </x:c>
+      <x:c r="L1" s="7" t="str">
+        <x:v>书页物品ID</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -33065,6 +33479,12 @@
       <x:c r="J2" s="12" t="str">
         <x:v>note</x:v>
       </x:c>
+      <x:c r="K2" s="12" t="str">
+        <x:v>required_role_level</x:v>
+      </x:c>
+      <x:c r="L2" s="12" t="str">
+        <x:v>page_item_id</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="15" t="str">
@@ -33097,78 +33517,354 @@
       <x:c r="J3" s="15" t="str">
         <x:v>string / 可空 / none</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="19"/>
-      <x:c r="B4" s="16"/>
-      <x:c r="C4" s="16"/>
-      <x:c r="D4" s="17"/>
-      <x:c r="E4" s="16"/>
-      <x:c r="F4" s="17"/>
-      <x:c r="G4" s="2"/>
-      <x:c r="H4" s="17"/>
-      <x:c r="I4" s="18"/>
-      <x:c r="J4" s="18"/>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="19"/>
-      <x:c r="B5" s="16"/>
-      <x:c r="C5" s="16"/>
-      <x:c r="D5" s="17"/>
-      <x:c r="E5" s="16"/>
-      <x:c r="F5" s="17"/>
-      <x:c r="G5" s="2"/>
-      <x:c r="H5" s="17"/>
-      <x:c r="I5" s="18"/>
-      <x:c r="J5" s="18"/>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="19"/>
-      <x:c r="B6" s="16"/>
-      <x:c r="C6" s="16"/>
-      <x:c r="D6" s="17"/>
-      <x:c r="E6" s="16"/>
-      <x:c r="F6" s="17"/>
-      <x:c r="G6" s="2"/>
-      <x:c r="H6" s="17"/>
-      <x:c r="I6" s="18"/>
-      <x:c r="J6" s="18"/>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="19"/>
-      <x:c r="B7" s="16"/>
-      <x:c r="C7" s="16"/>
-      <x:c r="D7" s="17"/>
-      <x:c r="E7" s="16"/>
-      <x:c r="F7" s="17"/>
-      <x:c r="G7" s="2"/>
-      <x:c r="H7" s="17"/>
-      <x:c r="I7" s="18"/>
-      <x:c r="J7" s="18"/>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="19"/>
-      <x:c r="B8" s="16"/>
-      <x:c r="C8" s="16"/>
-      <x:c r="D8" s="17"/>
-      <x:c r="E8" s="16"/>
-      <x:c r="F8" s="17"/>
-      <x:c r="G8" s="2"/>
-      <x:c r="H8" s="17"/>
-      <x:c r="I8" s="18"/>
-      <x:c r="J8" s="18"/>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="19"/>
-      <x:c r="B9" s="16"/>
-      <x:c r="C9" s="16"/>
-      <x:c r="D9" s="17"/>
-      <x:c r="E9" s="16"/>
-      <x:c r="F9" s="17"/>
-      <x:c r="G9" s="2"/>
-      <x:c r="H9" s="17"/>
-      <x:c r="I9" s="18"/>
-      <x:c r="J9" s="18"/>
+      <x:c r="K3" s="15" t="str">
+        <x:v>int / 必填 / both</x:v>
+      </x:c>
+      <x:c r="L3" s="15" t="str">
+        <x:v>int / 必填 / both</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="70" hidden="0" customHeight="1">
+      <x:c r="A4" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="17" t="str">
+        <x:v>[{"item_id":7,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F4" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G4" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I4" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J4" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L4" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="70" hidden="0" customHeight="1">
+      <x:c r="A5" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="17" t="str">
+        <x:v>[{"item_id":7,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F5" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I5" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J5" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L5" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="70" hidden="0" customHeight="1">
+      <x:c r="A6" s="19" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="17" t="str">
+        <x:v>[{"item_id":7,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F6" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G6" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I6" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J6" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K6" s="16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L6" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="70" hidden="0" customHeight="1">
+      <x:c r="A7" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="str">
+        <x:v>[{"item_id":21,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G7" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I7" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J7" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K7" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L7" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="70" hidden="0" customHeight="1">
+      <x:c r="A8" s="19" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C8" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="str">
+        <x:v>[{"item_id":21,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E8" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I8" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J8" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L8" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="70" hidden="0" customHeight="1">
+      <x:c r="A9" s="19" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D9" s="17" t="str">
+        <x:v>[{"item_id":21,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I9" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L9" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="70" customHeight="1">
+      <x:c r="A10" s="19" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="str">
+        <x:v>[{"item_id":1,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I10" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K10" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L10" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="70" customHeight="1">
+      <x:c r="A11" s="19" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="str">
+        <x:v>[{"item_id":1,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I11" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K11" s="16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L11" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="70" customHeight="1">
+      <x:c r="A12" s="19" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="str">
+        <x:v>[{"item_id":1,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I12" s="18" t="str">
+        <x:v>用户2026-10-27：每阶技能书=目标阶+1；docs/技能获取与升级实施边界.md（页与等级门槛候选）</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K12" s="16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L12" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
@@ -36470,18 +37166,104 @@
         <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="19"/>
-      <x:c r="B9" s="16"/>
-      <x:c r="C9" s="16"/>
+    <x:row r="9" ht="70" hidden="0" customHeight="1">
+      <x:c r="A9" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="D9" s="17"/>
-      <x:c r="E9" s="16"/>
-      <x:c r="F9" s="16"/>
-      <x:c r="G9" s="16"/>
-      <x:c r="H9" s="17"/>
-      <x:c r="I9" s="17"/>
-      <x:c r="J9" s="18"/>
-      <x:c r="K9" s="18"/>
+      <x:c r="E9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="70" customHeight="1">
+      <x:c r="A10" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I10" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="70" customHeight="1">
+      <x:c r="A11" s="19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I11" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
@@ -44963,16 +45745,16 @@
         <x:v>first_loop_closed_development</x:v>
       </x:c>
       <x:c r="C4" s="17" t="str">
-        <x:v>{"rule_version":3,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"skills":[{"learn_level":7,"learned_level":0,"mp_base_cost":3,"mp_level_cost":2,"cooldown_base_ms":1800,"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"range_cells":9,"delay_base_ms":500,"accuracy_per_level":0,"power_bonus":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"id":1,"name":"火球术","job_id":1,"book_item_id":7,"behavior":"fireball","projectile_ms_per_cell":50,"target_move_tolerance_cells":2,"power_base":2,"mpower_base":8},{"learn_level":7,"learned_level":0,"mp_base_cost":3,"mp_level_cost":2,"cooldown_base_ms":1800,"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"range_cells":9,"delay_base_ms":500,"accuracy_per_level":0,"power_bonus":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"id":2,"name":"治愈术","job_id":2,"book_item_id":21,"behavior":"healing","projectile_ms_per_cell":0,"target_move_tolerance_cells":0,"power_base":0,"mpower_base":14},{"learn_level":7,"learned_level":0,"mp_base_cost":0,"mp_level_cost":0,"cooldown_base_ms":1800,"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"range_cells":0,"delay_base_ms":0,"accuracy_per_level":3,"power_bonus":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"id":3,"name":"基本剑术","job_id":0,"book_item_id":1,"behavior":"fencing","projectile_ms_per_cell":0,"target_move_tolerance_cells":0,"power_base":0,"mpower_base":0}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}]}</x:v>
+        <x:v>{"rule_version":4,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1}</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）</x:v>
+        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>仅development候选。红蓝药与首组三职业技能；完整技能、升级、1.80还原及正式发布仍待验收。来源与例外见技能/药品边界文档。</x:v>
+        <x:v>仅development候选；技能数值已迁入技能基础定义与逐级扩展，不保留平行技能参数。书本公式按用户；页/报价/开发掉落仍待平衡。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -2,101 +2,101 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R4a446053f0d445f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R9a68b6b3631f4457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Re3963f1b06fd42fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="R5199767e057e4193"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="Rb187396033d842db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="R7ce00b25f624475b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R84cf22d68f684b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R99e75a614a9147e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R42bfe4fe41d246ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="Rafd3659511a5496e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="R5b4735e34b6c4dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R19488783206b4dfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R24b87d25257242e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Rfd3adc7253a74b85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="Rb4aea4f4656848a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="Rd479a0f12130459a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R65a3c4e9f32b4c47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R658e43f2665c4676"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R18f5e61d87654271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R0a43034c71c74736"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="Rf41f89b14a424b3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="Rac28d13ce501470f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R2138b25026994695"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R47b14fdb43ef4703"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="R5e860261b1924b48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="R75fe4b6f27344a19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="Rc741a8788e7d454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="Rdaeead3348c44e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="Ra1fd52784e4843d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R75ab300ad3bc471b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="Re2431555b2da416b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="R04a5963b72254f56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R6ec5356c93e04191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R2c6bf35fc6a64715"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Re175e5dc5fce4fb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="Rf4efd8f36f1744ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R6147c85dab7042ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R7adb023fca4243da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R48f839df00c04dcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="Rab16edb15f554909"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="Re339e8531199460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R2cbc666458b04354"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="Re0bc92ef6ab84520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="R12a2291fb44a476f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="Re0f5920ad98f42f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="R1e51525dc56d4728"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="Rc2f086b8365741bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R62bd1d0435254210"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R4250fbe5a4854e2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="Rbd902b8c3d294828"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R5a8d17b6f2ae4934"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="R306cdbe523e64a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Ra3c5e96d716a4adf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R25ec5d0e4ac04637"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="Rb6135214a8eb4e25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R7218adc1798e45b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="Rfe98e538e58f47cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R0b18111adf054269"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="Rebfa4fffe9c741bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R7f3877472aac4dcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="Rfe86f68e0f0b44de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="Ra21c0a56b5794a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R154b30958e544c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R928bff76f5e3400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R932d84cc64ae4769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="Rd08639de67c9475d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R00e17b50e8fb4ecc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="R9ec044d49d334374"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="R32e41d9ed3c8484f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R4dcb3ecb2e774334"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Re7e0bf38509749c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R36f707e594c148c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R7e045910c8dc4c53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Ra623b3348c574246"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R85905960f8044156"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="R94437812f02f499d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Ra6cfee0aa59f4e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="Rc1410b7441c24520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R44c3add78bcc4e2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="R80fe5ed22b604518"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R3adfe257c87e44c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="Ra4fe03525ac74170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rfc4bb70541f74491"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="Re79b0315c9984dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="Rb3c3e8f7c1074c6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R54ff0b1a7c284fcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="R3e76750798ff47e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="Rd067ecb7ae994da6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Re222824bbf0d403f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R06065ddc61b84938"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R5cca22d53ab84fcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R7848443fb8164174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="Ref7d114d823f483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="R532ecf91ebf04310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="R81b287beee4d4dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R1fed9b799c074be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="Rbcfc6e28eb904f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="R48b93137c88a4cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rf8d4d1cbe3c44e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R97585a857b4948ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="Rf3d9f02dc0f9425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R4d864b483b5d464d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="Rad4ac899d1904ffb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R1f06824924a24a2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R7716683f56da4e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="R45f8c5ece69a45dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="Rfe276755c34d48eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R10849a785b5a461b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Rcb9f586989394832"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="R912a12c62cac4833"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="R3c28f1c166704df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R31a5134bc6694ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="Rf5e576e3576d4104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="Ra4adb3c0138a48aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R555a4f0e2d2c4eb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R9bd01bc2ccc946f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="R51b1450d45ef4e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R0a3cc86bea58426a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R9fbceff823264357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="Rb1168f6e31424a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="R31b5450129804db6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="R7e0864c2b17e46e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="Rf57bbeb086f74918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="Re226a7daa899469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R4af5bc7cb4a44668"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="R1ee8da1421d44140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Re8b3b9069f51435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R84efa964143143d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R7310b4c7e97b41a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="R8e49938c36d24262"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="R02ca1ccbf60b4aa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R8e639d89ca5e4284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R8cfdf1c10db64c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="Rd2decad8e4704759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R924c4f09318043eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="R5a6e35f506d948b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R2445d994f06048df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R880454c7492d4f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="Rb38066bd8cdd46ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="R68bd15990fdb40a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="R7bba55e529b94cb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R1c5ec022cb004a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="Ra0a007548122452d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="Rca2eec92ca4a48fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="Rf825a3843f314339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R7158536d60024cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="Ree1a62875153412e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Rd2d3b457413f4830"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="Re0892139a0ac4106"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="Rb4d6b446fc444e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R838e21a11c2c4532"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="Re1edf9f98ee2402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="Rdd5ef54f1f3540c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R1d4a04bb418c4e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="Ra8f9c2d64952429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="Re82ed3235f944920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R8facf2bbbfde442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R082bb3de2bf4470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R880e1015c6654e17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R2c63e6ba02814490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R71bf74b5f96b4b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R75ffc19fb7444a0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="R6e7c526faada488e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="R57bb98dea43f4a41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R53ffda69848a4c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Rf4c47d97531849e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R521f2258c4ad433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R80e5df48686d4def"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Ra13f02e6b86143d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="Rba62d6eff69d4e96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="Rb7cfdb44fc994656"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rbb710f0a4dd44d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="R9f49f000e20c41a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R2b6194599c2c4a87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="Ra2cf678f769a48f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="Rdc7d1b183d574ef2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R2245024173064094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rf611502ae1b4473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R436b3c1f3ad84588"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="Rf71940e649dd4c4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="Re655c82bfcd94c41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="Rf2ab31ff2b144c76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="R8db5280710064ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Ra5f5f945e42843e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R34a18b9848204f5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R9a7222b6dc864522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R37aaeda023234c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R72bfd0b2d4034abb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="Rff362490a0664995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Rc90dc3e9942444f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8092,7 +8092,7 @@
       </x:c>
       <x:c r="C39" s="2" t="n">
         <x:f>COUNTA('商城商品候选'!$A$4:$A$10003)</x:f>
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"confirmed")</x:f>
@@ -8100,7 +8100,7 @@
       </x:c>
       <x:c r="E39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"candidate")</x:f>
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"unverified")</x:f>
@@ -8588,7 +8588,7 @@
       </x:c>
       <x:c r="C55" s="2" t="n">
         <x:f>COUNTA('物品定义'!$A$4:$A$10003)</x:f>
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"confirmed")</x:f>
@@ -8596,7 +8596,7 @@
       </x:c>
       <x:c r="E55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"candidate")</x:f>
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"unverified")</x:f>
@@ -8867,7 +8867,7 @@
       </x:c>
       <x:c r="C64" s="2" t="n">
         <x:f>COUNTA('技能基础定义'!$A$4:$A$10003)</x:f>
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"confirmed")</x:f>
@@ -8875,7 +8875,7 @@
       </x:c>
       <x:c r="E64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"candidate")</x:f>
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"unverified")</x:f>
@@ -8898,7 +8898,7 @@
       </x:c>
       <x:c r="C65" s="2" t="n">
         <x:f>COUNTA('技能逐级扩展'!$A$4:$A$10003)</x:f>
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"confirmed")</x:f>
@@ -8906,7 +8906,7 @@
       </x:c>
       <x:c r="E65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"candidate")</x:f>
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"unverified")</x:f>
@@ -9177,7 +9177,7 @@
       </x:c>
       <x:c r="C74" s="2" t="n">
         <x:f>COUNTA('掉落条目'!$A$4:$A$10003)</x:f>
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"confirmed")</x:f>
@@ -9185,7 +9185,7 @@
       </x:c>
       <x:c r="E74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"candidate")</x:f>
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"unverified")</x:f>
@@ -22399,6 +22399,176 @@
       </x:c>
       <x:c r="L11" s="17" t="n">
         <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="70" customHeight="1">
+      <x:c r="A12" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="str">
+        <x:v>skill_book_4</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="str">
+        <x:v>《精神力战法》</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E12" s="16"/>
+      <x:c r="F12" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="16"/>
+      <x:c r="I12" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="str">
+        <x:v>MYF stditems item22源Price600；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L12" s="17" t="n">
+        <x:v>600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="70" customHeight="1">
+      <x:c r="A13" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:v>skill_book_5</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>《大火球》</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E13" s="16"/>
+      <x:c r="F13" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="16"/>
+      <x:c r="I13" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="str">
+        <x:v>MYF stditems item12源Price2000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L13" s="17" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="70" customHeight="1">
+      <x:c r="A14" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B14" s="17" t="str">
+        <x:v>skill_book_11</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="str">
+        <x:v>《雷电术》</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E14" s="16"/>
+      <x:c r="F14" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="16"/>
+      <x:c r="I14" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="str">
+        <x:v>MYF stditems item11源Price1600；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L14" s="17" t="n">
+        <x:v>1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="70" customHeight="1">
+      <x:c r="A15" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B15" s="17" t="str">
+        <x:v>skill_book_23</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="str">
+        <x:v>《爆裂火焰》</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E15" s="16"/>
+      <x:c r="F15" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="16"/>
+      <x:c r="I15" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="str">
+        <x:v>MYF stditems item14源Price3000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L15" s="17" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="70" customHeight="1">
+      <x:c r="A16" s="19" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="17" t="str">
+        <x:v>skill_book_29</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="str">
+        <x:v>《群体治疗术》</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E16" s="16"/>
+      <x:c r="F16" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="16"/>
+      <x:c r="I16" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="str">
+        <x:v>MYF stditems item32源Price15000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L16" s="17" t="n">
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -29770,6 +29940,191 @@
         <x:v>65535为本项目开发计数堆叠上限候选；不合并不同来源/绑定，图标尚待制作。</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="70" customHeight="1">
+      <x:c r="A12" s="19" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="str">
+        <x:v>skill_book_4</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="str">
+        <x:v>《精神力战法》</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="16"/>
+      <x:c r="G12" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J12" s="17"/>
+      <x:c r="K12" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L12" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:24；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M12" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="70" customHeight="1">
+      <x:c r="A13" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:v>skill_book_5</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>《大火球》</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="16"/>
+      <x:c r="G13" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J13" s="17"/>
+      <x:c r="K13" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L13" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:14；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M13" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="70" customHeight="1">
+      <x:c r="A14" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B14" s="17" t="str">
+        <x:v>skill_book_11</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="str">
+        <x:v>《雷电术》</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="16"/>
+      <x:c r="G14" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J14" s="17"/>
+      <x:c r="K14" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L14" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:13；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M14" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="70" customHeight="1">
+      <x:c r="A15" s="19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="17" t="str">
+        <x:v>skill_book_23</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="str">
+        <x:v>《爆裂火焰》</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="16"/>
+      <x:c r="G15" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J15" s="17"/>
+      <x:c r="K15" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L15" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:16；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M15" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="70" customHeight="1">
+      <x:c r="A16" s="19" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B16" s="17" t="str">
+        <x:v>skill_book_29</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="str">
+        <x:v>《群体治疗术》</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="16"/>
+      <x:c r="G16" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J16" s="17"/>
+      <x:c r="K16" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L16" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:34；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M16" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="382" priority="1">
@@ -29995,7 +30350,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="17" t="str">
-        <x:v>{"physical_attack_min":2,"physical_attack_max":5,"physical_defence_min":0,"physical_defence_max":0,"magic_defence_min":0,"magic_defence_max":0}</x:v>
+        <x:v>{"physical_attack_min":2,"physical_attack_max":5,"physical_defence_min":0,"physical_defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"attack_speed":0}</x:v>
       </x:c>
       <x:c r="I4" s="16" t="n">
         <x:v>4000</x:v>
@@ -30013,7 +30368,7 @@
         <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:220</x:v>
       </x:c>
       <x:c r="N4" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 品质0、阶段0是开发夹具对接本项目枚举的工程选择；不把来源Color当品质。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 品质0、阶段0是开发夹具对接本项目枚举的工程选择；不把来源Color当品质。 首组开发装备未接额外攻速词条，本轮明确attack_speed=0适配；不证明源服全部词条。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -30039,7 +30394,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="17" t="str">
-        <x:v>{"physical_attack_min":0,"physical_attack_max":0,"physical_defence_min":2,"physical_defence_max":2,"magic_defence_min":0,"magic_defence_max":1}</x:v>
+        <x:v>{"physical_attack_min":0,"physical_attack_max":0,"physical_defence_min":2,"physical_defence_max":2,"magic_defence_min":0,"magic_defence_max":1,"attack_speed":0}</x:v>
       </x:c>
       <x:c r="I5" s="16" t="n">
         <x:v>10000</x:v>
@@ -30057,7 +30412,7 @@
         <x:v>最终策划案.md:113-115、485-497（4.2、4.20）；资料参考/myf/Mud2/DB/ApexM2_stditems.csv:195</x:v>
       </x:c>
       <x:c r="N5" s="18" t="str">
-        <x:v>来源原名布衣(男)。本作无性别穿戴门槛，不新增男女装备分类，同itemID按职业固定外观；允许职业[0,1,2]是目标规则适配。女法师衣服外观映射仍待正式资源验收。仅development候选，未通过目标1.80行为或数值验收。</x:v>
+        <x:v>来源原名布衣(男)。本作无性别穿戴门槛，不新增男女装备分类，同itemID按职业固定外观；允许职业[0,1,2]是目标规则适配。女法师衣服外观映射仍待正式资源验收。仅development候选，未通过目标1.80行为或数值验收。 首组开发装备未接额外攻速词条，本轮明确attack_speed=0适配；不证明源服全部词条。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -30656,7 +31011,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="17" t="str">
-        <x:v>{"mp":0,"physical_attack_min":1,"physical_attack_max":2,"physical_defence_min":0,"physical_defence_max":0,"magic_defence":0,"accuracy":5,"agility":10}</x:v>
+        <x:v>{"mp":0,"physical_attack_min":1,"physical_attack_max":2,"physical_defence_min":0,"physical_defence_max":0,"magic_defence":0,"accuracy":5,"agility":10,"undead":true}</x:v>
       </x:c>
       <x:c r="H4" s="16" t="n">
         <x:v>2500</x:v>
@@ -30685,7 +31040,7 @@
         <x:v>资料参考/myf/Mud2/DB/ApexM2_Monster.csv:13；client/assets/resources/development/manifest.json</x:v>
       </x:c>
       <x:c r="R4" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 本轮Undead仅按原CSV字段显式投影，不能凭名称推断。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -30708,7 +31063,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G5" s="17" t="str">
-        <x:v>{"mp":0,"physical_attack_min":10,"physical_attack_max":20,"physical_defence_min":10,"physical_defence_max":10,"magic_defence":10,"accuracy":15,"agility":20}</x:v>
+        <x:v>{"mp":0,"physical_attack_min":10,"physical_attack_max":20,"physical_defence_min":10,"physical_defence_max":10,"magic_defence":10,"accuracy":15,"agility":20,"undead":true}</x:v>
       </x:c>
       <x:c r="H5" s="16" t="n">
         <x:v>1000</x:v>
@@ -30735,7 +31090,7 @@
         <x:v>资料参考/myf/Mud2/DB/ApexM2_Monster.csv:381；client/assets/resources/development/manifest.json</x:v>
       </x:c>
       <x:c r="R5" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 本轮Undead仅按原CSV字段显式投影，不能凭名称推断。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -33068,7 +33423,7 @@
         <x:v>fireball</x:v>
       </x:c>
       <x:c r="G5" s="17" t="str">
-        <x:v>{"kind":"active_monster","range_cells":9,"target_move_tolerance_cells":2}</x:v>
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":10,"auto_min_targets":1}</x:v>
       </x:c>
       <x:c r="H5" s="16"/>
       <x:c r="I5" s="16" t="n">
@@ -33102,7 +33457,7 @@
         <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
       </x:c>
       <x:c r="S5" s="18" t="str">
-        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。</x:v>
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
       </x:c>
       <x:c r="T5" s="17" t="n">
         <x:v>7</x:v>
@@ -33114,7 +33469,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W5" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":2,"power_bonus":0,"mpower_base":8,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":2,"power_bonus":0,"mpower_base":8,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" hidden="0" customHeight="1">
@@ -33137,7 +33492,7 @@
         <x:v>healing</x:v>
       </x:c>
       <x:c r="G6" s="17" t="str">
-        <x:v>{"kind":"friendly_self_pet","range_cells":9,"target_move_tolerance_cells":0}</x:v>
+        <x:v>{"kind":"friendly_entity","range_cells":9,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1}</x:v>
       </x:c>
       <x:c r="H6" s="16"/>
       <x:c r="I6" s="16" t="n">
@@ -33171,7 +33526,7 @@
         <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
       </x:c>
       <x:c r="S6" s="18" t="str">
-        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。</x:v>
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
       </x:c>
       <x:c r="T6" s="17" t="n">
         <x:v>21</x:v>
@@ -33183,7 +33538,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W6" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":14,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":14,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":2,"add_caster_level":true,"undead_multiplier_ppm":1000000}</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="70" hidden="0" customHeight="1">
@@ -33206,7 +33561,7 @@
         <x:v>fencing</x:v>
       </x:c>
       <x:c r="G7" s="17" t="str">
-        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0}</x:v>
+        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0}</x:v>
       </x:c>
       <x:c r="H7" s="16"/>
       <x:c r="I7" s="16" t="n">
@@ -33240,7 +33595,7 @@
         <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
       </x:c>
       <x:c r="S7" s="18" t="str">
-        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。</x:v>
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
       </x:c>
       <x:c r="T7" s="17" t="n">
         <x:v>1</x:v>
@@ -33252,50 +33607,353 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W7" s="17" t="str">
-        <x:v>{"accuracy_per_level":3,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0}</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="19"/>
-      <x:c r="B8" s="17"/>
-      <x:c r="C8" s="17"/>
-      <x:c r="D8" s="16"/>
-      <x:c r="E8" s="16"/>
-      <x:c r="F8" s="17"/>
-      <x:c r="G8" s="17"/>
+        <x:v>{"accuracy_per_level":3,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,3,6,9],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="70" hidden="0" customHeight="1">
+      <x:c r="A8" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
+        <x:v>source_spirit_sword</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>精神力战法</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E8" s="16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F8" s="17" t="str">
+        <x:v>spirit_sword</x:v>
+      </x:c>
+      <x:c r="G8" s="17" t="str">
+        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0}</x:v>
+      </x:c>
       <x:c r="H8" s="16"/>
-      <x:c r="I8" s="16"/>
-      <x:c r="J8" s="17"/>
-      <x:c r="K8" s="17"/>
-      <x:c r="L8" s="17"/>
-      <x:c r="M8" s="17"/>
-      <x:c r="N8" s="17"/>
-      <x:c r="O8" s="17"/>
-      <x:c r="P8" s="2"/>
-      <x:c r="Q8" s="17"/>
-      <x:c r="R8" s="18"/>
-      <x:c r="S8" s="18"/>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="19"/>
-      <x:c r="B9" s="17"/>
-      <x:c r="C9" s="17"/>
-      <x:c r="D9" s="16"/>
-      <x:c r="E9" s="16"/>
-      <x:c r="F9" s="17"/>
-      <x:c r="G9" s="17"/>
+      <x:c r="I8" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0}</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="str">
+        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L8" s="17" t="str">
+        <x:v>spirit_sword</x:v>
+      </x:c>
+      <x:c r="M8" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N8" s="17" t="str">
+        <x:v>passive</x:v>
+      </x:c>
+      <x:c r="O8" s="17" t="str">
+        <x:v>development_source_spirit_sword_v1</x:v>
+      </x:c>
+      <x:c r="P8" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R8" s="18" t="str">
+        <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S8" s="18" t="str">
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+      </x:c>
+      <x:c r="T8" s="17" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="U8" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V8" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W8" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,3,5,8],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="70" hidden="0" customHeight="1">
+      <x:c r="A9" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="17" t="str">
+        <x:v>source_great_fireball</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>大火球</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F9" s="17" t="str">
+        <x:v>great_fireball</x:v>
+      </x:c>
+      <x:c r="G9" s="17" t="str">
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":20,"auto_min_targets":1}</x:v>
+      </x:c>
       <x:c r="H9" s="16"/>
-      <x:c r="I9" s="16"/>
-      <x:c r="J9" s="17"/>
-      <x:c r="K9" s="17"/>
-      <x:c r="L9" s="17"/>
-      <x:c r="M9" s="17"/>
-      <x:c r="N9" s="17"/>
-      <x:c r="O9" s="17"/>
-      <x:c r="P9" s="2"/>
-      <x:c r="Q9" s="17"/>
-      <x:c r="R9" s="18"/>
-      <x:c r="S9" s="18"/>
+      <x:c r="I9" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J9" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50}</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="str">
+        <x:v>{"mp_base_cost":5,"mp_level_cost":1,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L9" s="17" t="str">
+        <x:v>great_fireball</x:v>
+      </x:c>
+      <x:c r="M9" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N9" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O9" s="17" t="str">
+        <x:v>development_source_great_fireball_v1</x:v>
+      </x:c>
+      <x:c r="P9" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R9" s="18" t="str">
+        <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S9" s="18" t="str">
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+      </x:c>
+      <x:c r="T9" s="17" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="U9" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V9" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W9" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":10,"power_bonus":0,"mpower_base":6,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="70" customHeight="1">
+      <x:c r="A10" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B10" s="17" t="str">
+        <x:v>source_thunderbolt</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="str">
+        <x:v>雷电术</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="str">
+        <x:v>thunderbolt</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="str">
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1}</x:v>
+      </x:c>
+      <x:c r="H10" s="16"/>
+      <x:c r="I10" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0}</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="str">
+        <x:v>{"mp_base_cost":9,"mp_level_cost":2,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L10" s="17" t="str">
+        <x:v>thunderbolt</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N10" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O10" s="17" t="str">
+        <x:v>development_source_thunderbolt_v1</x:v>
+      </x:c>
+      <x:c r="P10" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R10" s="18" t="str">
+        <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S10" s="18" t="str">
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+      </x:c>
+      <x:c r="T10" s="17" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="U10" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V10" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W10" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":9,"power_bonus":0,"mpower_base":8,"mpower_bonus":20,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1500000}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="70" customHeight="1">
+      <x:c r="A11" s="19" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="str">
+        <x:v>source_firebang</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="str">
+        <x:v>爆裂火焰</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="str">
+        <x:v>firebang</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="str">
+        <x:v>{"kind":"enemy_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2}</x:v>
+      </x:c>
+      <x:c r="H11" s="16"/>
+      <x:c r="I11" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0}</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="str">
+        <x:v>{"mp_base_cost":14,"mp_level_cost":4,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L11" s="17" t="str">
+        <x:v>firebang</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N11" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O11" s="17" t="str">
+        <x:v>development_source_firebang_v1</x:v>
+      </x:c>
+      <x:c r="P11" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R11" s="18" t="str">
+        <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S11" s="18" t="str">
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+      </x:c>
+      <x:c r="T11" s="17" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="U11" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V11" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W11" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":8,"power_bonus":0,"mpower_base":8,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="70" customHeight="1">
+      <x:c r="A12" s="19" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="str">
+        <x:v>source_mass_healing</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="str">
+        <x:v>群体治疗术</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="str">
+        <x:v>mass_healing</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="str">
+        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2}</x:v>
+      </x:c>
+      <x:c r="H12" s="16"/>
+      <x:c r="I12" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0}</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="str">
+        <x:v>{"mp_base_cost":28,"mp_level_cost":3,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L12" s="17" t="str">
+        <x:v>mass_healing</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N12" s="17" t="str">
+        <x:v>player_male.casting</x:v>
+      </x:c>
+      <x:c r="O12" s="17" t="str">
+        <x:v>development_source_mass_healing_v1</x:v>
+      </x:c>
+      <x:c r="P12" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R12" s="18" t="str">
+        <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S12" s="18" t="str">
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+      </x:c>
+      <x:c r="T12" s="17" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="U12" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V12" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W12" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":4,"power_bonus":0,"mpower_base":10,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":1,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
@@ -33866,6 +34524,576 @@
         <x:v>900001</x:v>
       </x:c>
     </x:row>
+    <x:row r="13" ht="70" customHeight="1">
+      <x:c r="A13" s="19" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="str">
+        <x:v>[{"item_id":22,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I13" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K13" s="16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L13" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="70" customHeight="1">
+      <x:c r="A14" s="19" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="str">
+        <x:v>[{"item_id":22,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I14" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K14" s="16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L14" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="70" customHeight="1">
+      <x:c r="A15" s="19" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="str">
+        <x:v>[{"item_id":22,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I15" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K15" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L15" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="70" customHeight="1">
+      <x:c r="A16" s="19" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="str">
+        <x:v>[{"item_id":12,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G16" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I16" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K16" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L16" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="70" customHeight="1">
+      <x:c r="A17" s="19" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="str">
+        <x:v>[{"item_id":12,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I17" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K17" s="16" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L17" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="70" customHeight="1">
+      <x:c r="A18" s="19" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="str">
+        <x:v>[{"item_id":12,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I18" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K18" s="16" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L18" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="70" customHeight="1">
+      <x:c r="A19" s="19" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B19" s="16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="str">
+        <x:v>[{"item_id":11,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G19" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I19" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K19" s="16" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L19" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="70" customHeight="1">
+      <x:c r="A20" s="19" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B20" s="16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="str">
+        <x:v>[{"item_id":11,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I20" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K20" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L20" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="70" customHeight="1">
+      <x:c r="A21" s="19" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="str">
+        <x:v>[{"item_id":11,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G21" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I21" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K21" s="16" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L21" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="70" customHeight="1">
+      <x:c r="A22" s="19" t="n">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B22" s="16" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="str">
+        <x:v>[{"item_id":14,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G22" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I22" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K22" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L22" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="70" customHeight="1">
+      <x:c r="A23" s="19" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B23" s="16" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="str">
+        <x:v>[{"item_id":14,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G23" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I23" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K23" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L23" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="70" customHeight="1">
+      <x:c r="A24" s="19" t="n">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B24" s="16" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="str">
+        <x:v>[{"item_id":14,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E24" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I24" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K24" s="16" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L24" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="70" customHeight="1">
+      <x:c r="A25" s="19" t="n">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B25" s="16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C25" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="str">
+        <x:v>[{"item_id":32,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E25" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G25" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H25" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I25" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K25" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L25" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="70" customHeight="1">
+      <x:c r="A26" s="19" t="n">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B26" s="16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C26" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="str">
+        <x:v>[{"item_id":32,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E26" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H26" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I26" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K26" s="16" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L26" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="70" customHeight="1">
+      <x:c r="A27" s="19" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B27" s="16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C27" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="str">
+        <x:v>[{"item_id":32,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E27" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G27" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I27" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="str">
+        <x:v>书本公式已定；书页5/10/20与门槛候选；rank0至3只改变各自数值，不扩大3×3或改变目标过滤。</x:v>
+      </x:c>
+      <x:c r="K27" s="16" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="L27" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="508" priority="1">
@@ -37262,6 +38490,171 @@
         <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
       </x:c>
       <x:c r="K11" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="70" customHeight="1">
+      <x:c r="A12" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I12" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="70" customHeight="1">
+      <x:c r="A13" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="70" customHeight="1">
+      <x:c r="A14" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="70" customHeight="1">
+      <x:c r="A15" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="70" customHeight="1">
+      <x:c r="A16" s="19" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="str">
         <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
       </x:c>
     </x:row>
@@ -45745,16 +47138,16 @@
         <x:v>first_loop_closed_development</x:v>
       </x:c>
       <x:c r="C4" s="17" t="str">
-        <x:v>{"rule_version":4,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1}</x:v>
+        <x:v>{"rule_version":5,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16}}</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md</x:v>
+        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>仅development候选；技能数值已迁入技能基础定义与逐级扩展，不保留平行技能参数。书本公式按用户；页/报价/开发掉落仍待平衡。</x:v>
+        <x:v>仅development候选；8技能与3×3范围、普通前格延迟命中及逐杀结算；书本按用户，升级页/学习门槛/书价/开发渠道仍候选。数字只维护本工作簿。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -2,101 +2,101 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R1fed9b799c074be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="Rbcfc6e28eb904f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="R48b93137c88a4cc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rf8d4d1cbe3c44e1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R97585a857b4948ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="Rf3d9f02dc0f9425c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R4d864b483b5d464d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="Rad4ac899d1904ffb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R1f06824924a24a2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R7716683f56da4e79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="R45f8c5ece69a45dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="Rfe276755c34d48eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R10849a785b5a461b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Rcb9f586989394832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="R912a12c62cac4833"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="R3c28f1c166704df6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R31a5134bc6694ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="Rf5e576e3576d4104"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="Ra4adb3c0138a48aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R555a4f0e2d2c4eb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R9bd01bc2ccc946f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="R51b1450d45ef4e67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R0a3cc86bea58426a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R9fbceff823264357"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="Rb1168f6e31424a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="R31b5450129804db6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="R7e0864c2b17e46e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="Rf57bbeb086f74918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="Re226a7daa899469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R4af5bc7cb4a44668"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="R1ee8da1421d44140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Re8b3b9069f51435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R84efa964143143d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R7310b4c7e97b41a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="R8e49938c36d24262"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="R02ca1ccbf60b4aa8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R8e639d89ca5e4284"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R8cfdf1c10db64c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="Rd2decad8e4704759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R924c4f09318043eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="R5a6e35f506d948b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R2445d994f06048df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R880454c7492d4f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="Rb38066bd8cdd46ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="R68bd15990fdb40a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="R7bba55e529b94cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R1c5ec022cb004a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="Ra0a007548122452d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="Rca2eec92ca4a48fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="Rf825a3843f314339"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R7158536d60024cf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="Ree1a62875153412e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Rd2d3b457413f4830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="Re0892139a0ac4106"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="Rb4d6b446fc444e2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R838e21a11c2c4532"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="Re1edf9f98ee2402e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="Rdd5ef54f1f3540c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R1d4a04bb418c4e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="Ra8f9c2d64952429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="Re82ed3235f944920"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R8facf2bbbfde442a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R082bb3de2bf4470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R880e1015c6654e17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R2c63e6ba02814490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R71bf74b5f96b4b9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R75ffc19fb7444a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="R6e7c526faada488e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="R57bb98dea43f4a41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R53ffda69848a4c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Rf4c47d97531849e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R521f2258c4ad433b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R80e5df48686d4def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Ra13f02e6b86143d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="Rba62d6eff69d4e96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="Rb7cfdb44fc994656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rbb710f0a4dd44d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="R9f49f000e20c41a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R2b6194599c2c4a87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="Ra2cf678f769a48f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="Rdc7d1b183d574ef2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R2245024173064094"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rf611502ae1b4473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R436b3c1f3ad84588"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="Rf71940e649dd4c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="Re655c82bfcd94c41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="Rf2ab31ff2b144c76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="R8db5280710064ea9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Ra5f5f945e42843e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R34a18b9848204f5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R9a7222b6dc864522"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R37aaeda023234c9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R72bfd0b2d4034abb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="Rff362490a0664995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Rc90dc3e9942444f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R186cb98bd3b4433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R6573dcb22e9e4cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Rd6f4b5968be0427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rcfd9030a1fc44bae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="Rdf472bb12e014c6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="Rdfd67b3435b44052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="Rdef71febdb514adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R7b1e61720eac4774"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="Rf93c56b033484362"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="Rdc5e7e3c9c234f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="Rb939b305108a458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="Rd3615c8fdf324670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R7ecfaa35df9541b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Rf08170645889449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="Rc5ea61b268744ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="R4d48bd63fd484675"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R368684891a494f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R9a331ca9a5584c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R567ac1eef9ad47b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R7f86926977914439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R49fc23d3253d46dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="Rbd3969ad5b2d4c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R91f3e79ba97e4e43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="Rc8702498d6e64c4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="Ree05f1ecd40a48aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="R201d2cce960a4883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="R167211da7937443d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="Rf5b793414cc44abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R44584fc725a04f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="Rbcc53996e9c24560"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="R4e16b35925694b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="R27ff2a66e7394596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="Rcc402075cd9c4760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="Rfa0618b49a9049cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Ra8ba7ce576bc4017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="R958c1dfa3bf44db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="Rad27edfaedf94610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R20a4f322734c4623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R151f23ad23dc420c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R2e9c664139024b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="Rd1105c6160204b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="Rd626544786d44eaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R8a231a9720a4410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="R9a1880d027c24a58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="R8753e99cbb964775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="R1f58923db7484851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R21c5080b5aa74328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R81f49477247e44e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R0aac7ef342a1407c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="R5de56f0f10c04d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="Rc2eb12b0956242e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="R448adfcc19fd4151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Ref5c8eea6f6843f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R722a10b9c7e74ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R46978fb319fc4e43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R2aa334e5cb4443a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="Rb562192a257247e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R95048fdaa6834df8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R9d76e9118ca24421"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R0b56b7e864be492d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R0fdcff641a48432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="Rd6875aba1f9d4329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R4624075301504a3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R0d8352e6a1924915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="Rd61669de43ad4489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R63b25fc073ad4a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="Rb7c8298337694e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="Rb269dd0ab7ec4078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="R02a4c7a369844ec4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R6a5da563018b4705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Rb9627010d8804a2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="Rbc59b0cbf1084dd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R714e543cb4fe40b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="R22906828ec2c4440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R3ee53b44ca334a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="R35e9d953975f4919"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rca977d57eb1845c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="Ra2631928573d4e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R77b0b43e57104888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="R5907ea7e96b94cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R0076c6b2353843c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R20d67cc89da640da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rdae166cbf87647d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R72201c05e3184954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="Rff81f98b17a944f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R8571b7dccab74a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="R9c8ff212a8224a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="Rbb2652e859744e2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Rf8857e11e00143f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R5217b743f0b340b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="Rceb5a3bc399c47af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R65296e028c4f4677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R14a2be3337fd4efb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="R11b07b34d725417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Ra38458ebf25d4289"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8092,7 +8092,7 @@
       </x:c>
       <x:c r="C39" s="2" t="n">
         <x:f>COUNTA('商城商品候选'!$A$4:$A$10003)</x:f>
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"confirmed")</x:f>
@@ -8100,7 +8100,7 @@
       </x:c>
       <x:c r="E39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"candidate")</x:f>
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"unverified")</x:f>
@@ -8588,7 +8588,7 @@
       </x:c>
       <x:c r="C55" s="2" t="n">
         <x:f>COUNTA('物品定义'!$A$4:$A$10003)</x:f>
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"confirmed")</x:f>
@@ -8596,7 +8596,7 @@
       </x:c>
       <x:c r="E55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"candidate")</x:f>
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"unverified")</x:f>
@@ -8867,7 +8867,7 @@
       </x:c>
       <x:c r="C64" s="2" t="n">
         <x:f>COUNTA('技能基础定义'!$A$4:$A$10003)</x:f>
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"confirmed")</x:f>
@@ -8875,7 +8875,7 @@
       </x:c>
       <x:c r="E64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"candidate")</x:f>
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"unverified")</x:f>
@@ -8898,7 +8898,7 @@
       </x:c>
       <x:c r="C65" s="2" t="n">
         <x:f>COUNTA('技能逐级扩展'!$A$4:$A$10003)</x:f>
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"confirmed")</x:f>
@@ -8906,7 +8906,7 @@
       </x:c>
       <x:c r="E65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"candidate")</x:f>
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"unverified")</x:f>
@@ -9177,7 +9177,7 @@
       </x:c>
       <x:c r="C74" s="2" t="n">
         <x:f>COUNTA('掉落条目'!$A$4:$A$10003)</x:f>
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"confirmed")</x:f>
@@ -9185,7 +9185,7 @@
       </x:c>
       <x:c r="E74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"candidate")</x:f>
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F74" s="2" t="n">
         <x:f>COUNTIFS('掉落条目'!$I$4:$I$10003,"unverified")</x:f>
@@ -22569,6 +22569,278 @@
       </x:c>
       <x:c r="L16" s="17" t="n">
         <x:v>15000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="70" customHeight="1">
+      <x:c r="A17" s="19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="17" t="str">
+        <x:v>skill_book_7</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="str">
+        <x:v>《攻杀剑术》</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E17" s="16"/>
+      <x:c r="F17" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="16"/>
+      <x:c r="I17" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="str">
+        <x:v>MYF stditems item2源Price2000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L17" s="17" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="70" customHeight="1">
+      <x:c r="A18" s="19" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B18" s="17" t="str">
+        <x:v>skill_book_12</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="str">
+        <x:v>《刺杀剑术》</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E18" s="16"/>
+      <x:c r="F18" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="16"/>
+      <x:c r="I18" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="str">
+        <x:v>MYF stditems item3源Price5000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L18" s="17" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="70" customHeight="1">
+      <x:c r="A19" s="19" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="17" t="str">
+        <x:v>skill_book_25</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="str">
+        <x:v>《半月弯刀》</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E19" s="16"/>
+      <x:c r="F19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="16"/>
+      <x:c r="I19" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="str">
+        <x:v>MYF stditems item4源Price8000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L19" s="17" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="70" customHeight="1">
+      <x:c r="A20" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="17" t="str">
+        <x:v>skill_book_26</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="str">
+        <x:v>《烈火剑法》</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E20" s="16"/>
+      <x:c r="F20" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="16"/>
+      <x:c r="I20" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="str">
+        <x:v>MYF stditems item6源Price20000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L20" s="17" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="70" customHeight="1">
+      <x:c r="A21" s="19" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B21" s="17" t="str">
+        <x:v>skill_book_10</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="str">
+        <x:v>《疾光电影》</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E21" s="16"/>
+      <x:c r="F21" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="16"/>
+      <x:c r="I21" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="str">
+        <x:v>MYF stditems item16源Price5000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L21" s="17" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="70" customHeight="1">
+      <x:c r="A22" s="19" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B22" s="17" t="str">
+        <x:v>skill_book_33</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="str">
+        <x:v>《冰咆哮》</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E22" s="16"/>
+      <x:c r="F22" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="16"/>
+      <x:c r="I22" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="str">
+        <x:v>MYF stditems item20源Price20000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L22" s="17" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="70" customHeight="1">
+      <x:c r="A23" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B23" s="17" t="str">
+        <x:v>skill_book_24</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="str">
+        <x:v>《地狱雷光》</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E23" s="16"/>
+      <x:c r="F23" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="16"/>
+      <x:c r="I23" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="str">
+        <x:v>MYF stditems item17源Price12000；本作development定价适配，非来源服实际成交核验</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L23" s="17" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="70" customHeight="1">
+      <x:c r="A24" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B24" s="17" t="str">
+        <x:v>skill_book_9</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="str">
+        <x:v>《地狱火》</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E24" s="16"/>
+      <x:c r="F24" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="16"/>
+      <x:c r="I24" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="str">
+        <x:v>MYF item10原Price1200作为development定价候选，非源服实库定价认证</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="str">
+        <x:v>金币绑定优先；本轮固定产物绑定，NPC书不允许拆页；金币回收价未定，暂拒绝分解。</x:v>
+      </x:c>
+      <x:c r="L24" s="17" t="n">
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -30122,6 +30394,302 @@
         <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:34；docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
       </x:c>
       <x:c r="M16" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="70" customHeight="1">
+      <x:c r="A17" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B17" s="17" t="str">
+        <x:v>skill_book_7</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="str">
+        <x:v>《攻杀剑术》</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="16"/>
+      <x:c r="G17" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J17" s="17"/>
+      <x:c r="K17" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L17" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:4；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M17" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="70" customHeight="1">
+      <x:c r="A18" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="17" t="str">
+        <x:v>skill_book_12</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="str">
+        <x:v>《刺杀剑术》</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="16"/>
+      <x:c r="G18" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J18" s="17"/>
+      <x:c r="K18" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L18" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:5；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M18" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="70" customHeight="1">
+      <x:c r="A19" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B19" s="17" t="str">
+        <x:v>skill_book_25</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="str">
+        <x:v>《半月弯刀》</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" s="16"/>
+      <x:c r="G19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J19" s="17"/>
+      <x:c r="K19" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L19" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:6；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M19" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="70" customHeight="1">
+      <x:c r="A20" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B20" s="17" t="str">
+        <x:v>skill_book_26</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="str">
+        <x:v>《烈火剑法》</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="16"/>
+      <x:c r="G20" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J20" s="17"/>
+      <x:c r="K20" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L20" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:8；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M20" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="70" customHeight="1">
+      <x:c r="A21" s="19" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" s="17" t="str">
+        <x:v>skill_book_10</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="str">
+        <x:v>《疾光电影》</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" s="16"/>
+      <x:c r="G21" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J21" s="17"/>
+      <x:c r="K21" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L21" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:18；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M21" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="70" customHeight="1">
+      <x:c r="A22" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B22" s="17" t="str">
+        <x:v>skill_book_33</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="str">
+        <x:v>《冰咆哮》</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" s="16"/>
+      <x:c r="G22" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J22" s="17"/>
+      <x:c r="K22" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L22" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:22；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M22" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="70" customHeight="1">
+      <x:c r="A23" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B23" s="17" t="str">
+        <x:v>skill_book_24</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="str">
+        <x:v>《地狱雷光》</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="16"/>
+      <x:c r="G23" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J23" s="17"/>
+      <x:c r="K23" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L23" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:19；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="M23" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="70" customHeight="1">
+      <x:c r="A24" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B24" s="17" t="str">
+        <x:v>skill_book_9</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="str">
+        <x:v>《地狱火》</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E24" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F24" s="16"/>
+      <x:c r="G24" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J24" s="17"/>
+      <x:c r="K24" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L24" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:12；用户2026-10-27审定地狱火所有阶固定正前4格；docs/战士攻击模式与方向技能实施边界.md；Crystal HumanObject.cs:4103–4118/Map.cs:875–910默认候选</x:v>
+      </x:c>
+      <x:c r="M24" s="18" t="str">
         <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
       </x:c>
     </x:row>
@@ -33423,14 +33991,14 @@
         <x:v>fireball</x:v>
       </x:c>
       <x:c r="G5" s="17" t="str">
-        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":10,"auto_min_targets":1}</x:v>
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":10,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
       </x:c>
       <x:c r="H5" s="16"/>
       <x:c r="I5" s="16" t="n">
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J5" s="17" t="str">
-        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50}</x:v>
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K5" s="17" t="str">
         <x:v>{"mp_base_cost":3,"mp_level_cost":2,"items":[]}</x:v>
@@ -33469,7 +34037,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W5" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":2,"power_bonus":0,"mpower_base":8,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":2,"power_bonus":0,"mpower_base":8,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" hidden="0" customHeight="1">
@@ -33492,14 +34060,14 @@
         <x:v>healing</x:v>
       </x:c>
       <x:c r="G6" s="17" t="str">
-        <x:v>{"kind":"friendly_entity","range_cells":9,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1}</x:v>
+        <x:v>{"kind":"friendly_entity","range_cells":9,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
       </x:c>
       <x:c r="H6" s="16"/>
       <x:c r="I6" s="16" t="n">
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J6" s="17" t="str">
-        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0}</x:v>
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K6" s="17" t="str">
         <x:v>{"mp_base_cost":3,"mp_level_cost":2,"items":[]}</x:v>
@@ -33538,7 +34106,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W6" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":14,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":2,"add_caster_level":true,"undead_multiplier_ppm":1000000}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":14,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":2,"add_caster_level":true,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="70" hidden="0" customHeight="1">
@@ -33561,14 +34129,14 @@
         <x:v>fencing</x:v>
       </x:c>
       <x:c r="G7" s="17" t="str">
-        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0}</x:v>
+        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"passive"}</x:v>
       </x:c>
       <x:c r="H7" s="16"/>
       <x:c r="I7" s="16" t="n">
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J7" s="17" t="str">
-        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0}</x:v>
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K7" s="17" t="str">
         <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
@@ -33607,7 +34175,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W7" s="17" t="str">
-        <x:v>{"accuracy_per_level":3,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,3,6,9],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+        <x:v>{"accuracy_per_level":3,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,3,6,9],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="70" hidden="0" customHeight="1">
@@ -33630,14 +34198,14 @@
         <x:v>spirit_sword</x:v>
       </x:c>
       <x:c r="G8" s="17" t="str">
-        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0}</x:v>
+        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"passive"}</x:v>
       </x:c>
       <x:c r="H8" s="16"/>
       <x:c r="I8" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="17" t="str">
-        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0}</x:v>
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K8" s="17" t="str">
         <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
@@ -33676,7 +34244,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W8" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,3,5,8],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,3,5,8],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="70" hidden="0" customHeight="1">
@@ -33699,14 +34267,14 @@
         <x:v>great_fireball</x:v>
       </x:c>
       <x:c r="G9" s="17" t="str">
-        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":20,"auto_min_targets":1}</x:v>
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":20,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
       </x:c>
       <x:c r="H9" s="16"/>
       <x:c r="I9" s="16" t="n">
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J9" s="17" t="str">
-        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50}</x:v>
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K9" s="17" t="str">
         <x:v>{"mp_base_cost":5,"mp_level_cost":1,"items":[]}</x:v>
@@ -33745,7 +34313,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W9" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":10,"power_bonus":0,"mpower_base":6,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":10,"power_bonus":0,"mpower_base":6,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
@@ -33768,14 +34336,14 @@
         <x:v>thunderbolt</x:v>
       </x:c>
       <x:c r="G10" s="17" t="str">
-        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1}</x:v>
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
       </x:c>
       <x:c r="H10" s="16"/>
       <x:c r="I10" s="16" t="n">
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J10" s="17" t="str">
-        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0}</x:v>
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K10" s="17" t="str">
         <x:v>{"mp_base_cost":9,"mp_level_cost":2,"items":[]}</x:v>
@@ -33814,7 +34382,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W10" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":9,"power_bonus":0,"mpower_base":8,"mpower_bonus":20,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1500000}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":9,"power_bonus":0,"mpower_base":8,"mpower_bonus":20,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1500000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="70" customHeight="1">
@@ -33837,14 +34405,14 @@
         <x:v>firebang</x:v>
       </x:c>
       <x:c r="G11" s="17" t="str">
-        <x:v>{"kind":"enemy_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2}</x:v>
+        <x:v>{"kind":"enemy_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
       </x:c>
       <x:c r="H11" s="16"/>
       <x:c r="I11" s="16" t="n">
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J11" s="17" t="str">
-        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0}</x:v>
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K11" s="17" t="str">
         <x:v>{"mp_base_cost":14,"mp_level_cost":4,"items":[]}</x:v>
@@ -33883,7 +34451,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W11" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":8,"power_bonus":0,"mpower_base":8,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":8,"power_bonus":0,"mpower_base":8,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="70" customHeight="1">
@@ -33906,14 +34474,14 @@
         <x:v>mass_healing</x:v>
       </x:c>
       <x:c r="G12" s="17" t="str">
-        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2}</x:v>
+        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
       </x:c>
       <x:c r="H12" s="16"/>
       <x:c r="I12" s="16" t="n">
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J12" s="17" t="str">
-        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0}</x:v>
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K12" s="17" t="str">
         <x:v>{"mp_base_cost":28,"mp_level_cost":3,"items":[]}</x:v>
@@ -33952,7 +34520,559 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="W12" s="17" t="str">
-        <x:v>{"accuracy_per_level":0,"power_base":4,"power_bonus":0,"mpower_base":10,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":1,"add_caster_level":false,"undead_multiplier_ppm":1000000}</x:v>
+        <x:v>{"accuracy_per_level":0,"power_base":4,"power_bonus":0,"mpower_base":10,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":1,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="70" customHeight="1">
+      <x:c r="A13" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:v>source_slaying</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>攻杀剑术</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="str">
+        <x:v>slaying</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="str">
+        <x:v>{"kind":"passive","activation_kind":"passive_proc","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+      </x:c>
+      <x:c r="H13" s="16"/>
+      <x:c r="I13" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="str">
+        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L13" s="17" t="str">
+        <x:v>slaying</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N13" s="17" t="str">
+        <x:v>player_male.attack</x:v>
+      </x:c>
+      <x:c r="O13" s="17" t="str">
+        <x:v>development_source_slaying_v1</x:v>
+      </x:c>
+      <x:c r="P13" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R13" s="18" t="str">
+        <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S13" s="18" t="str">
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+      </x:c>
+      <x:c r="T13" s="17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V13" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W13" s="17" t="str">
+        <x:v>{"accuracy_per_level":1,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,1,2,3],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[5,6,7,8],"ready_proc_denominator":12,"ready_proc_numerators":[1,2,3,4],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="70" customHeight="1">
+      <x:c r="A14" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B14" s="17" t="str">
+        <x:v>source_thrusting</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="str">
+        <x:v>刺杀剑术</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="str">
+        <x:v>thrusting</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="str">
+        <x:v>{"kind":"attack_mode","activation_kind":"toggle","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[0],"secondary_distance_cells":2,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+      </x:c>
+      <x:c r="H14" s="16"/>
+      <x:c r="I14" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="str">
+        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L14" s="17" t="str">
+        <x:v>thrusting</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N14" s="17" t="str">
+        <x:v>player_male.attack</x:v>
+      </x:c>
+      <x:c r="O14" s="17" t="str">
+        <x:v>development_source_thrusting_v1</x:v>
+      </x:c>
+      <x:c r="P14" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R14" s="18" t="str">
+        <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S14" s="18" t="str">
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+      </x:c>
+      <x:c r="T14" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U14" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V14" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W14" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":250000,"multiplier_bonus_ppm":250000,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="70" customHeight="1">
+      <x:c r="A15" s="19" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B15" s="17" t="str">
+        <x:v>source_half_moon</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="str">
+        <x:v>半月弯刀</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="str">
+        <x:v>half_moon</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="str">
+        <x:v>{"kind":"attack_mode","activation_kind":"toggle","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[-1,1,2],"secondary_distance_cells":1,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+      </x:c>
+      <x:c r="H15" s="16"/>
+      <x:c r="I15" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="str">
+        <x:v>{"mp_base_cost":3,"mp_level_cost":0,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L15" s="17" t="str">
+        <x:v>half_moon</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N15" s="17" t="str">
+        <x:v>player_male.attack</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="str">
+        <x:v>development_source_half_moon_v1</x:v>
+      </x:c>
+      <x:c r="P15" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R15" s="18" t="str">
+        <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S15" s="18" t="str">
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+      </x:c>
+      <x:c r="T15" s="17" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V15" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W15" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":300000,"multiplier_bonus_ppm":100000,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="70" customHeight="1">
+      <x:c r="A16" s="19" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B16" s="17" t="str">
+        <x:v>source_flaming_sword</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="str">
+        <x:v>烈火剑法</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="str">
+        <x:v>flaming_sword</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="str">
+        <x:v>{"kind":"attack_charge","activation_kind":"charge","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+      </x:c>
+      <x:c r="H16" s="16"/>
+      <x:c r="I16" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":10000,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="str">
+        <x:v>{"mp_base_cost":7,"mp_level_cost":0,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L16" s="17" t="str">
+        <x:v>flaming_sword</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N16" s="17" t="str">
+        <x:v>player_male.attack</x:v>
+      </x:c>
+      <x:c r="O16" s="17" t="str">
+        <x:v>development_source_flaming_sword_v1</x:v>
+      </x:c>
+      <x:c r="P16" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R16" s="18" t="str">
+        <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S16" s="18" t="str">
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+      </x:c>
+      <x:c r="T16" s="17" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="U16" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V16" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W16" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1400000,"multiplier_bonus_ppm":400000,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="70" customHeight="1">
+      <x:c r="A17" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B17" s="17" t="str">
+        <x:v>source_lightning</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="str">
+        <x:v>疾光电影</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="str">
+        <x:v>{"kind":"enemy_direction","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":6,"line_stop_on_blocked":false}</x:v>
+      </x:c>
+      <x:c r="H17" s="16"/>
+      <x:c r="I17" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="str">
+        <x:v>{"mp_base_cost":38,"mp_level_cost":7,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L17" s="17" t="str">
+        <x:v>lightning</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N17" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O17" s="17" t="str">
+        <x:v>development_source_lightning_v1</x:v>
+      </x:c>
+      <x:c r="P17" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R17" s="18" t="str">
+        <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S17" s="18" t="str">
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+      </x:c>
+      <x:c r="T17" s="17" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="U17" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V17" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W17" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":12,"power_bonus":0,"mpower_base":12,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="70" customHeight="1">
+      <x:c r="A18" s="19" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B18" s="17" t="str">
+        <x:v>source_ice_storm</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="str">
+        <x:v>冰咆哮</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="str">
+        <x:v>ice_storm</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="str">
+        <x:v>{"kind":"enemy_grid","activation_kind":"cast","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":60,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+      </x:c>
+      <x:c r="H18" s="16"/>
+      <x:c r="I18" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="str">
+        <x:v>{"mp_base_cost":33,"mp_level_cost":3,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L18" s="17" t="str">
+        <x:v>ice_storm</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N18" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O18" s="17" t="str">
+        <x:v>development_source_ice_storm_v1</x:v>
+      </x:c>
+      <x:c r="P18" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R18" s="18" t="str">
+        <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S18" s="18" t="str">
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+      </x:c>
+      <x:c r="T18" s="17" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="U18" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V18" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W18" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":14,"power_bonus":0,"mpower_base":12,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="70" customHeight="1">
+      <x:c r="A19" s="19" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B19" s="17" t="str">
+        <x:v>source_thunder_storm</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="str">
+        <x:v>地狱雷光</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="str">
+        <x:v>thunder_storm</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="str">
+        <x:v>{"kind":"enemy_self","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":2,"require_line_of_sight":false,"auto_priority":50,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+      </x:c>
+      <x:c r="H19" s="16"/>
+      <x:c r="I19" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="str">
+        <x:v>{"mp_base_cost":29,"mp_level_cost":9,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L19" s="17" t="str">
+        <x:v>thunder_storm</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N19" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O19" s="17" t="str">
+        <x:v>development_source_thunder_storm_v1</x:v>
+      </x:c>
+      <x:c r="P19" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q19" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R19" s="18" t="str">
+        <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="S19" s="18" t="str">
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+      </x:c>
+      <x:c r="T19" s="17" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="U19" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V19" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W19" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":10,"power_bonus":20,"mpower_base":10,"mpower_bonus":20,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":10}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="70" customHeight="1">
+      <x:c r="A20" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B20" s="17" t="str">
+        <x:v>source_hell_fire</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="str">
+        <x:v>地狱火</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="str">
+        <x:v>hell_fire</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="str">
+        <x:v>{"kind":"enemy_direction","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":35,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":4,"line_stop_on_blocked":true}</x:v>
+      </x:c>
+      <x:c r="H20" s="16"/>
+      <x:c r="I20" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":100}</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="str">
+        <x:v>{"mp_base_cost":10,"mp_level_cost":3,"items":[]}</x:v>
+      </x:c>
+      <x:c r="L20" s="17" t="str">
+        <x:v>hell_fire</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="N20" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O20" s="17" t="str">
+        <x:v>development_source_hell_fire_fixed_four_v1</x:v>
+      </x:c>
+      <x:c r="P20" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q20" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R20" s="18" t="str">
+        <x:v>用户2026-10-27审定地狱火所有阶固定正前4格；docs/战士攻击模式与方向技能实施边界.md；Crystal HumanObject.cs:4103–4118/Map.cs:875–910默认候选</x:v>
+      </x:c>
+      <x:c r="S20" s="18" t="str">
+        <x:v>形状按用户已定：rank0–3均正前4格，明确不采用源rank3左右射线；MP/威力/门槛/书价仍源码开发候选。首格500，后格实际处理时钟+100，阻挡break，同对象可跨格再次受击；不是整cast去重。</x:v>
+      </x:c>
+      <x:c r="T20" s="17" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U20" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V20" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W20" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":6,"power_bonus":0,"mpower_base":14,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -35094,6 +36214,918 @@
         <x:v>900001</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="70" customHeight="1">
+      <x:c r="A28" s="19" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B28" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C28" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="str">
+        <x:v>[{"item_id":2,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E28" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I28" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K28" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L28" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="70" customHeight="1">
+      <x:c r="A29" s="19" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B29" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C29" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="str">
+        <x:v>[{"item_id":2,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E29" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G29" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I29" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K29" s="16" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L29" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="70" customHeight="1">
+      <x:c r="A30" s="19" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B30" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C30" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="str">
+        <x:v>[{"item_id":2,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E30" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I30" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J30" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K30" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L30" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="70" customHeight="1">
+      <x:c r="A31" s="19" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B31" s="16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C31" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="str">
+        <x:v>[{"item_id":3,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E31" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G31" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I31" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J31" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K31" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L31" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="70" customHeight="1">
+      <x:c r="A32" s="19" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B32" s="16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C32" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="str">
+        <x:v>[{"item_id":3,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E32" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H32" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I32" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J32" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K32" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L32" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="70" customHeight="1">
+      <x:c r="A33" s="19" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B33" s="16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C33" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="str">
+        <x:v>[{"item_id":3,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E33" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G33" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I33" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J33" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K33" s="16" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L33" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="70" customHeight="1">
+      <x:c r="A34" s="19" t="n">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B34" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C34" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="str">
+        <x:v>[{"item_id":4,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E34" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F34" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I34" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J34" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K34" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L34" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="70" customHeight="1">
+      <x:c r="A35" s="19" t="n">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B35" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C35" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="str">
+        <x:v>[{"item_id":4,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E35" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G35" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H35" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I35" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J35" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K35" s="16" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L35" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="70" customHeight="1">
+      <x:c r="A36" s="19" t="n">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B36" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C36" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="str">
+        <x:v>[{"item_id":4,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E36" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G36" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H36" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I36" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J36" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K36" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L36" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="70" customHeight="1">
+      <x:c r="A37" s="19" t="n">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B37" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C37" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="str">
+        <x:v>[{"item_id":6,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E37" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G37" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H37" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I37" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J37" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K37" s="16" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="L37" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="70" customHeight="1">
+      <x:c r="A38" s="19" t="n">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B38" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C38" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="str">
+        <x:v>[{"item_id":6,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E38" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G38" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H38" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I38" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J38" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K38" s="16" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L38" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="70" customHeight="1">
+      <x:c r="A39" s="19" t="n">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B39" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C39" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="str">
+        <x:v>[{"item_id":6,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E39" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G39" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H39" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I39" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J39" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K39" s="16" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L39" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="70" customHeight="1">
+      <x:c r="A40" s="19" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B40" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C40" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="str">
+        <x:v>[{"item_id":16,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E40" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G40" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H40" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I40" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J40" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K40" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L40" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="70" customHeight="1">
+      <x:c r="A41" s="19" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B41" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C41" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="str">
+        <x:v>[{"item_id":16,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E41" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F41" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G41" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H41" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I41" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J41" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K41" s="16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L41" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="70" customHeight="1">
+      <x:c r="A42" s="19" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B42" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C42" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="str">
+        <x:v>[{"item_id":16,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E42" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F42" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H42" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I42" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J42" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K42" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L42" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="70" customHeight="1">
+      <x:c r="A43" s="19" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B43" s="16" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C43" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D43" s="17" t="str">
+        <x:v>[{"item_id":20,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E43" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G43" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H43" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I43" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J43" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K43" s="16" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="L43" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="70" customHeight="1">
+      <x:c r="A44" s="19" t="n">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B44" s="16" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C44" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D44" s="17" t="str">
+        <x:v>[{"item_id":20,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E44" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F44" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I44" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J44" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K44" s="16" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L44" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="70" customHeight="1">
+      <x:c r="A45" s="19" t="n">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B45" s="16" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C45" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D45" s="17" t="str">
+        <x:v>[{"item_id":20,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E45" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F45" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G45" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H45" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I45" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J45" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K45" s="16" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L45" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="70" customHeight="1">
+      <x:c r="A46" s="19" t="n">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B46" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C46" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D46" s="17" t="str">
+        <x:v>[{"item_id":17,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E46" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F46" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G46" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H46" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I46" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J46" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K46" s="16" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L46" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="70" customHeight="1">
+      <x:c r="A47" s="19" t="n">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B47" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C47" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D47" s="17" t="str">
+        <x:v>[{"item_id":17,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E47" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F47" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G47" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H47" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I47" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J47" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K47" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L47" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="70" customHeight="1">
+      <x:c r="A48" s="19" t="n">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B48" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C48" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D48" s="17" t="str">
+        <x:v>[{"item_id":17,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E48" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F48" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G48" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H48" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I48" s="18" t="str">
+        <x:v>用户2026-10-27书本=目标阶+1；docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
+      </x:c>
+      <x:c r="J48" s="18" t="str">
+        <x:v>书本公式已定，页5/10/20与门槛候选；0至3阶只改数值或概率，保持本项格集、模式、目标过滤与耗费路径。</x:v>
+      </x:c>
+      <x:c r="K48" s="16" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="L48" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="70" customHeight="1">
+      <x:c r="A49" s="19" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B49" s="16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C49" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D49" s="17" t="str">
+        <x:v>[{"item_id":10,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E49" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F49" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G49" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H49" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I49" s="18" t="str">
+        <x:v>用户2026-10-27审定地狱火所有阶固定正前4格；docs/战士攻击模式与方向技能实施边界.md；Crystal HumanObject.cs:4103–4118/Map.cs:875–910默认候选</x:v>
+      </x:c>
+      <x:c r="J49" s="18" t="str">
+        <x:v>书本按用户目标阶+1，页5/10/20与等级门槛候选；所有阶固定正前4格，不增加两侧射线。</x:v>
+      </x:c>
+      <x:c r="K49" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L49" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="70" customHeight="1">
+      <x:c r="A50" s="19" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B50" s="16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C50" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D50" s="17" t="str">
+        <x:v>[{"item_id":10,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E50" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F50" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G50" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H50" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I50" s="18" t="str">
+        <x:v>用户2026-10-27审定地狱火所有阶固定正前4格；docs/战士攻击模式与方向技能实施边界.md；Crystal HumanObject.cs:4103–4118/Map.cs:875–910默认候选</x:v>
+      </x:c>
+      <x:c r="J50" s="18" t="str">
+        <x:v>书本按用户目标阶+1，页5/10/20与等级门槛候选；所有阶固定正前4格，不增加两侧射线。</x:v>
+      </x:c>
+      <x:c r="K50" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L50" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="70" customHeight="1">
+      <x:c r="A51" s="19" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B51" s="16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C51" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D51" s="17" t="str">
+        <x:v>[{"item_id":10,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E51" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F51" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G51" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H51" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I51" s="18" t="str">
+        <x:v>用户2026-10-27审定地狱火所有阶固定正前4格；docs/战士攻击模式与方向技能实施边界.md；Crystal HumanObject.cs:4103–4118/Map.cs:875–910默认候选</x:v>
+      </x:c>
+      <x:c r="J51" s="18" t="str">
+        <x:v>书本按用户目标阶+1，页5/10/20与等级门槛候选；所有阶固定正前4格，不增加两侧射线。</x:v>
+      </x:c>
+      <x:c r="K51" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L51" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="508" priority="1">
@@ -38655,6 +40687,270 @@
         <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
       </x:c>
       <x:c r="K16" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="70" customHeight="1">
+      <x:c r="A17" s="19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D17" s="17"/>
+      <x:c r="E17" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I17" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="70" customHeight="1">
+      <x:c r="A18" s="19" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D18" s="17"/>
+      <x:c r="E18" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I18" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="70" customHeight="1">
+      <x:c r="A19" s="19" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D19" s="17"/>
+      <x:c r="E19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I19" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="70" customHeight="1">
+      <x:c r="A20" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D20" s="17"/>
+      <x:c r="E20" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I20" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="70" customHeight="1">
+      <x:c r="A21" s="19" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D21" s="17"/>
+      <x:c r="E21" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I21" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="70" customHeight="1">
+      <x:c r="A22" s="19" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B22" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D22" s="17"/>
+      <x:c r="E22" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="70" customHeight="1">
+      <x:c r="A23" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B23" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D23" s="17"/>
+      <x:c r="E23" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I23" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="str">
+        <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="70" customHeight="1">
+      <x:c r="A24" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B24" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D24" s="17"/>
+      <x:c r="E24" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F24" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="17" t="str">
+        <x:v>kill_event_privilege</x:v>
+      </x:c>
+      <x:c r="I24" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="str">
+        <x:v>最终策划4.8/5.11书页特殊条目；本轮development普通道具子集适配</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="str">
         <x:v>开发分类内等权加入精良职业书，不新增独立概率池，不称目标稻草人原掉落或正式精英/BOSS来源已验收。</x:v>
       </x:c>
     </x:row>
@@ -47138,16 +49434,16 @@
         <x:v>first_loop_closed_development</x:v>
       </x:c>
       <x:c r="C4" s="17" t="str">
-        <x:v>{"rule_version":5,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16}}</x:v>
+        <x:v>{"rule_version":6,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16}}</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选</x:v>
+        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>仅development候选；8技能与3×3范围、普通前格延迟命中及逐杀结算；书本按用户，升级页/学习门槛/书价/开发渠道仍候选。数字只维护本工作簿。</x:v>
+        <x:v>仅development候选；16技能，地狱火所有阶正前4格为用户已审定适配。书本目标阶+1已定，页/门槛/书价候选；唯一数字只维护本工作簿。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -2,101 +2,101 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R186cb98bd3b4433b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R6573dcb22e9e4cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Rd6f4b5968be0427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rcfd9030a1fc44bae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="Rdf472bb12e014c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="Rdfd67b3435b44052"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="Rdef71febdb514adb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R7b1e61720eac4774"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="Rf93c56b033484362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="Rdc5e7e3c9c234f44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="Rb939b305108a458a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="Rd3615c8fdf324670"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R7ecfaa35df9541b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Rf08170645889449e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="Rc5ea61b268744ce5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="R4d48bd63fd484675"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R368684891a494f3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R9a331ca9a5584c2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R567ac1eef9ad47b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R7f86926977914439"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R49fc23d3253d46dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="Rbd3969ad5b2d4c89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R91f3e79ba97e4e43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="Rc8702498d6e64c4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="Ree05f1ecd40a48aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="R201d2cce960a4883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="R167211da7937443d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="Rf5b793414cc44abd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R44584fc725a04f7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="Rbcc53996e9c24560"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="R4e16b35925694b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="R27ff2a66e7394596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="Rcc402075cd9c4760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="Rfa0618b49a9049cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Ra8ba7ce576bc4017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="R958c1dfa3bf44db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="Rad27edfaedf94610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R20a4f322734c4623"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R151f23ad23dc420c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R2e9c664139024b30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="Rd1105c6160204b6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="Rd626544786d44eaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R8a231a9720a4410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="R9a1880d027c24a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="R8753e99cbb964775"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="R1f58923db7484851"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R21c5080b5aa74328"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R81f49477247e44e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R0aac7ef342a1407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="R5de56f0f10c04d33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="Rc2eb12b0956242e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="R448adfcc19fd4151"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Ref5c8eea6f6843f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R722a10b9c7e74ce3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R46978fb319fc4e43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R2aa334e5cb4443a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="Rb562192a257247e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R95048fdaa6834df8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R9d76e9118ca24421"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R0b56b7e864be492d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R0fdcff641a48432d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="Rd6875aba1f9d4329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R4624075301504a3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R0d8352e6a1924915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="Rd61669de43ad4489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R63b25fc073ad4a8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="Rb7c8298337694e13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="Rb269dd0ab7ec4078"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="R02a4c7a369844ec4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R6a5da563018b4705"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Rb9627010d8804a2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="Rbc59b0cbf1084dd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R714e543cb4fe40b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="R22906828ec2c4440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R3ee53b44ca334a8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="R35e9d953975f4919"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rca977d57eb1845c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="Ra2631928573d4e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R77b0b43e57104888"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="R5907ea7e96b94cdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R0076c6b2353843c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R20d67cc89da640da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rdae166cbf87647d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R72201c05e3184954"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="Rff81f98b17a944f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R8571b7dccab74a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="R9c8ff212a8224a5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="Rbb2652e859744e2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Rf8857e11e00143f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R5217b743f0b340b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="Rceb5a3bc399c47af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R65296e028c4f4677"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R14a2be3337fd4efb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="R11b07b34d725417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Ra38458ebf25d4289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R98eb88ca07bc4c39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R8ea3f20f1a6a4490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Rc65997c3c5344bd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rf7cd87836f104bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R0b3d646ac4844bfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="R5b8a8f542af5405d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R2fe73c7c055248cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R893c0bb063e443c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R04ec61e4ec7b41f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R30f2db0d7a37406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="R14e7135d286f4548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R282c8d1f6541461d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R62dad1e8d5054c9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Re0428c908b6f4d12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="R8fa555bd68174f9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="R94a6d065748f424c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="Ra921d1df21c24f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R27ffc182e6a2453e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R7bc8aa3f6595477c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R030377714cf04b17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R156846028aea4950"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="Rcdf5a4b63f684888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R00235279ddb549c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R5fac3de6b30e4bb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="R4664bec3dca04839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="Rf4c7a715e79f4018"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="R9ee0dc551bb34b8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="R3a33802bb6614018"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R1bf3b2b9161c45d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R0a9e10bd05d54506"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="Rfab2a865f5f84e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Rd45f04caf8c44620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R4e06239ae4494466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R3e83485d685d4961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Rae0557da8fad46bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="Rbdc27a604ec0466b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="Rb104e444c9624909"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R8c1a2258fe944a53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="Rad8cf9e68589429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R6fa1427de57e436e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="R5e0b824ba7194e43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R7a2d0e65312c45db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="Rce6ec7762a0f4850"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="Re6e71f67f76a4d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="Rfcb00f881b594d14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="Rc8e4cffa63ad408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="Rdc2e092a83644736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R94f9b02252de4400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="Rf56417584598403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="Rfd4e3c2c9a0b4d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R4d68a593c7bf43db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="R99a1d9d435214063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Rd9116da6928a4cb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R9e29e78ba68b4b16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R798fd1c35f754a1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R6dee40cd94a54ba1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="Rbd15d5a692854b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R39204e6d7c274e81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R7e969ba5afad4308"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R4cbd9b78df68478f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R15c8abe5b354410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R4d7b50dbf0a1493d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R8b2982c518a84ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R99ca0dbb55d748ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R8d72146e4ac24e3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R50dbf6cc8e1a4470"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R014d219b674e4c3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="Rcfbf65ecf9ba46c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="R1a799940fdb94de5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R473bfa3167914ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Rc984f0814e90481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R2941626a13fb4858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R53db6cb678dd477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="R8098a5c8920e4194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R261ad13c148a4121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="Rf3d3ec9d8bab4e30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rb99b4c2d9e044741"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="Rc622f61b75984e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R3dae6a68a85f4870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="R5de0e77178ad4024"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R380e08e17e3d4ede"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R2ccfbbe9eda24484"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rda4ff83d7ee044f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R5b9b1265d98b4460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="R70b08685e9dc40a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R0954eb49cf4b4a63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="R92e96f5086c943f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="R65998e32eee84870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Ra02a08d9feb44cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R13393f2b11fe46e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R03c335ff22644c95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="Rd190d4cbf3ae4b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R9f08c986d2a14b76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="R2cc431190676434d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Recf6ba57364d4a84"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -31849,6 +31849,8 @@
     <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="48" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="70" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="60" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="60" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -31894,6 +31896,12 @@
       <x:c r="N1" s="7" t="str">
         <x:v>说明</x:v>
       </x:c>
+      <x:c r="O1" s="7" t="str">
+        <x:v>地图投影与土层</x:v>
+      </x:c>
+      <x:c r="P1" s="7" t="str">
+        <x:v>场边小型装饰</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -31938,6 +31946,12 @@
       <x:c r="N2" s="12" t="str">
         <x:v>note</x:v>
       </x:c>
+      <x:c r="O2" s="12" t="str">
+        <x:v>visual_geometry</x:v>
+      </x:c>
+      <x:c r="P2" s="12" t="str">
+        <x:v>decorations</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="15" t="str">
@@ -31982,8 +31996,14 @@
       <x:c r="N3" s="15" t="str">
         <x:v>string / 可空 / none</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="O3" s="15" t="str">
+        <x:v>json / 必填 / client</x:v>
+      </x:c>
+      <x:c r="P3" s="15" t="str">
+        <x:v>json / 必填 / client</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="196" hidden="0" customHeight="1">
       <x:c r="A4" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -31991,16 +32011,16 @@
         <x:v>dev_map0_crop128_128</x:v>
       </x:c>
       <x:c r="C4" s="17" t="str">
-        <x:v>开发地图0局部</x:v>
+        <x:v>林间战场</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>ordinary</x:v>
       </x:c>
       <x:c r="E4" s="16" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="16" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G4" s="16" t="n">
         <x:v>1</x:v>
@@ -32015,16 +32035,22 @@
         <x:v>development/maps/first-map</x:v>
       </x:c>
       <x:c r="K4" s="17" t="str">
-        <x:v>8bc3c4db1edfddb3</x:v>
+        <x:v>development-isometric17-open-v2</x:v>
       </x:c>
       <x:c r="L4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="M4" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格</x:v>
+        <x:v>用户2026-10-27新要求：中央无大型遮挡物，四周少量小型代表性设施与装饰；原0.map只提供地板来源，原树阻挡不继续沿用；docs/17x17菱形地图实施边界.md</x:v>
       </x:c>
       <x:c r="N4" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>17×17及菱形/土层保持；用户最新要求无大型遮挡，场边4件原尺寸独立小物。decorations只通过collision_cell_index引用唯一碰撞位置，不维护第二份摆放坐标。木制设施外观似井台，不认证原游戏正式名称；火盆本轮静态原帧。</x:v>
+      </x:c>
+      <x:c r="O4" s="17" t="str">
+        <x:v>{"projection":"isometric_diamond","tile_width":64,"tile_height":32,"soil_thickness_px":48,"source_origin":{"x":128,"y":128}}</x:v>
+      </x:c>
+      <x:c r="P4" s="17" t="str">
+        <x:v>[{"id":"edge_wood_fixture","frame":"Objects:9760","collision_cell_index":0},{"id":"edge_brazier","frame":"Objects:1127","collision_cell_index":1},{"id":"edge_sign","frame":"Objects:8898","collision_cell_index":2},{"id":"edge_grass_rock","frame":"Objects:7092","collision_cell_index":3}]</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -32309,7 +32335,7 @@
         <x:v>string / 可空 / none</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="4" ht="112" hidden="0" customHeight="1">
       <x:c r="A4" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -32317,19 +32343,19 @@
         <x:v>dev_map0_crop128_128</x:v>
       </x:c>
       <x:c r="C4" s="16" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="16" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="17" t="str">
-        <x:v>[{"x":0,"y":0},{"x":7,"y":3},{"x":8,"y":3},{"x":7,"y":4},{"x":8,"y":4},{"x":12,"y":4},{"x":13,"y":4},{"x":12,"y":5},{"x":13,"y":5},{"x":0,"y":7},{"x":1,"y":7},{"x":2,"y":7},{"x":0,"y":8},{"x":1,"y":8},{"x":2,"y":8},{"x":7,"y":14},{"x":7,"y":15}]</x:v>
+        <x:v>[{"x":1,"y":7},{"x":7,"y":1},{"x":15,"y":9},{"x":7,"y":15}]</x:v>
       </x:c>
       <x:c r="F4" s="17" t="str">
         <x:v>blocked_xy_objects</x:v>
       </x:c>
       <x:c r="G4" s="17" t="str">
-        <x:v>{"cell_width":48,"cell_height":32,"source_origin":{"x":128,"y":128}}</x:v>
+        <x:v>{"geometry_reference":"game_maps/1.visual_geometry","collision_basis":"authored_edge_decorations"}</x:v>
       </x:c>
       <x:c r="H4" s="17" t="str">
         <x:v>development_no_corner_cutting</x:v>
@@ -32341,10 +32367,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="K4" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格</x:v>
+        <x:v>用户2026-10-27新要求：中央无大型遮挡物，四周少量小型代表性设施与装饰；原0.map只提供地板来源，原树阻挡不继续沿用；docs/17x17菱形地图实施边界.md</x:v>
       </x:c>
       <x:c r="L4" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>用户审定开阔战场：4格仅对应四周小物；原图289格及原17阻挡作为source_blocked证据保存，runtime blocked明确来自此表，不再宣称直接采用原碰撞位。中央无大树及空气阻挡，285可走格静态连通；原出生不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -32870,10 +32896,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="J4" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格；最终策划案.md:普通怪10秒复活</x:v>
+        <x:v>用户2026-10-27：17×17菱形2.5D地图与土层厚度；原Map/0.map(128,128)完整289格；docs/17x17菱形地图实施边界.md；最终策划普通怪10秒复活</x:v>
       </x:c>
       <x:c r="K4" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 原8槽不变，按17×17源格重新核验静态可达。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -32905,10 +32931,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="J5" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格；最终策划案.md:普通怪10秒复活</x:v>
+        <x:v>用户2026-10-27：17×17菱形2.5D地图与土层厚度；原Map/0.map(128,128)完整289格；docs/17x17菱形地图实施边界.md；最终策划普通怪10秒复活</x:v>
       </x:c>
       <x:c r="K5" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 原8槽不变，按17×17源格重新核验静态可达。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -32940,10 +32966,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="J6" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格；最终策划案.md:普通怪10秒复活</x:v>
+        <x:v>用户2026-10-27：17×17菱形2.5D地图与土层厚度；原Map/0.map(128,128)完整289格；docs/17x17菱形地图实施边界.md；最终策划普通怪10秒复活</x:v>
       </x:c>
       <x:c r="K6" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 原8槽不变，按17×17源格重新核验静态可达。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -32975,10 +33001,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="J7" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格；最终策划案.md:普通怪10秒复活</x:v>
+        <x:v>用户2026-10-27：17×17菱形2.5D地图与土层厚度；原Map/0.map(128,128)完整289格；docs/17x17菱形地图实施边界.md；最终策划普通怪10秒复活</x:v>
       </x:c>
       <x:c r="K7" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 原8槽不变，按17×17源格重新核验静态可达。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -33010,10 +33036,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="J8" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格；最终策划案.md:普通怪10秒复活</x:v>
+        <x:v>用户2026-10-27：17×17菱形2.5D地图与土层厚度；原Map/0.map(128,128)完整289格；docs/17x17菱形地图实施边界.md；最终策划普通怪10秒复活</x:v>
       </x:c>
       <x:c r="K8" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 原8槽不变，按17×17源格重新核验静态可达。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -33045,10 +33071,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="J9" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格；最终策划案.md:普通怪10秒复活</x:v>
+        <x:v>用户2026-10-27：17×17菱形2.5D地图与土层厚度；原Map/0.map(128,128)完整289格；docs/17x17菱形地图实施边界.md；最终策划普通怪10秒复活</x:v>
       </x:c>
       <x:c r="K9" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 原8槽不变，按17×17源格重新核验静态可达。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -33080,10 +33106,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="J10" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格；最终策划案.md:普通怪10秒复活</x:v>
+        <x:v>用户2026-10-27：17×17菱形2.5D地图与土层厚度；原Map/0.map(128,128)完整289格；docs/17x17菱形地图实施边界.md；最终策划普通怪10秒复活</x:v>
       </x:c>
       <x:c r="K10" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 原8槽不变，按17×17源格重新核验静态可达。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -33115,10 +33141,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="J11" s="18" t="str">
-        <x:v>client/assets/resources/development/maps/first-map.json；传奇1.80客户端/Map/0.map裁剪原格；最终策划案.md:普通怪10秒复活</x:v>
+        <x:v>用户2026-10-27：17×17菱形2.5D地图与土层厚度；原Map/0.map(128,128)完整289格；docs/17x17菱形地图实施边界.md；最终策划普通怪10秒复活</x:v>
       </x:c>
       <x:c r="K11" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 原8槽不变，按17×17源格重新核验静态可达。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -49434,16 +49460,16 @@
         <x:v>first_loop_closed_development</x:v>
       </x:c>
       <x:c r="C4" s="17" t="str">
-        <x:v>{"rule_version":6,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16}}</x:v>
+        <x:v>{"rule_version":8,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16},"pet_spawn":{"x":8,"y":7}}</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格</x:v>
+        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>仅development候选；16技能，地狱火所有阶正前4格为用户已审定适配。书本目标阶+1已定，页/门槛/书价候选；唯一数字只维护本工作簿。</x:v>
+        <x:v>仅development：17×17菱形与土层保持，中央开阔，四周4件小物；源17旧阻挡仅保留证据，runtime碰撞来自4件小物位置。名字字号24、预制体0.7并与血条置头顶；技能和经济不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -2,101 +2,101 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R98eb88ca07bc4c39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="R8ea3f20f1a6a4490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Rc65997c3c5344bd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rf7cd87836f104bed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R0b3d646ac4844bfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="R5b8a8f542af5405d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R2fe73c7c055248cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R893c0bb063e443c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R04ec61e4ec7b41f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R30f2db0d7a37406d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="R14e7135d286f4548"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R282c8d1f6541461d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R62dad1e8d5054c9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Re0428c908b6f4d12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="R8fa555bd68174f9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="R94a6d065748f424c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="Ra921d1df21c24f02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R27ffc182e6a2453e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R7bc8aa3f6595477c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R030377714cf04b17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R156846028aea4950"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="Rcdf5a4b63f684888"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="R00235279ddb549c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R5fac3de6b30e4bb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="R4664bec3dca04839"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="Rf4c7a715e79f4018"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="R9ee0dc551bb34b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="R3a33802bb6614018"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R1bf3b2b9161c45d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="R0a9e10bd05d54506"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="Rfab2a865f5f84e1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Rd45f04caf8c44620"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R4e06239ae4494466"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R3e83485d685d4961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Rae0557da8fad46bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="Rbdc27a604ec0466b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="Rb104e444c9624909"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R8c1a2258fe944a53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="Rad8cf9e68589429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R6fa1427de57e436e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="R5e0b824ba7194e43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R7a2d0e65312c45db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="Rce6ec7762a0f4850"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="Re6e71f67f76a4d26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="Rfcb00f881b594d14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="Rc8e4cffa63ad408a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="Rdc2e092a83644736"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R94f9b02252de4400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="Rf56417584598403b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="Rfd4e3c2c9a0b4d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R4d68a593c7bf43db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="R99a1d9d435214063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Rd9116da6928a4cb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R9e29e78ba68b4b16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R798fd1c35f754a1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="R6dee40cd94a54ba1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="Rbd15d5a692854b30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R39204e6d7c274e81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R7e969ba5afad4308"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R4cbd9b78df68478f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R15c8abe5b354410f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R4d7b50dbf0a1493d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="R8b2982c518a84ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R99ca0dbb55d748ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R8d72146e4ac24e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R50dbf6cc8e1a4470"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R014d219b674e4c3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="Rcfbf65ecf9ba46c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="R1a799940fdb94de5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R473bfa3167914ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="Rc984f0814e90481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R2941626a13fb4858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R53db6cb678dd477a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="R8098a5c8920e4194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R261ad13c148a4121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="Rf3d3ec9d8bab4e30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rb99b4c2d9e044741"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="Rc622f61b75984e9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R3dae6a68a85f4870"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="R5de0e77178ad4024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R380e08e17e3d4ede"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R2ccfbbe9eda24484"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rda4ff83d7ee044f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R5b9b1265d98b4460"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="R70b08685e9dc40a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R0954eb49cf4b4a63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="R92e96f5086c943f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="R65998e32eee84870"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Ra02a08d9feb44cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R13393f2b11fe46e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R03c335ff22644c95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="Rd190d4cbf3ae4b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R9f08c986d2a14b76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="R2cc431190676434d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Recf6ba57364d4a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="Rfae4e249352f4cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="Rcc5df82ad60c43c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="R59fca1435b1b4e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rdb7e770156e7498c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R2fc0b60728a74b11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="R188dfc56422648f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R67e79e2ebf2941da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R9bc3deb3c3a341c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R0c905510f3ed4448"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R0da6e4dd2d404b07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="R29db931592764b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R54db387c9be843d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="Rc8695133cac24263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="R40de03d9c9624b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="R9765442c4ffc4133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="Rd852d0c96efa44e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R1e102f413c014895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R602db9850c7948b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R6a25049affd74aa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="Rd0e2890d73544836"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R411b7d96b3ac4230"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="R46e8fdeea5554b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="Re38f4a7752d54e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R256fc3a4c4794759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="R3cbece57dae04879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="Rd1c201b0dec848d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="Ra8221b93acc547f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="R620a926e7ef94369"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R0d79b08ef66c40a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="Racc0e21b57df4a57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="R29c99dbe88f84d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Rbfac4d2659ca41a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="Raf7f0077c1ee4618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R715ca3992a89442d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="R35e7cce79fb740f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="Rdcfe1df99a40495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R463a60971cfa4a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R1b603bff64a64fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R6f95a140dc2949a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R39ae269e9b5f47a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="R407bb957fa204af9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R98c6d0cae3694fcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R96569fbbeb0c4080"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="Rdbd56ddcb0474022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="R1066b57484eb435d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="Rcbe90fcf1a804916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R97c5028ff1ce4e90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R61b3560c932b4604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R7bd4772904db4d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="R01a37bfe1b3c4353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="Re1883a16176042b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="Rebc6cefc46bf4c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="R6a719da870694378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R723f01f3a2bb4d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R20cecf05b5ed47d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="Rffcdc109387a4783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="R203ddc466e3149e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R9e5180feb64743d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R87ddfb22b35844ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R70d57354b42d4e64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R89dab226fe0c4388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R5d0b9b948ed3494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="Rf5c0e111a0a446d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R5649df2bbb864e73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R36ed4a73cff044d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R8e573421fc4b46ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R74e32213ecc74c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="Rb0c38915d6344016"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="Rdc8641e8f8f4475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R5f8932bc0dfd4b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="R4333f1b931ad4c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R1219a1382331400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="Reefe0a5046684cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Rc796c1a0d136482e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R0e6a95338b584634"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="Rb0f221f0a1234130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rc199f464f7a244df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="R1a025dfe82764ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="Rd2e7d4b03e2a4c25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="Ra977da5ff8f04f62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R9706aeb3d2cc47ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="Rb75fd5ba12fd4a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rd37b53be25ca47e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="Re7ee8b1728344d21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="R2f9abc3a38d143dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="Re32dcca5c03f4160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="Rba001c2612714551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="R340dc0a308494bf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Ra25956a25f914235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R781cd5cd5c7f46e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R88b5e39abe764763"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R43bdb3e6e98a44af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R151ad3f7726e4d35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="Re1af4f2d45b549f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="R6663cc427b6645bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -179,7 +179,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -246,6 +246,25 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -8092,7 +8111,7 @@
       </x:c>
       <x:c r="C39" s="2" t="n">
         <x:f>COUNTA('商城商品候选'!$A$4:$A$10003)</x:f>
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"confirmed")</x:f>
@@ -8100,7 +8119,7 @@
       </x:c>
       <x:c r="E39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"candidate")</x:f>
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F39" s="2" t="n">
         <x:f>COUNTIFS('商城商品候选'!$I$4:$I$10003,"unverified")</x:f>
@@ -8588,7 +8607,7 @@
       </x:c>
       <x:c r="C55" s="2" t="n">
         <x:f>COUNTA('物品定义'!$A$4:$A$10003)</x:f>
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"confirmed")</x:f>
@@ -8596,11 +8615,11 @@
       </x:c>
       <x:c r="E55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"candidate")</x:f>
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"unverified")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G55" s="2" t="n">
         <x:f>COUNTIFS('物品定义'!$K$4:$K$10003,"historical")</x:f>
@@ -8867,7 +8886,7 @@
       </x:c>
       <x:c r="C64" s="2" t="n">
         <x:f>COUNTA('技能基础定义'!$A$4:$A$10003)</x:f>
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"confirmed")</x:f>
@@ -8875,7 +8894,7 @@
       </x:c>
       <x:c r="E64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"candidate")</x:f>
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F64" s="2" t="n">
         <x:f>COUNTIFS('技能基础定义'!$Q$4:$Q$10003,"unverified")</x:f>
@@ -8898,7 +8917,7 @@
       </x:c>
       <x:c r="C65" s="2" t="n">
         <x:f>COUNTA('技能逐级扩展'!$A$4:$A$10003)</x:f>
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"confirmed")</x:f>
@@ -8906,7 +8925,7 @@
       </x:c>
       <x:c r="E65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"candidate")</x:f>
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F65" s="2" t="n">
         <x:f>COUNTIFS('技能逐级扩展'!$H$4:$H$10003,"unverified")</x:f>
@@ -8960,7 +8979,7 @@
       </x:c>
       <x:c r="C67" s="2" t="n">
         <x:f>COUNTA('Buff定义'!$A$4:$A$10003)</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D67" s="2" t="n">
         <x:f>COUNTIFS('Buff定义'!$J$4:$J$10003,"confirmed")</x:f>
@@ -8968,7 +8987,7 @@
       </x:c>
       <x:c r="E67" s="2" t="n">
         <x:f>COUNTIFS('Buff定义'!$J$4:$J$10003,"candidate")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F67" s="2" t="n">
         <x:f>COUNTIFS('Buff定义'!$J$4:$J$10003,"unverified")</x:f>
@@ -8991,7 +9010,7 @@
       </x:c>
       <x:c r="C68" s="2" t="n">
         <x:f>COUNTA('效果列表'!$A$4:$A$10003)</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D68" s="2" t="n">
         <x:f>COUNTIFS('效果列表'!$I$4:$I$10003,"confirmed")</x:f>
@@ -8999,7 +9018,7 @@
       </x:c>
       <x:c r="E68" s="2" t="n">
         <x:f>COUNTIFS('效果列表'!$I$4:$I$10003,"candidate")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F68" s="2" t="n">
         <x:f>COUNTIFS('效果列表'!$I$4:$I$10003,"unverified")</x:f>
@@ -22841,6 +22860,108 @@
       </x:c>
       <x:c r="L24" s="17" t="n">
         <x:v>1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="56" customHeight="1">
+      <x:c r="A25" s="19" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B25" s="17" t="str">
+        <x:v>development_skill_book_14</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="str">
+        <x:v>《幽灵盾》</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E25" s="16"/>
+      <x:c r="F25" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H25" s="16"/>
+      <x:c r="I25" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:30 Price；本作首测开发候选</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="str">
+        <x:v>MYF原Price仅为开发报价候选；NPC购入来源禁拆书页，不认证来源服实际价格。</x:v>
+      </x:c>
+      <x:c r="L25" s="17" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="56" customHeight="1">
+      <x:c r="A26" s="19" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B26" s="17" t="str">
+        <x:v>development_skill_book_15</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="str">
+        <x:v>《神圣战甲术》</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E26" s="16"/>
+      <x:c r="F26" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H26" s="16"/>
+      <x:c r="I26" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:31 Price；本作首测开发候选</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="str">
+        <x:v>MYF原Price仅为开发报价候选；NPC购入来源禁拆书页，不认证来源服实际价格。</x:v>
+      </x:c>
+      <x:c r="L26" s="17" t="n">
+        <x:v>4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="56" customHeight="1">
+      <x:c r="A27" s="19" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B27" s="17" t="str">
+        <x:v>development_skill_book_31</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="str">
+        <x:v>《魔法盾》</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="str">
+        <x:v>gold</x:v>
+      </x:c>
+      <x:c r="E27" s="16"/>
+      <x:c r="F27" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="16"/>
+      <x:c r="I27" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:20 Price；本作首测开发候选</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="str">
+        <x:v>MYF原Price仅为开发报价候选；NPC购入来源禁拆书页，不认证来源服实际价格。</x:v>
+      </x:c>
+      <x:c r="L27" s="17" t="n">
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -30691,6 +30812,150 @@
       </x:c>
       <x:c r="M24" s="18" t="str">
         <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="56" customHeight="1">
+      <x:c r="A25" s="19" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="17" t="str">
+        <x:v>skill_book_14</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="str">
+        <x:v>《幽灵盾》</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E25" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F25" s="16"/>
+      <x:c r="G25" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J25" s="17"/>
+      <x:c r="K25" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L25" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:30；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="M25" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="56" customHeight="1">
+      <x:c r="A26" s="19" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B26" s="17" t="str">
+        <x:v>skill_book_15</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="str">
+        <x:v>《神圣战甲术》</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E26" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F26" s="16"/>
+      <x:c r="G26" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H26" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J26" s="17"/>
+      <x:c r="K26" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L26" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:31；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="M26" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="56" customHeight="1">
+      <x:c r="A27" s="19" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B27" s="17" t="str">
+        <x:v>skill_book_31</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="str">
+        <x:v>《魔法盾》</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="str">
+        <x:v>skill_book</x:v>
+      </x:c>
+      <x:c r="E27" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F27" s="16"/>
+      <x:c r="G27" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="17" t="str">
+        <x:v>学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:v>
+      </x:c>
+      <x:c r="J27" s="17"/>
+      <x:c r="K27" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="L27" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:20；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="M27" s="18" t="str">
+        <x:v>原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="56" customHeight="1">
+      <x:c r="A28" s="19" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B28" s="17" t="str">
+        <x:v>casting_supply_amulet</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="str">
+        <x:v>护身符</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="str">
+        <x:v>casting_supply</x:v>
+      </x:c>
+      <x:c r="E28" s="16"/>
+      <x:c r="F28" s="16"/>
+      <x:c r="G28" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="16"/>
+      <x:c r="I28" s="17" t="str">
+        <x:v>道士防御法术的已装备消耗材料；独立材料槽；包数量待定时关闭</x:v>
+      </x:c>
+      <x:c r="J28" s="17"/>
+      <x:c r="K28" s="17" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="L28" s="18" t="str">
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:189；Crystal HumanObject.cs:6859-6868,1346-1375</x:v>
+      </x:c>
+      <x:c r="M28" s="18" t="str">
+        <x:v>MYF Shape5/DuraMax1000不证明Crystal Shape0/Count1000。max_stack留空，casting_supply.enabled=false；未创建NPC护符商品，不能以0充当可用堆叠。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -34027,7 +34292,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K5" s="17" t="str">
-        <x:v>{"mp_base_cost":3,"mp_level_cost":2,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":3,"mp_level_cost":2,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L5" s="17" t="str">
         <x:v>fireball</x:v>
@@ -34096,7 +34361,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K6" s="17" t="str">
-        <x:v>{"mp_base_cost":3,"mp_level_cost":2,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":3,"mp_level_cost":2,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L6" s="17" t="str">
         <x:v>healing</x:v>
@@ -34165,7 +34430,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K7" s="17" t="str">
-        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L7" s="17" t="str">
         <x:v>fencing</x:v>
@@ -34234,7 +34499,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K8" s="17" t="str">
-        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L8" s="17" t="str">
         <x:v>spirit_sword</x:v>
@@ -34303,7 +34568,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K9" s="17" t="str">
-        <x:v>{"mp_base_cost":5,"mp_level_cost":1,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":5,"mp_level_cost":1,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L9" s="17" t="str">
         <x:v>great_fireball</x:v>
@@ -34372,7 +34637,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K10" s="17" t="str">
-        <x:v>{"mp_base_cost":9,"mp_level_cost":2,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":9,"mp_level_cost":2,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L10" s="17" t="str">
         <x:v>thunderbolt</x:v>
@@ -34441,7 +34706,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K11" s="17" t="str">
-        <x:v>{"mp_base_cost":14,"mp_level_cost":4,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":14,"mp_level_cost":4,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L11" s="17" t="str">
         <x:v>firebang</x:v>
@@ -34510,7 +34775,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K12" s="17" t="str">
-        <x:v>{"mp_base_cost":28,"mp_level_cost":3,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":28,"mp_level_cost":3,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L12" s="17" t="str">
         <x:v>mass_healing</x:v>
@@ -34579,7 +34844,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K13" s="17" t="str">
-        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L13" s="17" t="str">
         <x:v>slaying</x:v>
@@ -34648,7 +34913,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K14" s="17" t="str">
-        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":0,"mp_level_cost":0,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L14" s="17" t="str">
         <x:v>thrusting</x:v>
@@ -34717,7 +34982,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K15" s="17" t="str">
-        <x:v>{"mp_base_cost":3,"mp_level_cost":0,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":3,"mp_level_cost":0,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L15" s="17" t="str">
         <x:v>half_moon</x:v>
@@ -34786,7 +35051,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":0,"action_ms":0,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":10000,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K16" s="17" t="str">
-        <x:v>{"mp_base_cost":7,"mp_level_cost":0,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":7,"mp_level_cost":0,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L16" s="17" t="str">
         <x:v>flaming_sword</x:v>
@@ -34855,7 +35120,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K17" s="17" t="str">
-        <x:v>{"mp_base_cost":38,"mp_level_cost":7,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":38,"mp_level_cost":7,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L17" s="17" t="str">
         <x:v>lightning</x:v>
@@ -34924,7 +35189,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K18" s="17" t="str">
-        <x:v>{"mp_base_cost":33,"mp_level_cost":3,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":33,"mp_level_cost":3,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L18" s="17" t="str">
         <x:v>ice_storm</x:v>
@@ -34993,7 +35258,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
-        <x:v>{"mp_base_cost":29,"mp_level_cost":9,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":29,"mp_level_cost":9,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L19" s="17" t="str">
         <x:v>thunder_storm</x:v>
@@ -35062,7 +35327,7 @@
         <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":100}</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
-        <x:v>{"mp_base_cost":10,"mp_level_cost":3,"items":[]}</x:v>
+        <x:v>{"mp_base_cost":10,"mp_level_cost":3,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
       </x:c>
       <x:c r="L20" s="17" t="str">
         <x:v>hell_fire</x:v>
@@ -35099,6 +35364,213 @@
       </x:c>
       <x:c r="W20" s="17" t="str">
         <x:v>{"accuracy_per_level":0,"power_base":6,"power_bonus":0,"mpower_base":14,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="56" customHeight="1">
+      <x:c r="A21" s="19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B21" s="17" t="str">
+        <x:v>source_soul_shield</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="str">
+        <x:v>幽灵盾</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="str">
+        <x:v>soul_shield</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="str">
+        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":3,"require_line_of_sight":false,"auto_priority":6,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+      </x:c>
+      <x:c r="H21" s="16"/>
+      <x:c r="I21" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="str">
+        <x:v>{"mp_base_cost":2,"mp_level_cost":2,"items":[],"material_item_id":187,"material_quantity":1}</x:v>
+      </x:c>
+      <x:c r="L21" s="17" t="str">
+        <x:v>soul_shield</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="str">
+        <x:v>[14]</x:v>
+      </x:c>
+      <x:c r="N21" s="17" t="str">
+        <x:v>player_male.casting</x:v>
+      </x:c>
+      <x:c r="O21" s="17" t="str">
+        <x:v>development_source_soul_shield_v1</x:v>
+      </x:c>
+      <x:c r="P21" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q21" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R21" s="18" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="S21" s="18" t="str">
+        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。</x:v>
+      </x:c>
+      <x:c r="T21" s="17" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="U21" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V21" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W21" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="56" customHeight="1">
+      <x:c r="A22" s="19" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B22" s="17" t="str">
+        <x:v>source_blessed_armour</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="str">
+        <x:v>神圣战甲术</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="str">
+        <x:v>blessed_armour</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="str">
+        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":3,"require_line_of_sight":false,"auto_priority":7,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+      </x:c>
+      <x:c r="H22" s="16"/>
+      <x:c r="I22" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J22" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":50,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="str">
+        <x:v>{"mp_base_cost":2,"mp_level_cost":2,"items":[],"material_item_id":187,"material_quantity":1}</x:v>
+      </x:c>
+      <x:c r="L22" s="17" t="str">
+        <x:v>blessed_armour</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="str">
+        <x:v>[15]</x:v>
+      </x:c>
+      <x:c r="N22" s="17" t="str">
+        <x:v>player_male.casting</x:v>
+      </x:c>
+      <x:c r="O22" s="17" t="str">
+        <x:v>development_source_blessed_armour_v1</x:v>
+      </x:c>
+      <x:c r="P22" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q22" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R22" s="18" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="S22" s="18" t="str">
+        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。</x:v>
+      </x:c>
+      <x:c r="T22" s="17" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="U22" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V22" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W22" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="56" customHeight="1">
+      <x:c r="A23" s="19" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B23" s="17" t="str">
+        <x:v>source_magic_shield</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="str">
+        <x:v>魔法盾</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="str">
+        <x:v>magic_shield</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="str">
+        <x:v>{"kind":"friendly_self","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":5,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+      </x:c>
+      <x:c r="H23" s="16"/>
+      <x:c r="I23" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J23" s="17" t="str">
+        <x:v>{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="str">
+        <x:v>{"mp_base_cost":35,"mp_level_cost":5,"items":[],"material_item_id":0,"material_quantity":0}</x:v>
+      </x:c>
+      <x:c r="L23" s="17" t="str">
+        <x:v>magic_shield</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="str">
+        <x:v>[31]</x:v>
+      </x:c>
+      <x:c r="N23" s="17" t="str">
+        <x:v>player_female.casting</x:v>
+      </x:c>
+      <x:c r="O23" s="17" t="str">
+        <x:v>development_source_magic_shield_v1</x:v>
+      </x:c>
+      <x:c r="P23" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q23" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="R23" s="18" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="S23" s="18" t="str">
+        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。</x:v>
+      </x:c>
+      <x:c r="T23" s="17" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="U23" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V23" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W23" s="17" t="str">
+        <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -37152,6 +37624,348 @@
         <x:v>900001</x:v>
       </x:c>
     </x:row>
+    <x:row r="52" ht="56" customHeight="1">
+      <x:c r="A52" s="19" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B52" s="16" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C52" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D52" s="17" t="str">
+        <x:v>[{"item_id":28,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E52" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F52" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G52" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H52" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I52" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J52" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K52" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L52" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="56" customHeight="1">
+      <x:c r="A53" s="19" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B53" s="16" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C53" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D53" s="17" t="str">
+        <x:v>[{"item_id":28,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E53" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F53" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G53" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H53" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I53" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J53" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K53" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L53" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="56" customHeight="1">
+      <x:c r="A54" s="19" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B54" s="16" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C54" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D54" s="17" t="str">
+        <x:v>[{"item_id":28,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E54" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F54" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G54" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H54" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I54" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J54" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K54" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L54" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="56" customHeight="1">
+      <x:c r="A55" s="19" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B55" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C55" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D55" s="17" t="str">
+        <x:v>[{"item_id":29,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E55" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F55" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G55" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H55" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I55" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J55" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K55" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L55" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="56" customHeight="1">
+      <x:c r="A56" s="19" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B56" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C56" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D56" s="17" t="str">
+        <x:v>[{"item_id":29,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E56" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F56" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G56" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H56" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I56" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J56" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K56" s="16" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L56" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="56" customHeight="1">
+      <x:c r="A57" s="19" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B57" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C57" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D57" s="17" t="str">
+        <x:v>[{"item_id":29,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E57" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F57" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G57" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H57" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I57" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J57" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K57" s="16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L57" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="56" customHeight="1">
+      <x:c r="A58" s="19" t="n">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B58" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C58" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D58" s="17" t="str">
+        <x:v>[{"item_id":18,"quantity":2}]</x:v>
+      </x:c>
+      <x:c r="E58" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F58" s="17" t="str">
+        <x:v>{"native_rank":1}</x:v>
+      </x:c>
+      <x:c r="G58" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H58" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I58" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J58" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K58" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L58" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="56" customHeight="1">
+      <x:c r="A59" s="19" t="n">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B59" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D59" s="17" t="str">
+        <x:v>[{"item_id":18,"quantity":3}]</x:v>
+      </x:c>
+      <x:c r="E59" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F59" s="17" t="str">
+        <x:v>{"native_rank":2}</x:v>
+      </x:c>
+      <x:c r="G59" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H59" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I59" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J59" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K59" s="16" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="L59" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="56" customHeight="1">
+      <x:c r="A60" s="19" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B60" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C60" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D60" s="17" t="str">
+        <x:v>[{"item_id":18,"quantity":4}]</x:v>
+      </x:c>
+      <x:c r="E60" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F60" s="17" t="str">
+        <x:v>{"native_rank":3}</x:v>
+      </x:c>
+      <x:c r="G60" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H60" s="17" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="I60" s="18" t="str">
+        <x:v>用户2026-10-27目标阶+1书本；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="J60" s="18" t="str">
+        <x:v>书本公式为用户确定；页数与等级门槛候选，保留源GetPower/耗蓝/准确差异，不改射程/目标/动作。</x:v>
+      </x:c>
+      <x:c r="K60" s="16" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L60" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="508" priority="1">
@@ -37447,6 +38261,9 @@
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="48" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="70" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="58" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -37486,6 +38303,15 @@
       <x:c r="L1" s="7" t="str">
         <x:v>说明</x:v>
       </x:c>
+      <x:c r="M1" s="7" t="str">
+        <x:v>按施法属性计算时长</x:v>
+      </x:c>
+      <x:c r="N1" s="7" t="str">
+        <x:v>状态名称</x:v>
+      </x:c>
+      <x:c r="O1" s="7" t="str">
+        <x:v>徽标短名</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -37524,6 +38350,15 @@
       <x:c r="L2" s="12" t="str">
         <x:v>note</x:v>
       </x:c>
+      <x:c r="M2" s="12" t="str">
+        <x:v>duration_rule</x:v>
+      </x:c>
+      <x:c r="N2" s="12" t="str">
+        <x:v>display_name</x:v>
+      </x:c>
+      <x:c r="O2" s="12" t="str">
+        <x:v>short_name</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="15" t="str">
@@ -37562,48 +38397,156 @@
       <x:c r="L3" s="15" t="str">
         <x:v>string / 可空 / none</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="19"/>
-      <x:c r="B4" s="17"/>
-      <x:c r="C4" s="17"/>
-      <x:c r="D4" s="16"/>
-      <x:c r="E4" s="16"/>
-      <x:c r="F4" s="17"/>
-      <x:c r="G4" s="17"/>
-      <x:c r="H4" s="17"/>
-      <x:c r="I4" s="17"/>
-      <x:c r="J4" s="17"/>
-      <x:c r="K4" s="18"/>
-      <x:c r="L4" s="18"/>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="19"/>
-      <x:c r="B5" s="17"/>
-      <x:c r="C5" s="17"/>
-      <x:c r="D5" s="16"/>
-      <x:c r="E5" s="16"/>
-      <x:c r="F5" s="17"/>
-      <x:c r="G5" s="17"/>
-      <x:c r="H5" s="17"/>
-      <x:c r="I5" s="17"/>
-      <x:c r="J5" s="17"/>
-      <x:c r="K5" s="18"/>
-      <x:c r="L5" s="18"/>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="19"/>
-      <x:c r="B6" s="17"/>
-      <x:c r="C6" s="17"/>
-      <x:c r="D6" s="16"/>
-      <x:c r="E6" s="16"/>
-      <x:c r="F6" s="17"/>
-      <x:c r="G6" s="17"/>
-      <x:c r="H6" s="17"/>
-      <x:c r="I6" s="17"/>
-      <x:c r="J6" s="17"/>
-      <x:c r="K6" s="18"/>
-      <x:c r="L6" s="18"/>
+      <x:c r="M3" s="15" t="str">
+        <x:v>json / 必填 / both</x:v>
+      </x:c>
+      <x:c r="N3" s="15" t="str">
+        <x:v>string / 必填 / both</x:v>
+      </x:c>
+      <x:c r="O3" s="15" t="str">
+        <x:v>string / 必填 / client</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="160" hidden="0" customHeight="1">
+      <x:c r="A4" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="str">
+        <x:v>soul_shield</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>{"kind":"max_magic_defence","value_by_level":[0,0,0,0],"target_level_divisor":7,"target_level_add":4,"hit_duration_loss_ms_per_hp":0}</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="str">
+        <x:v>refresh_duration_keep_values</x:v>
+      </x:c>
+      <x:c r="G4" s="23" t="str">
+        <x:v>["despawn","scene_dispose"]</x:v>
+      </x:c>
+      <x:c r="H4" s="23" t="str">
+        <x:v>{"allow_dead_targets":true,"friendly_only":true}</x:v>
+      </x:c>
+      <x:c r="I4" s="23" t="str">
+        <x:v>source_defence_candidate</x:v>
+      </x:c>
+      <x:c r="J4" s="23" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="K4" s="23" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="L4" s="23" t="str">
+        <x:v>duration_ms=0表示无固定毫秒分量，实际时长按duration_rule计算。时钟按actualNow离散推进；重施/受击均不重置LastTime和NextTime。</x:v>
+      </x:c>
+      <x:c r="M4" s="23" t="str">
+        <x:v>{"kind":"sc_rank_linear","stat_add":0,"stat_multiplier":4,"seconds_by_level":[50,100,150,200]}</x:v>
+      </x:c>
+      <x:c r="N4" s="23" t="str">
+        <x:v>幽灵盾</x:v>
+      </x:c>
+      <x:c r="O4" s="23" t="str">
+        <x:v>幽盾</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="160" hidden="0" customHeight="1">
+      <x:c r="A5" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5" s="23" t="str">
+        <x:v>blessed_armour</x:v>
+      </x:c>
+      <x:c r="C5" s="23" t="str">
+        <x:v>{"kind":"max_physical_defence","value_by_level":[0,0,0,0],"target_level_divisor":7,"target_level_add":4,"hit_duration_loss_ms_per_hp":0}</x:v>
+      </x:c>
+      <x:c r="D5" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="23" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="F5" s="23" t="str">
+        <x:v>refresh_duration_keep_values</x:v>
+      </x:c>
+      <x:c r="G5" s="23" t="str">
+        <x:v>["despawn","scene_dispose"]</x:v>
+      </x:c>
+      <x:c r="H5" s="23" t="str">
+        <x:v>{"allow_dead_targets":true,"friendly_only":true}</x:v>
+      </x:c>
+      <x:c r="I5" s="23" t="str">
+        <x:v>source_defence_candidate</x:v>
+      </x:c>
+      <x:c r="J5" s="23" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="K5" s="23" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="L5" s="23" t="str">
+        <x:v>duration_ms=0表示无固定毫秒分量，实际时长按duration_rule计算。时钟按actualNow离散推进；重施/受击均不重置LastTime和NextTime。</x:v>
+      </x:c>
+      <x:c r="M5" s="23" t="str">
+        <x:v>{"kind":"sc_rank_linear","stat_add":0,"stat_multiplier":4,"seconds_by_level":[50,100,150,200]}</x:v>
+      </x:c>
+      <x:c r="N5" s="23" t="str">
+        <x:v>神圣战甲术</x:v>
+      </x:c>
+      <x:c r="O5" s="23" t="str">
+        <x:v>战甲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="160" hidden="0" customHeight="1">
+      <x:c r="A6" s="23" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B6" s="23" t="str">
+        <x:v>magic_shield</x:v>
+      </x:c>
+      <x:c r="C6" s="23" t="str">
+        <x:v>{"kind":"magic_shield","value_by_level":[20,30,40,50],"target_level_divisor":0,"target_level_add":0,"hit_duration_loss_ms_per_hp":60}</x:v>
+      </x:c>
+      <x:c r="D6" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="23" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="F6" s="23" t="str">
+        <x:v>ignore_present_on_impact</x:v>
+      </x:c>
+      <x:c r="G6" s="23" t="str">
+        <x:v>["player_death","despawn","scene_dispose"]</x:v>
+      </x:c>
+      <x:c r="H6" s="23" t="str">
+        <x:v>{"allow_dead_targets":false,"friendly_only":true}</x:v>
+      </x:c>
+      <x:c r="I6" s="23" t="str">
+        <x:v>source_defence_candidate</x:v>
+      </x:c>
+      <x:c r="J6" s="23" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="K6" s="23" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="L6" s="23" t="str">
+        <x:v>duration_ms=0表示无固定毫秒分量，实际时长按duration_rule计算。时钟按actualNow离散推进；重施/受击均不重置LastTime和NextTime。</x:v>
+      </x:c>
+      <x:c r="M6" s="23" t="str">
+        <x:v>{"kind":"mc_source_power","stat_add":15,"stat_multiplier":0,"seconds_by_level":[0,0,0,0]}</x:v>
+      </x:c>
+      <x:c r="N6" s="23" t="str">
+        <x:v>魔法盾</x:v>
+      </x:c>
+      <x:c r="O6" s="23" t="str">
+        <x:v>魔盾</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="19"/>
@@ -37824,44 +38767,110 @@
         <x:v>string / 可空 / none</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="19"/>
-      <x:c r="B4" s="17"/>
-      <x:c r="C4" s="17"/>
-      <x:c r="D4" s="17"/>
-      <x:c r="E4" s="17"/>
-      <x:c r="F4" s="17"/>
-      <x:c r="G4" s="17"/>
-      <x:c r="H4" s="2"/>
-      <x:c r="I4" s="17"/>
-      <x:c r="J4" s="18"/>
-      <x:c r="K4" s="18"/>
-    </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="19"/>
-      <x:c r="B5" s="17"/>
-      <x:c r="C5" s="17"/>
-      <x:c r="D5" s="17"/>
-      <x:c r="E5" s="17"/>
-      <x:c r="F5" s="17"/>
-      <x:c r="G5" s="17"/>
-      <x:c r="H5" s="2"/>
-      <x:c r="I5" s="17"/>
-      <x:c r="J5" s="18"/>
-      <x:c r="K5" s="18"/>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="19"/>
-      <x:c r="B6" s="17"/>
-      <x:c r="C6" s="17"/>
-      <x:c r="D6" s="17"/>
-      <x:c r="E6" s="17"/>
-      <x:c r="F6" s="17"/>
-      <x:c r="G6" s="17"/>
-      <x:c r="H6" s="2"/>
-      <x:c r="I6" s="17"/>
-      <x:c r="J6" s="18"/>
-      <x:c r="K6" s="18"/>
+    <x:row r="4" ht="160" hidden="0" customHeight="1">
+      <x:c r="A4" s="23" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="str">
+        <x:v>apply_soul_shield</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>defensive_buff</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="str">
+        <x:v>{"buff_id":14}</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="str">
+        <x:v>cast_impact</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="str">
+        <x:v>{"kind":"friendly_grid"}</x:v>
+      </x:c>
+      <x:c r="G4" s="23" t="str">
+        <x:v>{"per_cast":1}</x:v>
+      </x:c>
+      <x:c r="H4" s="24" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="23" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J4" s="23" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="K4" s="23" t="str">
+        <x:v>仅应用引用的有类型防御状态；不递归触发，不把表现完成当权威命中。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="160" hidden="0" customHeight="1">
+      <x:c r="A5" s="23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5" s="23" t="str">
+        <x:v>apply_blessed_armour</x:v>
+      </x:c>
+      <x:c r="C5" s="23" t="str">
+        <x:v>defensive_buff</x:v>
+      </x:c>
+      <x:c r="D5" s="23" t="str">
+        <x:v>{"buff_id":15}</x:v>
+      </x:c>
+      <x:c r="E5" s="23" t="str">
+        <x:v>cast_impact</x:v>
+      </x:c>
+      <x:c r="F5" s="23" t="str">
+        <x:v>{"kind":"friendly_grid"}</x:v>
+      </x:c>
+      <x:c r="G5" s="23" t="str">
+        <x:v>{"per_cast":1}</x:v>
+      </x:c>
+      <x:c r="H5" s="24" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" s="23" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J5" s="23" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="K5" s="23" t="str">
+        <x:v>仅应用引用的有类型防御状态；不递归触发，不把表现完成当权威命中。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="160" hidden="0" customHeight="1">
+      <x:c r="A6" s="23" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B6" s="23" t="str">
+        <x:v>apply_magic_shield</x:v>
+      </x:c>
+      <x:c r="C6" s="23" t="str">
+        <x:v>defensive_buff</x:v>
+      </x:c>
+      <x:c r="D6" s="23" t="str">
+        <x:v>{"buff_id":31}</x:v>
+      </x:c>
+      <x:c r="E6" s="23" t="str">
+        <x:v>cast_impact</x:v>
+      </x:c>
+      <x:c r="F6" s="23" t="str">
+        <x:v>{"kind":"friendly_self"}</x:v>
+      </x:c>
+      <x:c r="G6" s="23" t="str">
+        <x:v>{"per_cast":1}</x:v>
+      </x:c>
+      <x:c r="H6" s="24" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="23" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J6" s="23" t="str">
+        <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+      </x:c>
+      <x:c r="K6" s="23" t="str">
+        <x:v>仅应用引用的有类型防御状态；不递归触发，不把表现完成当权威命中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="19"/>
@@ -49460,16 +50469,16 @@
         <x:v>first_loop_closed_development</x:v>
       </x:c>
       <x:c r="C4" s="17" t="str">
-        <x:v>{"rule_version":8,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16},"pet_spawn":{"x":8,"y":7}}</x:v>
+        <x:v>{"rule_version":9,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]}}</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离</x:v>
+        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>仅development：17×17菱形与土层保持，中央开阔，四周4件小物；源17旧阻挡仅保留证据，runtime碰撞来自4件小物位置。名字字号24、预制体0.7并与血条置头顶；技能和经济不变。</x:v>
+        <x:v>rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -2,101 +2,101 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="Rfae4e249352f4cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="Rcc5df82ad60c43c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="R59fca1435b1b4e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="Rdb7e770156e7498c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R2fc0b60728a74b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="R188dfc56422648f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R67e79e2ebf2941da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="R9bc3deb3c3a341c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R0c905510f3ed4448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R0da6e4dd2d404b07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="R29db931592764b26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R54db387c9be843d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="Rc8695133cac24263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="R40de03d9c9624b1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="R9765442c4ffc4133"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="Rd852d0c96efa44e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="R1e102f413c014895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R602db9850c7948b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R6a25049affd74aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="Rd0e2890d73544836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="R411b7d96b3ac4230"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="R46e8fdeea5554b7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="Re38f4a7752d54e1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="R256fc3a4c4794759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="R3cbece57dae04879"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="Rd1c201b0dec848d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="Ra8221b93acc547f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="R620a926e7ef94369"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R0d79b08ef66c40a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="Racc0e21b57df4a57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="R29c99dbe88f84d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="Rbfac4d2659ca41a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="Raf7f0077c1ee4618"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="R715ca3992a89442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="R35e7cce79fb740f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="Rdcfe1df99a40495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R463a60971cfa4a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R1b603bff64a64fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R6f95a140dc2949a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R39ae269e9b5f47a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="R407bb957fa204af9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R98c6d0cae3694fcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R96569fbbeb0c4080"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="Rdbd56ddcb0474022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="R1066b57484eb435d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="Rcbe90fcf1a804916"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="R97c5028ff1ce4e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="R61b3560c932b4604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R7bd4772904db4d86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="R01a37bfe1b3c4353"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="Re1883a16176042b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="Rebc6cefc46bf4c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="R6a719da870694378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="R723f01f3a2bb4d11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R20cecf05b5ed47d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="Rffcdc109387a4783"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="R203ddc466e3149e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="R9e5180feb64743d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="R87ddfb22b35844ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="R70d57354b42d4e64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R89dab226fe0c4388"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R5d0b9b948ed3494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="Rf5c0e111a0a446d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R5649df2bbb864e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R36ed4a73cff044d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R8e573421fc4b46ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="R74e32213ecc74c38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="Rb0c38915d6344016"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="Rdc8641e8f8f4475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="R5f8932bc0dfd4b49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="R4333f1b931ad4c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="R1219a1382331400a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="Reefe0a5046684cf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="Rc796c1a0d136482e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R0e6a95338b584634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="Rb0f221f0a1234130"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rc199f464f7a244df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="R1a025dfe82764ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="Rd2e7d4b03e2a4c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="Ra977da5ff8f04f62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="R9706aeb3d2cc47ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="Rb75fd5ba12fd4a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="Rd37b53be25ca47e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="Re7ee8b1728344d21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="R2f9abc3a38d143dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="Re32dcca5c03f4160"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="Rba001c2612714551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="R340dc0a308494bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="Ra25956a25f914235"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R781cd5cd5c7f46e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="R88b5e39abe764763"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="R43bdb3e6e98a44af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R151ad3f7726e4d35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="Re1af4f2d45b549f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="R6663cc427b6645bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置目录" sheetId="1" r:id="R29979a24eadd476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四货币" sheetId="2" r:id="Rd15872cfa37546d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业与固定形象" sheetId="3" r:id="Rd8e7ade54edd4841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备部位" sheetId="4" r:id="R65b1787e927e45ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质与词条槽" sheetId="5" r:id="R89b5ae0cb12c4dac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备阶段" sheetId="6" r:id="R2d626453d6b4421d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品范围与基础约束" sheetId="7" r:id="R8b5434a04bac4550"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色与仓库规则" sheetId="8" r:id="Ra31798710f024c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定判定事件" sheetId="9" r:id="R6f8012785c4b4a42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绑定资源授权" sheetId="10" r:id="R1876eab79a524cb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡产品" sheetId="11" r:id="Rd295305fa2f84033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="双卡与托管权益" sheetId="12" r:id="R68d0332e34694561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具竞购规则" sheetId="13" r:id="R14bc423b2709443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金币撮合规则" sheetId="14" r:id="Rf38757f92719422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="普通掉落互斥分类" sheetId="15" r:id="R1795e7453cc040d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="保底与掉落限额规则" sheetId="16" r:id="Rf34caad4842c4b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼16词条池" sheetId="17" r:id="Rfb40a19a6fa9448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼品质消耗" sheetId="18" r:id="R3bfba8ab6b10471a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼五档" sheetId="19" r:id="R204e3b064a3d4fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗炼锁槽费用" sheetId="20" r:id="R7d8c4d13ef9d4b54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部位强化逐级候选" sheetId="21" r:id="Rf48f18d8be244075"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体七系候选" sheetId="22" r:id="R874d960fc63345e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="炼体逐级概率" sheetId="23" r:id="Rb1abe7add6a74402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始幸运生成" sheetId="24" r:id="Rad50d1a01ae5465f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用油逐级规则" sheetId="25" r:id="Red5f9b7c588840f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运一击贡献" sheetId="26" r:id="Rf4f5e47a06a447fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运11贡献位" sheetId="27" r:id="R9aaceb2371304631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸运结算与分解规则" sheetId="28" r:id="R81cb4e0b92ca4350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿种候选" sheetId="29" r:id="R6b689c1ee7194023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿区楼层候选" sheetId="30" r:id="Rb78b7061d87148cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矿石纯度档" sheetId="31" r:id="Rbc97a8ff928b4e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挖矿打造修理规则" sheetId="32" r:id="R040deac1ca3d4645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级档费用候选" sheetId="33" r:id="R4370743c75b54b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能书分解候选" sheetId="34" r:id="Rc2ff6ad51d5f4540"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商城商品候选" sheetId="35" r:id="Re38e6c31797a4009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="挑战与副本规则" sheetId="36" r:id="R1e9a3657d3764ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本等级入口" sheetId="37" r:id="R7138dc2fc1714444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="镜像竞技规则" sheetId="38" r:id="R4736534700924f98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技连胜积分" sheetId="39" r:id="R98dbfe4fe44248c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级转生与任务规则" sheetId="40" r:id="R5c7661a3b9074e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽名录" sheetId="41" r:id="R65079e9903404cc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽三池词条" sheetId="42" r:id="R22bf7dee501441a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽勋章翅膀规则" sheetId="43" r:id="R6eddd4d6a0404829"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翅膀逐阶待定" sheetId="44" r:id="R7be18f66c44b49e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令档位候选" sheetId="45" r:id="R09aa52083b2241d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战令奖励候选" sheetId="46" r:id="R0a42f2ab3e6f480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="首充与广告候选" sheetId="47" r:id="Rc53f531a853641b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全来源预算候选" sheetId="48" r:id="Rc6db772d2bc44c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户端显示与操作" sheetId="49" r:id="R324412749a9a4639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业基础与成长" sheetId="50" r:id="R7a235b2f13104779"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物品定义" sheetId="51" r:id="R1d19599022394158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备定义" sheetId="52" r:id="Rbc09aedc5e884043"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备外观映射" sheetId="53" r:id="Rf361fdf839b74a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物定义" sheetId="54" r:id="Rcb585e94884641ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图定义" sheetId="55" r:id="R9f5fa1315aa24ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图碰撞" sheetId="56" r:id="Rd14a63abb3b64fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地图区域与NPC" sheetId="57" r:id="R5d318beb6be04f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刷怪生成点" sheetId="58" r:id="Rf8b528d8519a4450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC功能" sheetId="59" r:id="Raef31f0d46b248e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能基础定义" sheetId="60" r:id="Rbf35baac298947d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能逐级扩展" sheetId="61" r:id="R4355447172514317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能范围格模板" sheetId="62" r:id="R2dca357a6a2048cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff定义" sheetId="63" r:id="Rcc19327d36744b3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果列表" sheetId="64" r:id="R2b7a6ceb73ad4ddf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="职业宠物模板" sheetId="65" r:id="R030cb3341b344cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宠物成长" sheetId="66" r:id="R915e42bcd0d04201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐级经验" sheetId="67" r:id="Rf0e24eb2ac144d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转生条件" sheetId="68" r:id="R852b8d9d8fa34d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落池定义" sheetId="69" r:id="Rb561ffc817b34ed4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落条目" sheetId="70" r:id="Rc3dc0833856940bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高品质随机掉落额度" sheetId="71" r:id="R4006ed8d46014fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备分解金币与副产物" sheetId="72" r:id="Rb72f75cc9e724dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词条阶段基数与上限" sheetId="73" r:id="R4c0bc58662fc4962"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锄头工具" sheetId="74" r:id="R302a2c9addb34c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图纸打造配方" sheetId="75" r:id="R281678abc54943d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修理配方" sheetId="76" r:id="R2e73b9edd7374f12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS与场次模板" sheetId="77" r:id="Rd07573472d174ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="讨伐链模板" sheetId="78" r:id="R4e51f7489202452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技赛季奖励与兑换" sheetId="79" r:id="R4abe9e25c3594304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线任务" sheetId="80" r:id="Rd9670dfebe1f49b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日任务池" sheetId="81" r:id="Rd1636a55e46b4342"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="永久成就" sheetId="82" r:id="R0313649dff254d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怪物图鉴条目" sheetId="83" r:id="R75c45d8870844f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魂兽逐星价值与消耗" sheetId="84" r:id="R235c4c959f23402b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勋章逐级配置" sheetId="85" r:id="Rb4c5175c340647ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组定义" sheetId="86" r:id="R2787df3765e04b6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="奖励组条目" sheetId="87" r:id="Re9f750d0f23941e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统邮件模板" sheetId="88" r:id="R9faf3c66a48d4431"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性单位与结算管线" sheetId="89" r:id="R7dd2a82d053048e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史七档行为样本" sheetId="90" r:id="R245175e490094214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史样本隔离" sheetId="91" r:id="Rc195fe1fe8344fdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务端权威规则" sheetId="92" r:id="Ra8575e7bfef34fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发布缺口" sheetId="93" r:id="R30a8341e665e42b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="94" r:id="R84f4fd80da80434c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发首循环夹具" sheetId="95" r:id="Rc8ccdce83d7e47ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -31844,7 +31844,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="17" t="str">
-        <x:v>{"mp":0,"physical_attack_min":1,"physical_attack_max":2,"physical_defence_min":0,"physical_defence_max":0,"magic_defence":0,"accuracy":5,"agility":10,"undead":true}</x:v>
+        <x:v>{"mp":0,"physical_attack_min":1,"physical_attack_max":2,"physical_defence_min":0,"physical_defence_max":0,"magic_defence":0,"accuracy":5,"agility":10,"undead":true,"can_push":true}</x:v>
       </x:c>
       <x:c r="H4" s="16" t="n">
         <x:v>2500</x:v>
@@ -31870,10 +31870,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="Q4" s="18" t="str">
-        <x:v>资料参考/myf/Mud2/DB/ApexM2_Monster.csv:13；client/assets/resources/development/manifest.json</x:v>
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_Monster.csv:13；client/assets/resources/development/manifest.json；资料参考/crystal/Server/MirDatabase/MonsterInfo.cs:39；资料参考/crystal/Server/MirObjects/MonsterObject.cs:1035-1093</x:v>
       </x:c>
       <x:c r="R4" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 本轮Undead仅按原CSV字段显式投影，不能凭名称推断。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 本轮Undead仅按原CSV字段显式投影，不能凭名称推断。；CanPush采用Crystal MonsterInfo默认true作为当前形象开发候选，并非MYF实库已认证；宠物从其monster_template_id同一怪物attributes引用，不另维护。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -31896,7 +31896,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G5" s="17" t="str">
-        <x:v>{"mp":0,"physical_attack_min":10,"physical_attack_max":20,"physical_defence_min":10,"physical_defence_max":10,"magic_defence":10,"accuracy":15,"agility":20,"undead":true}</x:v>
+        <x:v>{"mp":0,"physical_attack_min":10,"physical_attack_max":20,"physical_defence_min":10,"physical_defence_max":10,"magic_defence":10,"accuracy":15,"agility":20,"undead":true,"can_push":true}</x:v>
       </x:c>
       <x:c r="H5" s="16" t="n">
         <x:v>1000</x:v>
@@ -31920,10 +31920,10 @@
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="Q5" s="18" t="str">
-        <x:v>资料参考/myf/Mud2/DB/ApexM2_Monster.csv:381；client/assets/resources/development/manifest.json</x:v>
+        <x:v>资料参考/myf/Mud2/DB/ApexM2_Monster.csv:381；client/assets/resources/development/manifest.json；资料参考/crystal/Server/MirDatabase/MonsterInfo.cs:39；资料参考/crystal/Server/MirObjects/MonsterObject.cs:1035-1093</x:v>
       </x:c>
       <x:c r="R5" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 本轮Undead仅按原CSV字段显式投影，不能凭名称推断。</x:v>
+        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 本轮Undead仅按原CSV字段显式投影，不能凭名称推断。；CanPush采用Crystal MonsterInfo默认true作为当前形象开发候选，并非MYF实库已认证；宠物从其monster_template_id同一怪物attributes引用，不另维护。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -34282,7 +34282,7 @@
         <x:v>fireball</x:v>
       </x:c>
       <x:c r="G5" s="17" t="str">
-        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":10,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":10,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H5" s="16"/>
       <x:c r="I5" s="16" t="n">
@@ -34316,7 +34316,7 @@
         <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
       </x:c>
       <x:c r="S5" s="18" t="str">
-        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T5" s="17" t="n">
         <x:v>7</x:v>
@@ -34351,7 +34351,7 @@
         <x:v>healing</x:v>
       </x:c>
       <x:c r="G6" s="17" t="str">
-        <x:v>{"kind":"friendly_entity","range_cells":9,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"friendly_entity","range_cells":9,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H6" s="16"/>
       <x:c r="I6" s="16" t="n">
@@ -34385,7 +34385,7 @@
         <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
       </x:c>
       <x:c r="S6" s="18" t="str">
-        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T6" s="17" t="n">
         <x:v>21</x:v>
@@ -34420,7 +34420,7 @@
         <x:v>fencing</x:v>
       </x:c>
       <x:c r="G7" s="17" t="str">
-        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"passive"}</x:v>
+        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"passive","auto_enabled":false}</x:v>
       </x:c>
       <x:c r="H7" s="16"/>
       <x:c r="I7" s="16" t="n">
@@ -34454,7 +34454,7 @@
         <x:v>docs/技能来源核验与实施清单.md；docs/技能获取与升级实施边界.md；Crystal默认源码候选</x:v>
       </x:c>
       <x:c r="S7" s="18" t="str">
-        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+        <x:v>从原开发夹具原值迁移；未核验目标1.80，未填造范围模板ID。初学0，开放原生阶0至3。 本轮显式登记目标类型/区域半径/飞行遮挡和非线性被动数组；原三技能费用与行为不变。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T7" s="17" t="n">
         <x:v>1</x:v>
@@ -34489,7 +34489,7 @@
         <x:v>spirit_sword</x:v>
       </x:c>
       <x:c r="G8" s="17" t="str">
-        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"passive"}</x:v>
+        <x:v>{"kind":"passive","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"passive","auto_enabled":false}</x:v>
       </x:c>
       <x:c r="H8" s="16"/>
       <x:c r="I8" s="16" t="n">
@@ -34523,7 +34523,7 @@
         <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
       </x:c>
       <x:c r="S8" s="18" t="str">
-        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T8" s="17" t="n">
         <x:v>22</x:v>
@@ -34558,7 +34558,7 @@
         <x:v>great_fireball</x:v>
       </x:c>
       <x:c r="G9" s="17" t="str">
-        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":20,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":true,"auto_priority":20,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H9" s="16"/>
       <x:c r="I9" s="16" t="n">
@@ -34592,7 +34592,7 @@
         <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
       </x:c>
       <x:c r="S9" s="18" t="str">
-        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T9" s="17" t="n">
         <x:v>12</x:v>
@@ -34627,7 +34627,7 @@
         <x:v>thunderbolt</x:v>
       </x:c>
       <x:c r="G10" s="17" t="str">
-        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"enemy_entity","range_cells":9,"target_move_tolerance_cells":2,"area_radius":0,"require_line_of_sight":false,"auto_priority":30,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H10" s="16"/>
       <x:c r="I10" s="16" t="n">
@@ -34661,7 +34661,7 @@
         <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
       </x:c>
       <x:c r="S10" s="18" t="str">
-        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T10" s="17" t="n">
         <x:v>11</x:v>
@@ -34696,7 +34696,7 @@
         <x:v>firebang</x:v>
       </x:c>
       <x:c r="G11" s="17" t="str">
-        <x:v>{"kind":"enemy_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"enemy_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H11" s="16"/>
       <x:c r="I11" s="16" t="n">
@@ -34730,7 +34730,7 @@
         <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
       </x:c>
       <x:c r="S11" s="18" t="str">
-        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T11" s="17" t="n">
         <x:v>14</x:v>
@@ -34765,7 +34765,7 @@
         <x:v>mass_healing</x:v>
       </x:c>
       <x:c r="G12" s="17" t="str">
-        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H12" s="16"/>
       <x:c r="I12" s="16" t="n">
@@ -34799,7 +34799,7 @@
         <x:v>docs/范围技能与战斗时序实施边界.md；资料参考/crystal/Server/MirEnvir/Envir.cs；HumanObject.cs与MirEnvir/Map.cs源码候选</x:v>
       </x:c>
       <x:c r="S12" s="18" t="str">
-        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。</x:v>
+        <x:v>development源码默认候选；学习取Crystal Level1为明确适配，升级门槛沿该技能Level1/2/3。MYF原书价格只作开发定价参考；未认证目标1.80。 auto_priority/min_targets是本作开发自动策略候选，不是原版AI行为认证。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T12" s="17" t="n">
         <x:v>32</x:v>
@@ -34834,7 +34834,7 @@
         <x:v>slaying</x:v>
       </x:c>
       <x:c r="G13" s="17" t="str">
-        <x:v>{"kind":"passive","activation_kind":"passive_proc","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+        <x:v>{"kind":"passive","activation_kind":"passive_proc","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"auto_enabled":false}</x:v>
       </x:c>
       <x:c r="H13" s="16"/>
       <x:c r="I13" s="16" t="n">
@@ -34868,7 +34868,7 @@
         <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
       </x:c>
       <x:c r="S13" s="18" t="str">
-        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T13" s="17" t="n">
         <x:v>2</x:v>
@@ -34903,7 +34903,7 @@
         <x:v>thrusting</x:v>
       </x:c>
       <x:c r="G14" s="17" t="str">
-        <x:v>{"kind":"attack_mode","activation_kind":"toggle","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[0],"secondary_distance_cells":2,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+        <x:v>{"kind":"attack_mode","activation_kind":"toggle","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[0],"secondary_distance_cells":2,"line_cells":0,"line_stop_on_blocked":false,"auto_enabled":false}</x:v>
       </x:c>
       <x:c r="H14" s="16"/>
       <x:c r="I14" s="16" t="n">
@@ -34937,7 +34937,7 @@
         <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
       </x:c>
       <x:c r="S14" s="18" t="str">
-        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T14" s="17" t="n">
         <x:v>3</x:v>
@@ -34972,7 +34972,7 @@
         <x:v>half_moon</x:v>
       </x:c>
       <x:c r="G15" s="17" t="str">
-        <x:v>{"kind":"attack_mode","activation_kind":"toggle","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[-1,1,2],"secondary_distance_cells":1,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+        <x:v>{"kind":"attack_mode","activation_kind":"toggle","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[-1,1,2],"secondary_distance_cells":1,"line_cells":0,"line_stop_on_blocked":false,"auto_enabled":false}</x:v>
       </x:c>
       <x:c r="H15" s="16"/>
       <x:c r="I15" s="16" t="n">
@@ -35006,7 +35006,7 @@
         <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
       </x:c>
       <x:c r="S15" s="18" t="str">
-        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T15" s="17" t="n">
         <x:v>4</x:v>
@@ -35041,7 +35041,7 @@
         <x:v>flaming_sword</x:v>
       </x:c>
       <x:c r="G16" s="17" t="str">
-        <x:v>{"kind":"attack_charge","activation_kind":"charge","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+        <x:v>{"kind":"attack_charge","activation_kind":"charge","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"auto_enabled":false}</x:v>
       </x:c>
       <x:c r="H16" s="16"/>
       <x:c r="I16" s="16" t="n">
@@ -35075,7 +35075,7 @@
         <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
       </x:c>
       <x:c r="S16" s="18" t="str">
-        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T16" s="17" t="n">
         <x:v>6</x:v>
@@ -35110,7 +35110,7 @@
         <x:v>lightning</x:v>
       </x:c>
       <x:c r="G17" s="17" t="str">
-        <x:v>{"kind":"enemy_direction","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":6,"line_stop_on_blocked":false}</x:v>
+        <x:v>{"kind":"enemy_direction","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":40,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":6,"line_stop_on_blocked":false,"auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H17" s="16"/>
       <x:c r="I17" s="16" t="n">
@@ -35144,7 +35144,7 @@
         <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
       </x:c>
       <x:c r="S17" s="18" t="str">
-        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T17" s="17" t="n">
         <x:v>16</x:v>
@@ -35179,7 +35179,7 @@
         <x:v>ice_storm</x:v>
       </x:c>
       <x:c r="G18" s="17" t="str">
-        <x:v>{"kind":"enemy_grid","activation_kind":"cast","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":60,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+        <x:v>{"kind":"enemy_grid","activation_kind":"cast","range_cells":9,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":60,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H18" s="16"/>
       <x:c r="I18" s="16" t="n">
@@ -35213,7 +35213,7 @@
         <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
       </x:c>
       <x:c r="S18" s="18" t="str">
-        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T18" s="17" t="n">
         <x:v>20</x:v>
@@ -35248,7 +35248,7 @@
         <x:v>thunder_storm</x:v>
       </x:c>
       <x:c r="G19" s="17" t="str">
-        <x:v>{"kind":"enemy_self","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":2,"require_line_of_sight":false,"auto_priority":50,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false}</x:v>
+        <x:v>{"kind":"enemy_self","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":2,"require_line_of_sight":false,"auto_priority":50,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H19" s="16"/>
       <x:c r="I19" s="16" t="n">
@@ -35282,7 +35282,7 @@
         <x:v>docs/战士攻击模式与方向技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs；MirEnvir/Map.cs与Envir.cs；Client/MirObjects/PlayerObject.cs源码候选</x:v>
       </x:c>
       <x:c r="S19" s="18" t="str">
-        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。</x:v>
+        <x:v>development源码默认候选；基础行为逐项登记，学习/升级门槛沿Crystal Level1/2/3；书本=目标阶+1已定，页与书价候选；未认证目标1.80。战士不用Magic默认1800时钟，按普通攻击550动作/300前格受理；新自动优先级只是本作候选。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T19" s="17" t="n">
         <x:v>17</x:v>
@@ -35317,7 +35317,7 @@
         <x:v>hell_fire</x:v>
       </x:c>
       <x:c r="G20" s="17" t="str">
-        <x:v>{"kind":"enemy_direction","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":35,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":4,"line_stop_on_blocked":true}</x:v>
+        <x:v>{"kind":"enemy_direction","activation_kind":"cast","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":35,"auto_min_targets":2,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":4,"line_stop_on_blocked":true,"auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H20" s="16"/>
       <x:c r="I20" s="16" t="n">
@@ -35351,7 +35351,7 @@
         <x:v>用户2026-10-27审定地狱火所有阶固定正前4格；docs/战士攻击模式与方向技能实施边界.md；Crystal HumanObject.cs:4103–4118/Map.cs:875–910默认候选</x:v>
       </x:c>
       <x:c r="S20" s="18" t="str">
-        <x:v>形状按用户已定：rank0–3均正前4格，明确不采用源rank3左右射线；MP/威力/门槛/书价仍源码开发候选。首格500，后格实际处理时钟+100，阻挡break，同对象可跨格再次受击；不是整cast去重。</x:v>
+        <x:v>形状按用户已定：rank0–3均正前4格，明确不采用源rank3左右射线；MP/威力/门槛/书价仍源码开发候选。首格500，后格实际处理时钟+100，阻挡break，同对象可跨格再次受击；不是整cast去重。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T20" s="17" t="n">
         <x:v>10</x:v>
@@ -35386,7 +35386,7 @@
         <x:v>soul_shield</x:v>
       </x:c>
       <x:c r="G21" s="17" t="str">
-        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":3,"require_line_of_sight":false,"auto_priority":6,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":3,"require_line_of_sight":false,"auto_priority":6,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H21" s="16"/>
       <x:c r="I21" s="16" t="n">
@@ -35420,7 +35420,7 @@
         <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
       </x:c>
       <x:c r="S21" s="18" t="str">
-        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。</x:v>
+        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T21" s="17" t="n">
         <x:v>28</x:v>
@@ -35455,7 +35455,7 @@
         <x:v>blessed_armour</x:v>
       </x:c>
       <x:c r="G22" s="17" t="str">
-        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":3,"require_line_of_sight":false,"auto_priority":7,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"friendly_grid","range_cells":9,"target_move_tolerance_cells":0,"area_radius":3,"require_line_of_sight":false,"auto_priority":7,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H22" s="16"/>
       <x:c r="I22" s="16" t="n">
@@ -35489,7 +35489,7 @@
         <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
       </x:c>
       <x:c r="S22" s="18" t="str">
-        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。</x:v>
+        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T22" s="17" t="n">
         <x:v>29</x:v>
@@ -35524,7 +35524,7 @@
         <x:v>magic_shield</x:v>
       </x:c>
       <x:c r="G23" s="17" t="str">
-        <x:v>{"kind":"friendly_self","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":5,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast"}</x:v>
+        <x:v>{"kind":"friendly_self","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":5,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":true}</x:v>
       </x:c>
       <x:c r="H23" s="16"/>
       <x:c r="I23" s="16" t="n">
@@ -35558,7 +35558,7 @@
         <x:v>docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
       </x:c>
       <x:c r="S23" s="18" t="str">
-        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。</x:v>
+        <x:v>源码防御分支开发候选；0至3阶，不启用随机练功。目标范围、死亡/重施/离散时钟以实施边界登记；自动优先级为本作候选。护符包单位待用户决定，未确认时永久材料入口关闭。；rule10显式auto_enabled保持已有普通自动选技候选行为；优先级0不表示关闭；被动、开关、充能不进入普通选技，烈火独立自动逻辑不变。</x:v>
       </x:c>
       <x:c r="T23" s="17" t="n">
         <x:v>18</x:v>
@@ -50469,16 +50469,16 @@
         <x:v>first_loop_closed_development</x:v>
       </x:c>
       <x:c r="C4" s="17" t="str">
-        <x:v>{"rule_version":9,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]}}</x:v>
+        <x:v>{"rule_version":10,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]}}</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证</x:v>
+        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。</x:v>
+        <x:v>rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -22964,6 +22964,98 @@
         <x:v>15000</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="56" customHeight="1">
+      <x:c r="A28" s="19">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B28" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_skill_book_8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">《抗拒火环》</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="16"/>
+      <x:c r="F28" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="16"/>
+      <x:c r="I28" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J28" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K28" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MYF原Price仅为开发报价候选；NPC购入来源禁拆书页，不认证来源服实际价格。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L28" s="17">
+        <x:v>800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="56" customHeight="1">
+      <x:c r="A29" s="19">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_skill_book_27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">《野蛮冲撞》</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="16"/>
+      <x:c r="F29" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="16"/>
+      <x:c r="I29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J29" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K29" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MYF原Price仅为开发报价候选；NPC购入来源禁拆书页，不认证来源服实际价格。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L29" s="17">
+        <x:v>12000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="257" priority="1">
@@ -30956,6 +31048,108 @@
       </x:c>
       <x:c r="M28" s="18" t="str">
         <x:v>MYF Shape5/DuraMax1000不证明Crystal Shape0/Count1000。max_stack留空，casting_supply.enabled=false；未创建NPC护符商品，不能以0充当可用堆叠。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="56" customHeight="1">
+      <x:c r="A29" s="19">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book_8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">《抗拒火环》</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F29" s="16"/>
+      <x:c r="G29" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J29" s="17"/>
+      <x:c r="K29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L29" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M29" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="56" customHeight="1">
+      <x:c r="A30" s="19">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book_27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">《野蛮冲撞》</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F30" s="16"/>
+      <x:c r="G30" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">学习与升级对应技能；来源按实例保存，商店/赠书不可拆页</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J30" s="17"/>
+      <x:c r="K30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L30" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M30" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">原始书身份候选；原像素图标尚待映射。NPC品质0、开发掉落品质另配为1，来源不由绑定推断。</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -35573,6 +35767,200 @@
         <x:v>{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="56" customHeight="1">
+      <x:c r="A24" s="19">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_repulsion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">抗拒火环</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="16">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">repulsion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"kind":"enemy_self","range_cells":0,"target_move_tolerance_cells":0,"area_radius":1,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":false,"displacement":{"distance_base_by_level":[1,1,2,3],"distance_random_bound":2,"success_denominator":20,"success_base":6,"success_per_level":3,"step_display_ms":300}}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" s="16"/>
+      <x:c r="I24" s="16">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"mp_base_cost":2,"mp_level_cost":2,"items":[],"material_item_id":0,"material_quantity":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">repulsion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">player_female.casting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_displacement_8_v1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P24" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R24" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="S24" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">逐阶距离已由用户选择；其余数值为源码开发候选。手动施放，自动显式关闭；怪物抗拒不受伤，野蛮只在结束时对首目标一次Defence.None；不启用练功、PK或来源账号数据。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T24" s="17">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="U24" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V24" s="17">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":4,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="56" customHeight="1">
+      <x:c r="A25" s="19">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_shoulder_dash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">野蛮冲撞</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" s="16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="16">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">shoulder_dash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"kind":"enemy_direction","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":false,"displacement":{"distance_base_by_level":[2,3,4,5],"distance_random_bound":2,"success_denominator":0,"success_base":0,"success_per_level":0,"step_display_ms":300}}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" s="16"/>
+      <x:c r="I25" s="16">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="J25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":0,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"mp_base_cost":4,"mp_level_cost":4,"items":[],"material_item_id":0,"material_quantity":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">shoulder_dash</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">player_male.running</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_displacement_27_v1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P25" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R25" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="S25" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">逐阶距离已由用户选择；其余数值为源码开发候选。手动施放，自动显式关闭；怪物抗拒不受伤，野蛮只在结束时对首目标一次Defence.None；不启用练功、PK或来源账号数据。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T25" s="17">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="U25" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V25" s="17">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":4,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="489" priority="1">
@@ -37963,6 +38351,294 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L60" s="16" t="n">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="56" customHeight="1">
+      <x:c r="A61" s="19">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B61" s="16">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C61" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D61" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":8,"quantity":2}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E61" s="16">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F61" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G61" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H61" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I61" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J61" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">书本目标阶+1为用户已定；页数与学习门槛为开发候选。距离随原生阶变化已获用户明确审定，其余行为形状保持。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K61" s="16">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L61" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="56" customHeight="1">
+      <x:c r="A62" s="19">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B62" s="16">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C62" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D62" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":8,"quantity":3}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E62" s="16">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F62" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":2}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G62" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H62" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I62" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J62" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">书本目标阶+1为用户已定；页数与学习门槛为开发候选。距离随原生阶变化已获用户明确审定，其余行为形状保持。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K62" s="16">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L62" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="56" customHeight="1">
+      <x:c r="A63" s="19">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B63" s="16">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C63" s="16">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D63" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":8,"quantity":4}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E63" s="16">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F63" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":3}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G63" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H63" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I63" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J63" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">书本目标阶+1为用户已定；页数与学习门槛为开发候选。距离随原生阶变化已获用户明确审定，其余行为形状保持。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K63" s="16">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L63" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="56" customHeight="1">
+      <x:c r="A64" s="19">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B64" s="16">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C64" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D64" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":5,"quantity":2}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E64" s="16">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F64" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G64" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H64" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I64" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J64" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">书本目标阶+1为用户已定；页数与学习门槛为开发候选。距离随原生阶变化已获用户明确审定，其余行为形状保持。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K64" s="16">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L64" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="56" customHeight="1">
+      <x:c r="A65" s="19">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B65" s="16">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C65" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D65" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":5,"quantity":3}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E65" s="16">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F65" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":2}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G65" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H65" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I65" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J65" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">书本目标阶+1为用户已定；页数与学习门槛为开发候选。距离随原生阶变化已获用户明确审定，其余行为形状保持。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K65" s="16">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L65" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="56" customHeight="1">
+      <x:c r="A66" s="19">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B66" s="16">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C66" s="16">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D66" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":5,"quantity":4}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E66" s="16">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F66" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":3}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G66" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H66" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I66" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J66" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">书本目标阶+1为用户已定；页数与学习门槛为开发候选。距离随原生阶变化已获用户明确审定，其余行为形状保持。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K66" s="16">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="L66" s="16">
         <x:v>900001</x:v>
       </x:c>
     </x:row>
@@ -50468,17 +51144,23 @@
       <x:c r="B4" s="17" t="str">
         <x:v>first_loop_closed_development</x:v>
       </x:c>
-      <x:c r="C4" s="17" t="str">
-        <x:v>{"rule_version":10,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]}}</x:v>
+      <x:c r="C4" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"rule_version":11,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。 用户2026-10-28审定抗拒/野蛮原生逐阶距离，rule11选入8/27但自动显式关闭；21按已选绑定点路线后续实现。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]}}</x:t>
+        </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
-      <x:c r="E4" s="18" t="str">
-        <x:v>用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）</x:v>
-      </x:c>
-      <x:c r="F4" s="18" t="str">
-        <x:v>rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。</x:v>
+      <x:c r="E4" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）；用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。；rule11两项位移技能按用户已审定范围接入；绑定点与21不以同图随机格替代。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -32512,21 +32512,77 @@
         <x:v>[{"id":"edge_wood_fixture","frame":"Objects:9760","collision_cell_index":0},{"id":"edge_brazier","frame":"Objects:1127","collision_cell_index":1},{"id":"edge_sign","frame":"Objects:8898","collision_cell_index":2},{"id":"edge_grass_rock","frame":"Objects:7092","collision_cell_index":3}]</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="19"/>
-      <x:c r="B5" s="17"/>
-      <x:c r="C5" s="17"/>
-      <x:c r="D5" s="17"/>
-      <x:c r="E5" s="16"/>
-      <x:c r="F5" s="16"/>
-      <x:c r="G5" s="16"/>
-      <x:c r="H5" s="16"/>
-      <x:c r="I5" s="17"/>
-      <x:c r="J5" s="17"/>
-      <x:c r="K5" s="17"/>
-      <x:c r="L5" s="17"/>
-      <x:c r="M5" s="18"/>
-      <x:c r="N5" s="18"/>
+    <x:row r="5" ht="196" hidden="0" customHeight="1">
+      <x:c r="A5" s="19">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_map0_town</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">比奇省</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">town</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="16">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="F5" s="16">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="G5" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"x":633,"y":613}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source-maps/map-2/manifest</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf-map0-2780766485d1-v1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；MiniMap.txt:98图号101与mmap原帧100视觉候选对齐，原引擎编号基址未认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">完整700×700来源地图，源坐标不裁剪；银杏/边界/比奇同属地图0。入口633,613仅取来源银杏传送坐标，不认证新生点。非战斗城镇原生48×32，与个人17×17菱形地图分开；门关闭候选，室内/NPC/实际切图业务另验收。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"projection":"source_rectangular","tile_width":48,"tile_height":32,"soil_thickness_px":0,"source_origin":{"x":0,"y":0},"chunk_size_cells":16,"source_map_code":"0","minimap":{"package":"mmap","raw_frame":100}}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="19"/>
@@ -32832,19 +32888,61 @@
         <x:v>用户审定开阔战场：4格仅对应四周小物；原图289格及原17阻挡作为source_blocked证据保存，runtime blocked明确来自此表，不再宣称直接采用原碰撞位。中央无大树及空气阻挡，285可走格静态连通；原出生不变。</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="19"/>
-      <x:c r="B5" s="17"/>
-      <x:c r="C5" s="16"/>
-      <x:c r="D5" s="16"/>
-      <x:c r="E5" s="17"/>
-      <x:c r="F5" s="17"/>
-      <x:c r="G5" s="17"/>
-      <x:c r="H5" s="17"/>
-      <x:c r="I5" s="17"/>
-      <x:c r="J5" s="17"/>
-      <x:c r="K5" s="18"/>
-      <x:c r="L5" s="18"/>
+    <x:row r="5" ht="112" hidden="0" customHeight="1">
+      <x:c r="A5" s="19">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_map0_town</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="16">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="D5" s="16">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="E5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"source_file":"myf:Mir200/Map/0.map","door_policy":"closed"}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_map_v0_closed_doors</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"geometry_reference":"game_maps/2.visual_geometry","collision_basis":"source_map_closed_doors"}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_no_corner_cutting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2780766485d1e047dc2e8f03578ee83c6a14fd91597fe4562329cb8f24e1d4ec</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可走位由本行唯一原图引用逐格生成，不把490000格复制进Excel文本单元格；静态位/门位/运行OR位分别可核验。关闭门候选不代表门开关与室内已实现；寻路禁止切角沿当前开发适配。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="19"/>
@@ -33099,65 +33197,225 @@
         <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="19"/>
-      <x:c r="B5" s="16"/>
-      <x:c r="C5" s="17"/>
-      <x:c r="D5" s="17"/>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A5" s="19">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B5" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_map0_safe_zone_line6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"min_x":642,"min_y":623,"max_x":658,"max_y":639}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E5" s="16"/>
-      <x:c r="F5" s="17"/>
-      <x:c r="G5" s="17"/>
-      <x:c r="H5" s="17"/>
-      <x:c r="I5" s="18"/>
-      <x:c r="J5" s="18"/>
+      <x:c r="F5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"region_kind":"safe_zone","center":{"x":650,"y":631},"radius":8,"geometry":"chebyshev_inclusive","source_order":6,"initial_binding_status":"unverified"}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；StartPoint.txt:6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">来源记录顺序/重复行保留；仅安全区方形几何候选，不认证MYF新生池或重复行权重，不开启绑定/瞬移、PK、NPC或来源收费。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="19"/>
-      <x:c r="B6" s="16"/>
-      <x:c r="C6" s="17"/>
-      <x:c r="D6" s="17"/>
+      <x:c r="A6" s="19">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B6" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_map0_safe_zone_line7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"min_x":642,"min_y":623,"max_x":658,"max_y":639}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E6" s="16"/>
-      <x:c r="F6" s="17"/>
-      <x:c r="G6" s="17"/>
-      <x:c r="H6" s="17"/>
-      <x:c r="I6" s="18"/>
-      <x:c r="J6" s="18"/>
+      <x:c r="F6" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"region_kind":"safe_zone","center":{"x":650,"y":631},"radius":8,"geometry":"chebyshev_inclusive","source_order":7,"initial_binding_status":"unverified"}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H6" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I6" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；StartPoint.txt:7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J6" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">来源记录顺序/重复行保留；仅安全区方形几何候选，不认证MYF新生池或重复行权重，不开启绑定/瞬移、PK、NPC或来源收费。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="19"/>
-      <x:c r="B7" s="16"/>
-      <x:c r="C7" s="17"/>
-      <x:c r="D7" s="17"/>
+      <x:c r="A7" s="19">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B7" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_map0_safe_zone_line8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"min_x":642,"min_y":623,"max_x":658,"max_y":639}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E7" s="16"/>
-      <x:c r="F7" s="17"/>
-      <x:c r="G7" s="17"/>
-      <x:c r="H7" s="17"/>
-      <x:c r="I7" s="18"/>
-      <x:c r="J7" s="18"/>
+      <x:c r="F7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"region_kind":"safe_zone","center":{"x":650,"y":631},"radius":8,"geometry":"chebyshev_inclusive","source_order":8,"initial_binding_status":"unverified"}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；StartPoint.txt:8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">来源记录顺序/重复行保留；仅安全区方形几何候选，不认证MYF新生池或重复行权重，不开启绑定/瞬移、PK、NPC或来源收费。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="19"/>
-      <x:c r="B8" s="16"/>
-      <x:c r="C8" s="17"/>
-      <x:c r="D8" s="17"/>
+      <x:c r="A8" s="19">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B8" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_map0_safe_zone_line13</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"min_x":281,"min_y":610,"max_x":297,"max_y":626}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E8" s="16"/>
-      <x:c r="F8" s="17"/>
-      <x:c r="G8" s="17"/>
-      <x:c r="H8" s="17"/>
-      <x:c r="I8" s="18"/>
-      <x:c r="J8" s="18"/>
+      <x:c r="F8" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"region_kind":"safe_zone","center":{"x":289,"y":618},"radius":8,"geometry":"chebyshev_inclusive","source_order":13,"initial_binding_status":"unverified"}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；StartPoint.txt:13</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J8" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">来源记录顺序/重复行保留；仅安全区方形几何候选，不认证MYF新生池或重复行权重，不开启绑定/瞬移、PK、NPC或来源收费。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="19"/>
-      <x:c r="B9" s="16"/>
-      <x:c r="C9" s="17"/>
-      <x:c r="D9" s="17"/>
+      <x:c r="A9" s="19">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B9" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_map0_safe_zone_line17</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"min_x":321,"min_y":257,"max_x":341,"max_y":277}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E9" s="16"/>
-      <x:c r="F9" s="17"/>
-      <x:c r="G9" s="17"/>
-      <x:c r="H9" s="17"/>
-      <x:c r="I9" s="18"/>
-      <x:c r="J9" s="18"/>
+      <x:c r="F9" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"region_kind":"safe_zone","center":{"x":331,"y":267},"radius":10,"geometry":"chebyshev_inclusive","source_order":17,"initial_binding_status":"unverified"}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；StartPoint.txt:17</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">来源记录顺序/重复行保留；仅安全区方形几何候选，不认证MYF新生池或重复行权重，不开启绑定/瞬移、PK、NPC或来源收费。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
@@ -51146,7 +51404,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":11,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。 用户2026-10-28审定抗拒/野蛮原生逐阶距离，rule11选入8/27但自动显式关闭；21按已选绑定点路线后续实现。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":12,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。 用户2026-10-28审定抗拒/野蛮原生逐阶距离，rule11选入8/27但自动显式关闭；21按已选绑定点路线后续实现。 rule12接入完整来源城镇目录与安全区数据；分块16/并发4/缓存49仅技术候选，绑定及21仍关闭。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[]},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -51154,12 +51412,12 @@
       </x:c>
       <x:c r="E4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）；用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证</x:t>
+          <x:t xml:space="preserve">用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）；用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证；用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。；rule11两项位移技能按用户已审定范围接入；绑定点与21不以同图随机格替代。</x:t>
+          <x:t xml:space="preserve">rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。；rule11两项位移技能按用户已审定范围接入；绑定点与21不以同图随机格替代。；rule12完整比奇省来源地图目录，与当前个人战斗图分离；实际健康切图和绑定另验收。</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -51404,7 +51404,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":12,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。 用户2026-10-28审定抗拒/野蛮原生逐阶距离，rule11选入8/27但自动显式关闭；21按已选绑定点路线后续实现。 rule12接入完整来源城镇目录与安全区数据；分块16/并发4/缓存49仅技术候选，绑定及21仍关闭。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[]},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":13,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。 用户2026-10-28审定抗拒/野蛮原生逐阶距离，rule11选入8/27但自动显式关闭；21按已选绑定点路线后续实现。 rule12接入完整来源城镇目录与安全区数据；分块16/并发4/缓存49仅技术候选，绑定及21仍关闭。 rule13同owner城镇开发往返；旅行120s准备/10s收束/120s基线确认与有界A*各项预算仅技术候选，不改变续租或事务时限、不作容量承诺。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[]},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -51412,12 +51412,12 @@
       </x:c>
       <x:c r="E4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）；用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证；用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证</x:t>
+          <x:t xml:space="preserve">用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）；用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证；用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；用户先接来源城镇及安全区；同owner健康场景移交和增量导航开发合同，初始新生/绑定/21仍关闭</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。；rule11两项位移技能按用户已审定范围接入；绑定点与21不以同图随机格替代。；rule12完整比奇省来源地图目录，与当前个人战斗图分离；实际健康切图和绑定另验收。</x:t>
+          <x:t xml:space="preserve">rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。；rule11两项位移技能按用户已审定范围接入；绑定点与21不以同图随机格替代。；rule12完整比奇省来源地图目录，与当前个人战斗图分离；实际健康切图和绑定另验收。；rule13城镇开发旅行只移交内存现场，普通怪/掉落原期限保留，不回放战斗收益；导航共享池有界。</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -51404,7 +51404,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":13,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。 用户2026-10-28审定抗拒/野蛮原生逐阶距离，rule11选入8/27但自动显式关闭；21按已选绑定点路线后续实现。 rule12接入完整来源城镇目录与安全区数据；分块16/并发4/缓存49仅技术候选，绑定及21仍关闭。 rule13同owner城镇开发往返；旅行120s准备/10s收束/120s基线确认与有界A*各项预算仅技术候选，不改变续租或事务时限、不作容量承诺。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[]},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":14,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。 用户2026-10-28审定抗拒/野蛮原生逐阶距离，rule11选入8/27但自动显式关闭；21按已选绑定点路线后续实现。 rule12接入完整来源城镇目录与安全区数据；分块16/并发4/缓存49仅技术候选，绑定及21仍关闭。 rule13同owner城镇开发往返；旅行120s准备/10s收束/120s基线确认与有界A*各项预算仅技术候选，不改变续租或事务时限、不作容量承诺。 rule14仅成功普通Walk触发来源安全区中心永久绑定；沿原Pending单槽、SourceSeq和3秒事务，初始新生池及瞬移21关闭。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -51412,12 +51412,12 @@
       </x:c>
       <x:c r="E4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）；用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证；用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；用户先接来源城镇及安全区；同owner健康场景移交和增量导航开发合同，初始新生/绑定/21仍关闭</x:t>
+          <x:t xml:space="preserve">用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）；用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证；用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；用户先接来源城镇及安全区；同owner健康场景移交和增量导航开发合同，初始新生/绑定/21仍关闭；docs/安全区永久绑定实施边界.md；Crystal SetBindSafeZone与成功Walk；可信取得回执不持久临时世界</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。；rule11两项位移技能按用户已审定范围接入；绑定点与21不以同图随机格替代。；rule12完整比奇省来源地图目录，与当前个人战斗图分离；实际健康切图和绑定另验收。；rule13城镇开发旅行只移交内存现场，普通怪/掉落原期限保留，不回放战斗收益；导航共享池有界。</x:t>
+          <x:t xml:space="preserve">rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。；rule11两项位移技能按用户已审定范围接入；绑定点与21不以同图随机格替代。；rule12完整比奇省来源地图目录，与当前个人战斗图分离；实际健康切图和绑定另验收。；rule13城镇开发旅行只移交内存现场，普通怪/掉落原期限保留，不回放战斗收益；导航共享池有界。；rule14独立安全区绑定门禁，不打开随机初始化；历史无证据坐标保留但不授予21资格。</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -23056,6 +23056,52 @@
         <x:v>12000</x:v>
       </x:c>
     </x:row>
+    <x:row r="30" ht="56" customHeight="1">
+      <x:c r="A30" s="19">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book_21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">《瞬息移动》</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="16"/>
+      <x:c r="F30" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="16"/>
+      <x:c r="I30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J30" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MYF Mud2/DB/ApexM2_stditems.csv:1,15（Idx13、Stdmode4、原名瞬息移动、Price2000）；仅开发来源候选，非原服实际成交认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K30" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">沿既有金币绑定优先、产物绑定及NPC品质0禁拆页；此候选不认证原服实际成交。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L30" s="17">
+        <x:v>2000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="257" priority="1">
@@ -31152,6 +31198,57 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="31" ht="56" customHeight="1">
+      <x:c r="A31" s="19">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book_21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">《瞬息移动》</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F31" s="16"/>
+      <x:c r="G31" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">学习与升级瞬息移动；实例来源/品质沿既有规则，NPC及初始赠书不得拆页</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J31" s="17"/>
+      <x:c r="K31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L31" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MYF Mud2/DB/ApexM2_stditems.csv:1,15（Idx13、Stdmode4、原名瞬息移动、Price2000）；仅开发来源候选，非原服实际成交认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M31" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">书13原身份候选，Price仅写商城独立价格行；不新增初始赠书，不把技能MP写成永久资产收费。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="382" priority="1">
@@ -33414,6 +33511,94 @@
       <x:c r="J9" s="18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">来源记录顺序/重复行保留；仅安全区方形几何候选，不认证MYF新生池或重复行权重，不开启绑定/瞬移、PK、NPC或来源收费。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="19">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B10" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map_1_policy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"min_x":0,"min_y":0,"max_x":16,"max_y":16}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="16"/>
+      <x:c r="F10" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"region_kind":"map_policy","no_teleport":false}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I10" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本作17×17个人图开发候选，rule15显式NoTeleport=false；非来源城镇、新生或复活规则</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J10" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本map唯一全图政策行；不得作为safe_zone参与绑定首匹配或ZoneSetHash，不配置怪物或NPC。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="19">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B11" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map_2_policy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"min_x":0,"min_y":0,"max_x":699,"max_y":699}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="16"/>
+      <x:c r="F11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"region_kind":"map_policy","no_teleport":false}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule15候选采用Crystal当前源图NoTeleport到期检查；Crystal Server/MirDatabase/MapInfo.cs:24、MirObjects/HumanObject.cs:6096–6100；原MYF Mir200/Envir/MapInfo.txt:5只读白名单为[0\t比奇省] NOMANNOMON，原文件SHA358056b0f13e0c26968b08cbde08d4742137c0453f6d634203b495addf7b6707；跨引擎candidate，不认证标记完全等价</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本map唯一全图政策行；不得作为safe_zone参与绑定首匹配或ZoneSetHash，不配置怪物或NPC。</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -36219,6 +36404,103 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="26" ht="56" customHeight="1">
+      <x:c r="A26" s="19">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_teleport</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">瞬息移动</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="16">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">teleport</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"kind":"friendly_self","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":1,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":false,"teleport":{"max_attempts":200,"axis_rule":"map_dimension_divided_by_rank_plus_one","landing_rule":"source_static_walk","allow_occupied":true,"allow_accepted_dead":true,"check_source_map_at_due":true}}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H26" s="16"/>
+      <x:c r="I26" s="16">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":200,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"mp_base_cost":10,"mp_level_cost":3,"items":[],"material_item_id":0,"material_quantity":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">teleport</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[21]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">player_female.casting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_teleport_21_v1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P26" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R26" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户先城镇/安全区与绑定后推进21路线；rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="S26" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">绑定地图完整尺寸随机，200ms到期200次独立尝试；静态Walk允许动态占格且不额外关门。仅手动；新施法死者拒绝，已受理同Life未Despawn者可尸体成功传送且保持HP0。失败不退MP、不加Flux。目标1.80仍未认证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T26" s="17">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="U26" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V26" s="17">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":1000000,"multiplier_bonus_ppm":0,"accuracy_by_level":[0,0,0,0],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":1000000,"max_attack_bonus_by_level":[0,0,0,0],"ready_proc_denominator":0,"ready_proc_numerators":[0,0,0,0],"non_undead_divisor":1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="489" priority="1">
@@ -38897,6 +39179,150 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L66" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="56" customHeight="1">
+      <x:c r="A67" s="19">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B67" s="16">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C67" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D67" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":13,"quantity":2}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E67" s="16">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F67" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G67" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H67" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I67" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户先城镇/安全区与绑定后推进21路线；rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；用户已定目标阶+1本，页数沿既有逐阶开发候选</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J67" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅native_rank改变MP和原生随机轴除数；书本2/3/4为用户既定公式，页数5/10/20候选保留，不启用随机练功。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K67" s="16">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L67" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="56" customHeight="1">
+      <x:c r="A68" s="19">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B68" s="16">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C68" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D68" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":13,"quantity":3}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E68" s="16">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F68" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":2}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G68" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H68" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I68" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户先城镇/安全区与绑定后推进21路线；rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；用户已定目标阶+1本，页数沿既有逐阶开发候选</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J68" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅native_rank改变MP和原生随机轴除数；书本2/3/4为用户既定公式，页数5/10/20候选保留，不启用随机练功。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K68" s="16">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L68" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="56" customHeight="1">
+      <x:c r="A69" s="19">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B69" s="16">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C69" s="16">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D69" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":13,"quantity":4}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E69" s="16">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F69" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":3}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G69" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H69" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I69" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">用户先城镇/安全区与绑定后推进21路线；rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；用户已定目标阶+1本，页数沿既有逐阶开发候选</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J69" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅native_rank改变MP和原生随机轴除数；书本2/3/4为用户既定公式，页数5/10/20候选保留，不启用随机练功。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K69" s="16">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L69" s="16">
         <x:v>900001</x:v>
       </x:c>
     </x:row>
@@ -39483,18 +39909,75 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="19"/>
-      <x:c r="B7" s="17"/>
-      <x:c r="C7" s="17"/>
-      <x:c r="D7" s="16"/>
-      <x:c r="E7" s="16"/>
-      <x:c r="F7" s="17"/>
-      <x:c r="G7" s="17"/>
-      <x:c r="H7" s="17"/>
-      <x:c r="I7" s="17"/>
-      <x:c r="J7" s="17"/>
-      <x:c r="K7" s="18"/>
-      <x:c r="L7" s="18"/>
+      <x:c r="A7" s="19">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">temporal_flux</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"kind":"teleport_mana_penalty","value_by_level":[30,30,30,30],"target_level_divisor":0,"target_level_add":0,"hit_duration_loss_ms_per_hp":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="16">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="E7" s="16">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">refresh_duration_keep_values</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">["despawn","world_dispose"]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"allow_dead_targets":true,"friendly_only":true}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_teleport_candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Crystal Server/MirObjects/HumanObject.cs:6096–6107,397–450；MirObjects/MapObject.cs:570–595；MirDatabase/BuffInfo.cs:19；PlayerObject.cs:578–667；TemporalFlux仅成功后添加、重置时长、不随死亡或安全区暂停</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L7" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">唯一固定时长在duration_ms，秒数数组保持空；百分比只在attribute_effects逐阶数组。成功传送后添加，允许已受理尸体到期成功；健康跨图/重连不移除、不退款、不复活。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"kind":"fixed_ms","stat_add":0,"stat_multiplier":0,"seconds_by_level":[]}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">时空波动</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">时空</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="19"/>
@@ -39807,17 +40290,57 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="19"/>
-      <x:c r="B7" s="17"/>
-      <x:c r="C7" s="17"/>
-      <x:c r="D7" s="17"/>
-      <x:c r="E7" s="17"/>
-      <x:c r="F7" s="17"/>
-      <x:c r="G7" s="17"/>
-      <x:c r="H7" s="2"/>
-      <x:c r="I7" s="17"/>
-      <x:c r="J7" s="18"/>
-      <x:c r="K7" s="18"/>
+      <x:c r="A7" s="19">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">apply_temporal_flux_after_teleport</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">teleport_success_buff</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"buff_id":21}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">teleport_success</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"kind":"friendly_self"}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"per_cast":1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Crystal Server/MirObjects/HumanObject.cs:6096–6107,397–450；MirObjects/MapObject.cs:570–595；MirDatabase/BuffInfo.cs:19；PlayerObject.cs:578–667；TemporalFlux仅成功后添加、重置时长、不随死亡或安全区暂停</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">独立传送成功后置；NoTeleport/200次尝试失败或取消不触发，不能套cast_impact；每次cast至多一次，不递归，也不复活尸体。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="19"/>
@@ -51404,7 +51927,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":14,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"32格/赠送清单/免费主动复活/等权子集是本次开发测试夹具。回收50/400仅借来源Price作绑定金币事务测试，不是正式分解值。 新角色按职业赠1本绑定开发技能书；首组三本7级学习为本项目候选资格，不是从MYF NeedLevel或Crystal Level1证明的原版读书门槛；初学原生等级0，重复书不升级。 本轮逐阶书本按用户目标rank+1；页5/10/20、首组三本NPC书500金币与普通道具子集新增精良职业书均为显式开发候选。商店与赠书禁拆页；旧未知来源不补推掉落。 本轮事件容量128和逐杀队列16是development技术预算；不证明承载量。人类攻击动作550/命中300/等级攻速公式与视觉动画时钟分离，首组装备尚无攻速词条按0适配。 新五本学习采用各自Crystal Level1适配，价格候选按MYF原字段分别600/2000/1600/3000/15000金币；不声称来源服实际报价。 战士持续模式与烈火充能为临时内存；健康离线沿绝对截止推进，不写永久聚合。 地狱火每个有效传播格发送权威CastStep，首格500ms；后格按实际处理时钟+100ms，不按客户端计时或一帧追赶。 用户2026-10-27审定地图17×17及菱形2.5D；64×32地格/48像素土层是本轮美术候选。宠物出生8,7从既有开发资产显式迁入本Excel，不再回读生成地图作数值源；界内与连通性逐项校验。 用户后续确认移除大遮挡物，场边4件小物；出生保持，碰撞仅取小物对应4格。名字24字号、预制体0.7缩放并与血条位于头顶。 本轮防御状态31/14/15为源码候选；独立材料槽100不占10个强化装备位。护符包数量未审定，入口关闭，不从DuraMax猜数量。 用户2026-10-28审定抗拒/野蛮原生逐阶距离，rule11选入8/27但自动显式关闭；21按已选绑定点路线后续实现。 rule12接入完整来源城镇目录与安全区数据；分块16/并发4/缓存49仅技术候选，绑定及21仍关闭。 rule13同owner城镇开发往返；旅行120s准备/10s收束/120s基线确认与有界A*各项预算仅技术候选，不改变续租或事务时限、不作容量承诺。 rule14仅成功普通Walk触发来源安全区中心永久绑定；沿原Pending单槽、SourceSeq和3秒事务，初始新生池及瞬移21关闭。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":15,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -51412,12 +51935,12 @@
       </x:c>
       <x:c r="E4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">用户2026-10-26授权1-5开发；../SuprcodeCrystal/Shared/BaseStats.cs:14-68,200-239；level=1逐项Calculate；空手0..0；HumanObject.cs:186,1766-1768 attack=1400-14=1386,move=600；docs/药品与技能实施边界.md:P01–P06（原字节摘要及候选适配）；docs/技能来源核验与实施清单.md（默认参数候选及开发适配）；用户2026-10-27目标阶+1书本；docs/技能获取与升级实施边界.md；范围技能与战斗时序实施边界；Crystal普通攻击与范围源码候选；战士攻击模式与方向技能实施边界；Crystal逐项分支与binary32候选；用户2026-10-27审定地狱火所有阶正前4格；用户17×17菱形2.5D地图；完整289原格与土层投影；宠物出生迁入唯一Excel；用户要求移除大型遮挡，仅四周4件小型设施；源碰撞位与本作摆放明确分离；docs/战斗状态与防御技能实施边界.md；资料参考/crystal/Server/MirObjects/HumanObject.cs与MirEnvir/Map.cs；开发候选，非目标1.80认证；资料参考/crystal/Server/MirObjects/HumanObject.cs:2649-2724；MonsterObject.cs:1035-1093；资料参考/crystal/Client/MirObjects/PlayerObject.cs:1037-1041,1493-1497,2384-2401；Frames.cs:158（Pushed六帧按步长2倒放、100ms帧间隔的300ms开发表现）；用户2026-10-28明确审定Crystal来源逐阶推距/冲距；docs/抗拒火环与野蛮冲撞实施边界.md；Crystal HumanObject.cs:3953-4008,4975-5157与Envir默认；非目标1.80认证；用户明确先接来源城镇及安全区；docs/来源城镇地图与安全区实施边界.md；资料索引/来源城镇地图补充.json；MYF MapInfo.txt L5与StartPoint.txt原字节副本；跨来源开发候选，非目标1.80认证；用户先接来源城镇及安全区；同owner健康场景移交和增量导航开发合同，初始新生/绑定/21仍关闭；docs/安全区永久绑定实施边界.md；Crystal SetBindSafeZone与成功Walk；可信取得回执不持久临时世界</x:t>
+          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule9防御状态和材料协议开发候选；护符单位未定，入口关闭；既有17×17小型场边装饰及头顶布局保持。；rule10仅位移共用底座：Human无Info.CanPush门槛；玩家推后动作500ms、怪物每推格动作300ms/移动500ms、推步表现300ms独立候选，不借用攻击命中时长。8/27/21仍未选入；推距、绑定目的地与护符单位未填。；rule11两项位移技能按用户已审定范围接入；绑定点与21不以同图随机格替代。；rule12完整比奇省来源地图目录，与当前个人战斗图分离；实际健康切图和绑定另验收。；rule13城镇开发旅行只移交内存现场，普通怪/掉落原期限保留，不回放战斗收益；导航共享池有界。；rule14独立安全区绑定门禁，不打开随机初始化；历史无证据坐标保留但不授予21资格。</x:t>
+          <x:t xml:space="preserve">rule15选入21及正常购书/原书升级候选，初始仅赠原三职业一本，不随新增技能增加赠书。随机新生池仍关闭；只有已核证明资格可施放21。</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -40566,25 +40566,39 @@
       <x:c r="D4" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E4" s="17" t="str">
-        <x:v>{"hp":60,"mp":0,"physical_attack_min":10,"physical_attack_max":20,"physical_defence_min":10,"physical_defence_max":10,"magic_defence":10,"accuracy":15,"agility":20}</x:v>
+      <x:c r="E4" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"kind":"inherit_monster_template","owner_job_id":2,"neutral_attributes":{"attack_speed":0,"magic_max":0,"magic_min":0,"magic_resist":0,"tao_max":0,"tao_min":0},"magic_resist_weight_source":"profile_player_shared"}</x:t>
+        </x:is>
       </x:c>
       <x:c r="F4" s="17" t="str">
         <x:v>development_melee_adjacent</x:v>
       </x:c>
-      <x:c r="G4" s="17"/>
-      <x:c r="H4" s="17"/>
+      <x:c r="G4" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"source_skill_id":17,"training":{"initial_level_by_rank":[0,1,2,3],"maximum_level_by_rank":[4,5,6,7],"experience_multiplier":3,"owner_range_cells":16,"experience_basis":"owner_actual_granted_experience","grant_phase":"confirmed_owner_experience","eligibility":"alive_same_world_within_owner_range","max_level_ups_per_grant":1,"excess_experience":"keep","at_maximum":"do_not_accumulate","current_hp_on_growth":"keep"},"speed":{"basis":"maximum_training_level","move_reduction_ms_per_level":130,"attack_reduction_ms_per_level":70,"minimum_move_interval_ms":400,"minimum_attack_interval_ms":400}}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H4" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"corpse_ttl_ms":180000,"spawn_ready_ms":2000,"live_expiry":"no_tame_expiry","cold_enter":"do_not_restore_temporary_pet"}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I4" s="17" t="str">
         <x:v>pet_skeleton</x:v>
       </x:c>
       <x:c r="J4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
-      <x:c r="K4" s="18" t="str">
-        <x:v>资料参考/myf/Mud2/DB/ApexM2_Monster.csv:381；client/assets/resources/development/manifest.json</x:v>
-      </x:c>
-      <x:c r="L4" s="18" t="str">
-        <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 只给道士开发夹具注入宠物，召唤资格/技能耗材未实现，不开放正式召唤。</x:v>
+      <x:c r="K4" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37；本任务选择BoneFamiliar/AI23行为的跨MYF候选；Crystal MonsterObject.cs:584–599,689–704,734–736,966–1005,1205–1215；MapObject.cs:358–375；不认证MYF Race100等于AI23；MYF Monster.csv:381基础模板由monster_template_id唯一引用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L4" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">rule16仅开启World身体/尸体生命周期；legacy_untrained_pet保留原免费bootstrap属性且不训练。SourceSkillID17仅来源身份，summon_skill_id仍空，17未选入、护符未开；新生或隔离训练另按typed规则。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -40805,64 +40819,292 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="19"/>
-      <x:c r="B4" s="16"/>
-      <x:c r="C4" s="16"/>
-      <x:c r="D4" s="17"/>
-      <x:c r="E4" s="17"/>
-      <x:c r="F4" s="17"/>
-      <x:c r="G4" s="18"/>
-      <x:c r="H4" s="18"/>
+      <x:c r="A4" s="19">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"hp_bonus":0,"attack_min_bonus":0,"attack_max_bonus":0,"defence_min_bonus":0,"defence_max_bonus":0,"magic_defence_min_bonus":0,"magic_defence_max_bonus":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"required_experience":20000}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H4" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">属性只保存相对monster基础的增量；阈值只在本表维护，倍率及资格只在PetDefs维护；仅终态7阈值明确null，不从模板Level15推断训练等级。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="19"/>
-      <x:c r="B5" s="16"/>
-      <x:c r="C5" s="16"/>
-      <x:c r="D5" s="17"/>
-      <x:c r="E5" s="17"/>
-      <x:c r="F5" s="17"/>
-      <x:c r="G5" s="18"/>
-      <x:c r="H5" s="18"/>
+      <x:c r="A5" s="19">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"hp_bonus":20,"attack_min_bonus":1,"attack_max_bonus":1,"defence_min_bonus":2,"defence_max_bonus":2,"magic_defence_min_bonus":2,"magic_defence_max_bonus":2}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"required_experience":40000}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">属性只保存相对monster基础的增量；阈值只在本表维护，倍率及资格只在PetDefs维护；仅终态7阈值明确null，不从模板Level15推断训练等级。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="19"/>
-      <x:c r="B6" s="16"/>
-      <x:c r="C6" s="16"/>
-      <x:c r="D6" s="17"/>
-      <x:c r="E6" s="17"/>
-      <x:c r="F6" s="17"/>
-      <x:c r="G6" s="18"/>
-      <x:c r="H6" s="18"/>
+      <x:c r="A6" s="19">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"hp_bonus":40,"attack_min_bonus":2,"attack_max_bonus":2,"defence_min_bonus":4,"defence_max_bonus":4,"magic_defence_min_bonus":4,"magic_defence_max_bonus":4}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"required_experience":60000}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H6" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">属性只保存相对monster基础的增量；阈值只在本表维护，倍率及资格只在PetDefs维护；仅终态7阈值明确null，不从模板Level15推断训练等级。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="19"/>
-      <x:c r="B7" s="16"/>
-      <x:c r="C7" s="16"/>
-      <x:c r="D7" s="17"/>
-      <x:c r="E7" s="17"/>
-      <x:c r="F7" s="17"/>
-      <x:c r="G7" s="18"/>
-      <x:c r="H7" s="18"/>
+      <x:c r="A7" s="19">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"hp_bonus":60,"attack_min_bonus":3,"attack_max_bonus":3,"defence_min_bonus":6,"defence_max_bonus":6,"magic_defence_min_bonus":6,"magic_defence_max_bonus":6}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"required_experience":80000}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">属性只保存相对monster基础的增量；阈值只在本表维护，倍率及资格只在PetDefs维护；仅终态7阈值明确null，不从模板Level15推断训练等级。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="19"/>
-      <x:c r="B8" s="16"/>
-      <x:c r="C8" s="16"/>
-      <x:c r="D8" s="17"/>
-      <x:c r="E8" s="17"/>
-      <x:c r="F8" s="17"/>
-      <x:c r="G8" s="18"/>
-      <x:c r="H8" s="18"/>
+      <x:c r="A8" s="19">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="16">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"hp_bonus":80,"attack_min_bonus":4,"attack_max_bonus":4,"defence_min_bonus":8,"defence_max_bonus":8,"magic_defence_min_bonus":8,"magic_defence_max_bonus":8}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"required_experience":100000}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">属性只保存相对monster基础的增量；阈值只在本表维护，倍率及资格只在PetDefs维护；仅终态7阈值明确null，不从模板Level15推断训练等级。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="19"/>
-      <x:c r="B9" s="16"/>
-      <x:c r="C9" s="16"/>
-      <x:c r="D9" s="17"/>
-      <x:c r="E9" s="17"/>
-      <x:c r="F9" s="17"/>
-      <x:c r="G9" s="18"/>
-      <x:c r="H9" s="18"/>
+      <x:c r="A9" s="19">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="16">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"hp_bonus":100,"attack_min_bonus":5,"attack_max_bonus":5,"defence_min_bonus":10,"defence_max_bonus":10,"magic_defence_min_bonus":10,"magic_defence_max_bonus":10}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"required_experience":120000}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">属性只保存相对monster基础的增量；阈值只在本表维护，倍率及资格只在PetDefs维护；仅终态7阈值明确null，不从模板Level15推断训练等级。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="19">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="16">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"hp_bonus":120,"attack_min_bonus":6,"attack_max_bonus":6,"defence_min_bonus":12,"defence_max_bonus":12,"magic_defence_min_bonus":12,"magic_defence_max_bonus":12}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"required_experience":140000}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">属性只保存相对monster基础的增量；阈值只在本表维护，倍率及资格只在PetDefs维护；仅终态7阈值明确null，不从模板Level15推断训练等级。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="19">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="16">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"hp_bonus":140,"attack_min_bonus":7,"attack_max_bonus":7,"defence_min_bonus":14,"defence_max_bonus":14,"magic_defence_min_bonus":14,"magic_defence_max_bonus":14}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"required_experience":null}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">属性只保存相对monster基础的增量；阈值只在本表维护，倍率及资格只在PetDefs维护；仅终态7阈值明确null，不从模板Level15推断训练等级。</x:t>
+        </x:is>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
@@ -51927,7 +52169,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":15,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":16,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -51935,12 +52177,12 @@
       </x:c>
       <x:c r="E4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选</x:t>
+          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选；本任务rule16宠物驻留/身体/训练候选，数值由PetDefs/Growth及架构预算共同维护</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule15选入21及正常购书/原书升级候选，初始仅赠原三职业一本，不随新增技能增加赠书。随机新生池仍关闭；只有已核证明资格可施放21。</x:t>
+          <x:t xml:space="preserve">rule15选入21及正常购书/原书升级候选，初始仅赠原三职业一本，不随新增技能增加赠书。随机新生池仍关闭；只有已核证明资格可施放21。 rule16仅旧免费bootstrap的原对象死亡/尸体生命周期，正常17材料召唤仍待用户护符单位决定；不新增初始书。</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -31249,6 +31249,57 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="32" ht="56" customHeight="1">
+      <x:c r="A32" s="19">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B32" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book_17</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">《召唤骷髅》</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill_book</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F32" s="16"/>
+      <x:c r="G32" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">关闭的召唤候选书；不增加初始赠书或商店，正常学习与升级入口待后续验收</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J32" s="17"/>
+      <x:c r="K32" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L32" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MYF Mud2/DB/ApexM2_stditems.csv:27（Idx25/Stdmode4/原名召唤骷髅）；本任务候选，未新增价格行</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M32" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">书25只由召唤独立catalog投影，不进入主22技能对应书表；未开17/购符/赠书/升级；护符187数量与售价继续未知。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="382" priority="1">
@@ -33539,7 +33590,7 @@
       </x:c>
       <x:c r="G10" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"region_kind":"map_policy","no_teleport":false}</x:t>
+          <x:t xml:space="preserve">{"region_kind":"map_policy","no_teleport":false,"no_pets":false}</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" s="17" t="inlineStr">
@@ -33549,12 +33600,12 @@
       </x:c>
       <x:c r="I10" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本作17×17个人图开发候选，rule15显式NoTeleport=false；非来源城镇、新生或复活规则</x:t>
+          <x:t xml:space="preserve">本作17×17个人图开发候选，rule15显式NoTeleport=false；非来源城镇、新生或复活规则；本任务rule17显式NoPets=false候选，保持当前可携宠地图开发范围；Crystal HumanObject.cs:4401、MonsterObject.cs:1334–1367；不从MYF NOMANNOMON或NoTeleport推定原服NoPets</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本map唯一全图政策行；不得作为safe_zone参与绑定首匹配或ZoneSetHash，不配置怪物或NPC。</x:t>
+          <x:t xml:space="preserve">本map唯一全图政策行；不得作为safe_zone参与绑定首匹配或ZoneSetHash，不配置怪物或NPC。 rule17独立no_pets布尔；不加入安全区或ZoneSetHash，受理与Recall到期时点按各自源规则。</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -33583,7 +33634,7 @@
       </x:c>
       <x:c r="G11" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"region_kind":"map_policy","no_teleport":false}</x:t>
+          <x:t xml:space="preserve">{"region_kind":"map_policy","no_teleport":false,"no_pets":false}</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" s="17" t="inlineStr">
@@ -33593,12 +33644,12 @@
       </x:c>
       <x:c r="I11" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本任务rule15候选采用Crystal当前源图NoTeleport到期检查；Crystal Server/MirDatabase/MapInfo.cs:24、MirObjects/HumanObject.cs:6096–6100；原MYF Mir200/Envir/MapInfo.txt:5只读白名单为[0\t比奇省] NOMANNOMON，原文件SHA358056b0f13e0c26968b08cbde08d4742137c0453f6d634203b495addf7b6707；跨引擎candidate，不认证标记完全等价</x:t>
+          <x:t xml:space="preserve">本任务rule15候选采用Crystal当前源图NoTeleport到期检查；Crystal Server/MirDatabase/MapInfo.cs:24、MirObjects/HumanObject.cs:6096–6100；原MYF Mir200/Envir/MapInfo.txt:5只读白名单为[0\t比奇省] NOMANNOMON，原文件SHA358056b0f13e0c26968b08cbde08d4742137c0453f6d634203b495addf7b6707；跨引擎candidate，不认证标记完全等价；本任务rule17显式NoPets=false候选，保持当前可携宠地图开发范围；Crystal HumanObject.cs:4401、MonsterObject.cs:1334–1367；不从MYF NOMANNOMON或NoTeleport推定原服NoPets</x:t>
         </x:is>
       </x:c>
       <x:c r="J11" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本map唯一全图政策行；不得作为safe_zone参与绑定首匹配或ZoneSetHash，不配置怪物或NPC。</x:t>
+          <x:t xml:space="preserve">本map唯一全图政策行；不得作为safe_zone参与绑定首匹配或ZoneSetHash，不配置怪物或NPC。 rule17独立no_pets布尔；不加入安全区或ZoneSetHash，受理与Recall到期时点按各自源规则。</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -36501,6 +36552,103 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="27" ht="56" customHeight="1">
+      <x:c r="A27" s="19">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_summon_skeleton</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">召唤骷髅</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E27" s="16">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">summon_pet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"kind":"friendly_self","range_cells":0,"target_move_tolerance_cells":0,"area_radius":0,"require_line_of_sight":false,"auto_priority":0,"auto_min_targets":0,"secondary_direction_offsets":[],"secondary_distance_cells":0,"line_cells":0,"line_stop_on_blocked":false,"activation_kind":"cast","auto_enabled":false,"summon":{"definition_id":1}}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H27" s="16"/>
+      <x:c r="I27" s="16">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="J27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"cooldown_reduction_ms":0,"global_spell_ms":1800,"action_ms":600,"delay_base_ms":500,"projectile_ms_per_cell":0,"secondary_impact_ms":0,"charge_window_ms":0,"line_step_ms":0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"mp_base_cost":12,"mp_level_cost":4,"items":[],"material_item_id":187,"material_quantity":1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">summon_pet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">player_male.casting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_source_summon_skeleton_v1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P27" s="9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R27" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule17关闭的开发候选；MYF ApexM2_Magic.csv:18技能17、ApexM2_stditems.csv:27书25；Crystal MirEnvir/Envir.cs:997–1012 MP12+4/range0/learn19；HumanObject.cs:3424–3451,4399–4438；MagicInfo.cs:18默认CD1800；不是MYF16困魔咒，不认证原服部署</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="S27" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅独立候选；同名存活有居民节点先Recall且不耗符，新生才材料1；主22技能不选17。MYF19/23/26与Crystal19/22/26不同，三阶另由171–173候选维护，主升级未选入。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T27" s="17">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="U27" s="17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V27" s="17">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"accuracy_per_level":0,"power_base":0,"power_bonus":0,"mpower_base":0,"mpower_bonus":0,"multiplier_base_ppm":0,"multiplier_bonus_ppm":0,"accuracy_by_level":[],"healing_stat_multiplier":0,"add_caster_level":false,"undead_multiplier_ppm":0,"max_attack_bonus_by_level":[],"ready_proc_denominator":0,"ready_proc_numerators":[],"non_undead_divisor":0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="489" priority="1">
@@ -39323,6 +39471,150 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L69" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="56" customHeight="1">
+      <x:c r="A70" s="19">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B70" s="16">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C70" s="16">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D70" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":25,"quantity":2}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E70" s="16">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F70" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":1}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G70" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H70" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I70" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule17关闭的开发候选；MYF ApexM2_Magic.csv:18技能17、ApexM2_stditems.csv:27书25；Crystal MirEnvir/Envir.cs:997–1012 MP12+4/range0/learn19；HumanObject.cs:3424–3451,4399–4438；MagicInfo.cs:18默认CD1800；不是MYF16困魔咒，不认证原服部署；本任务已选Crystal19/22/26作开发候选，明确区别MYF19/23/26；书目标阶+1为既定公式，页数沿已审5/10/20候选</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J70" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅关闭召唤catalog逐阶合同，保证完整Cfg.Validate；不进主22技能升级，不开商店/赠书/随机练功。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K70" s="16">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L70" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="56" customHeight="1">
+      <x:c r="A71" s="19">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B71" s="16">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C71" s="16">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D71" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":25,"quantity":3}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E71" s="16">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F71" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":2}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G71" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H71" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I71" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule17关闭的开发候选；MYF ApexM2_Magic.csv:18技能17、ApexM2_stditems.csv:27书25；Crystal MirEnvir/Envir.cs:997–1012 MP12+4/range0/learn19；HumanObject.cs:3424–3451,4399–4438；MagicInfo.cs:18默认CD1800；不是MYF16困魔咒，不认证原服部署；本任务已选Crystal19/22/26作开发候选，明确区别MYF19/23/26；书目标阶+1为既定公式，页数沿已审5/10/20候选</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J71" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅关闭召唤catalog逐阶合同，保证完整Cfg.Validate；不进主22技能升级，不开商店/赠书/随机练功。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K71" s="16">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L71" s="16">
+        <x:v>900001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="56" customHeight="1">
+      <x:c r="A72" s="19">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B72" s="16">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C72" s="16">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D72" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[{"item_id":25,"quantity":4}]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E72" s="16">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F72" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"native_rank":3}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G72" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H72" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I72" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule17关闭的开发候选；MYF ApexM2_Magic.csv:18技能17、ApexM2_stditems.csv:27书25；Crystal MirEnvir/Envir.cs:997–1012 MP12+4/range0/learn19；HumanObject.cs:3424–3451,4399–4438；MagicInfo.cs:18默认CD1800；不是MYF16困魔咒，不认证原服部署；本任务已选Crystal19/22/26作开发候选，明确区别MYF19/23/26；书目标阶+1为既定公式，页数沿已审5/10/20候选</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J72" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅关闭召唤catalog逐阶合同，保证完整Cfg.Validate；不进主22技能升级，不开商店/赠书/随机练功。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K72" s="16">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L72" s="16">
         <x:v>900001</x:v>
       </x:c>
     </x:row>
@@ -40562,7 +40854,9 @@
       <x:c r="B4" s="17" t="str">
         <x:v>dev_skeleton</x:v>
       </x:c>
-      <x:c r="C4" s="16"/>
+      <x:c r="C4" s="16">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="D4" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -40576,7 +40870,7 @@
       </x:c>
       <x:c r="G4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"source_skill_id":17,"training":{"initial_level_by_rank":[0,1,2,3],"maximum_level_by_rank":[4,5,6,7],"experience_multiplier":3,"owner_range_cells":16,"experience_basis":"owner_actual_granted_experience","grant_phase":"confirmed_owner_experience","eligibility":"alive_same_world_within_owner_range","max_level_ups_per_grant":1,"excess_experience":"keep","at_maximum":"do_not_accumulate","current_hp_on_growth":"keep"},"speed":{"basis":"maximum_training_level","move_reduction_ms_per_level":130,"attack_reduction_ms_per_level":70,"minimum_move_interval_ms":400,"minimum_attack_interval_ms":400}}</x:t>
+          <x:t xml:space="preserve">{"source_skill_id":17,"training":{"initial_level_by_rank":[0,1,2,3],"maximum_level_by_rank":[4,5,6,7],"experience_multiplier":3,"owner_range_cells":16,"experience_basis":"owner_actual_granted_experience","grant_phase":"confirmed_owner_experience","eligibility":"alive_same_world_within_owner_range","max_level_ups_per_grant":1,"excess_experience":"keep","at_maximum":"do_not_accumulate","current_hp_on_growth":"keep"},"speed":{"basis":"maximum_training_level","move_reduction_ms_per_level":130,"attack_reduction_ms_per_level":70,"minimum_move_interval_ms":400,"minimum_attack_interval_ms":400},"recall_name":"BoneFamiliar"}</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" s="17" t="inlineStr">
@@ -40592,12 +40886,12 @@
       </x:c>
       <x:c r="K4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37；本任务选择BoneFamiliar/AI23行为的跨MYF候选；Crystal MonsterObject.cs:584–599,689–704,734–736,966–1005,1205–1215；MapObject.cs:358–375；不认证MYF Race100等于AI23；MYF Monster.csv:381基础模板由monster_template_id唯一引用</x:t>
+          <x:t xml:space="preserve">本任务rule16开发候选；资料索引/职业宠物补充来源契约.json；Crystal MonsterObject.cs:811–833,3502–3515；PlayerObject.cs:895–899；Shared/Globals.cs:37；本任务选择BoneFamiliar/AI23行为的跨MYF候选；Crystal MonsterObject.cs:584–599,689–704,734–736,966–1005,1205–1215；MapObject.cs:358–375；不认证MYF Race100等于AI23；MYF Monster.csv:381基础模板由monster_template_id唯一引用；资料索引/职业宠物补充来源契约.json及crystal-supplement/source-slices/Settings.pet-defaults.json:技术行162 SkeletonName=BoneFamiliar；与MYF变异骷髅是明确跨来源候选，不是客户端display_name</x:t>
         </x:is>
       </x:c>
       <x:c r="L4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule16仅开启World身体/尸体生命周期；legacy_untrained_pet保留原免费bootstrap属性且不训练。SourceSkillID17仅来源身份，summon_skill_id仍空，17未选入、护符未开；新生或隔离训练另按typed规则。</x:t>
+          <x:t xml:space="preserve">rule17主仍原免费legacy_untrained_pet且不训练；summon_skill_id17仅正式候选引用，不加入运行skill_ids。RecallName大小写敏感同名，不由DefinitionID/显示名推断；现有Training.owner_range_cells唯一16兼作源自动Recall范围，未复制第二个16；出生2000/尸体180000不变。</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -52169,7 +52463,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":16,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":17,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -52177,12 +52471,12 @@
       </x:c>
       <x:c r="E4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选；本任务rule16宠物驻留/身体/训练候选，数值由PetDefs/Growth及架构预算共同维护</x:t>
+          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选；本任务rule16宠物驻留/身体/训练候选，数值由PetDefs/Growth及架构预算共同维护；rule17地图宠物政策与独立召唤候选，同源参数不激活主技能</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule15选入21及正常购书/原书升级候选，初始仅赠原三职业一本，不随新增技能增加赠书。随机新生池仍关闭；只有已核证明资格可施放21。 rule16仅旧免费bootstrap的原对象死亡/尸体生命周期，正常17材料召唤仍待用户护符单位决定；不新增初始书。</x:t>
+          <x:t xml:space="preserve">rule15选入21及正常购书/原书升级候选，初始仅赠原三职业一本，不随新增技能增加赠书。随机新生池仍关闭；只有已核证明资格可施放21。 rule16仅旧免费bootstrap的原对象死亡/尸体生命周期，正常17材料召唤仍待用户护符单位决定；不新增初始书。 rule17主profile不追加技能17/书25/商店/升级/初始赠书；护符187未知值保持。独立catalog含完整三阶候选，不绕过校验。</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -52463,7 +52463,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":17,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":18,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -52463,7 +52463,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":18,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":19,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -42052,6 +42052,1086 @@
         <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A24" s="19">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B24" s="16">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C24" s="16">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:24；[Exp].Level21；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A25" s="19">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B25" s="16">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C25" s="16">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F25" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:25；[Exp].Level22；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A26" s="19">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B26" s="16">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C26" s="16">
+        <x:v>1300</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F26" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:26；[Exp].Level23；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H26" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A27" s="19">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B27" s="16">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C27" s="16">
+        <x:v>1400</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:27；[Exp].Level24；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H27" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A28" s="19">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B28" s="16">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C28" s="16">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F28" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G28" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:28；[Exp].Level25；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H28" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A29" s="19">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B29" s="16">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C29" s="16">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G29" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:29；[Exp].Level26；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H29" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A30" s="19">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B30" s="16">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C30" s="16">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G30" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:30；[Exp].Level27；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H30" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A31" s="19">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B31" s="16">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C31" s="16">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G31" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:31；[Exp].Level28；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H31" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A32" s="19">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B32" s="16">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C32" s="16">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G32" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:32；[Exp].Level29；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H32" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A33" s="19">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B33" s="16">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C33" s="16">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G33" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:33；[Exp].Level30；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H33" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A34" s="19">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B34" s="16">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C34" s="16">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G34" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:34；[Exp].Level31；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H34" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A35" s="19">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B35" s="16">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C35" s="16">
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G35" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:35；[Exp].Level32；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H35" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A36" s="19">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B36" s="16">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C36" s="16">
+        <x:v>32000</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G36" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:36；[Exp].Level33；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H36" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A37" s="19">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B37" s="16">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C37" s="16">
+        <x:v>33000</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G37" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:37；[Exp].Level34；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H37" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A38" s="19">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B38" s="16">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C38" s="16">
+        <x:v>35000</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G38" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:38；[Exp].Level35；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A39" s="19">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B39" s="16">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C39" s="16">
+        <x:v>80000</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E39" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G39" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:39；[Exp].Level36；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H39" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A40" s="19">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B40" s="16">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C40" s="16">
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E40" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F40" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G40" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:40；[Exp].Level37；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H40" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A41" s="19">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B41" s="16">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C41" s="16">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E41" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F41" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G41" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:41；[Exp].Level38；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H41" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A42" s="19">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B42" s="16">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C42" s="16">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E42" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F42" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G42" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:42；[Exp].Level39；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H42" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A43" s="19">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B43" s="16">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C43" s="16">
+        <x:v>900000</x:v>
+      </x:c>
+      <x:c r="D43" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E43" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F43" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G43" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:43；[Exp].Level40；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H43" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A44" s="19">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B44" s="16">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C44" s="16">
+        <x:v>1200000</x:v>
+      </x:c>
+      <x:c r="D44" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E44" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F44" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G44" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:44；[Exp].Level41；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H44" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A45" s="19">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B45" s="16">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C45" s="16">
+        <x:v>2400000</x:v>
+      </x:c>
+      <x:c r="D45" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E45" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F45" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G45" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:45；[Exp].Level42；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H45" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A46" s="19">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B46" s="16">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C46" s="16">
+        <x:v>3600000</x:v>
+      </x:c>
+      <x:c r="D46" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E46" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G46" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:46；[Exp].Level43；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H46" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A47" s="19">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B47" s="16">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C47" s="16">
+        <x:v>7200000</x:v>
+      </x:c>
+      <x:c r="D47" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E47" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:47；[Exp].Level44；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H47" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A48" s="19">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B48" s="16">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C48" s="16">
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="D48" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E48" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G48" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:48；[Exp].Level45；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H48" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A49" s="19">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B49" s="16">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C49" s="16">
+        <x:v>24000000</x:v>
+      </x:c>
+      <x:c r="D49" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E49" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G49" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:49；[Exp].Level46；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H49" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A50" s="19">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B50" s="16">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C50" s="16">
+        <x:v>38000000</x:v>
+      </x:c>
+      <x:c r="D50" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E50" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F50" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G50" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:50；[Exp].Level47；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H50" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A51" s="19">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B51" s="16">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C51" s="16">
+        <x:v>52000000</x:v>
+      </x:c>
+      <x:c r="D51" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E51" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F51" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G51" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:51；[Exp].Level48；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H51" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A52" s="19">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B52" s="16">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C52" s="16">
+        <x:v>63000000</x:v>
+      </x:c>
+      <x:c r="D52" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E52" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G52" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:52；[Exp].Level49；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H52" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A53" s="19">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B53" s="16">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C53" s="16">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="D53" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">development_candidate_only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">myf_source_unbalanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G53" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mir200/Exps.ini:53；[Exp].Level50；独立副本SHA256=b3682dc6194a880790fdbc6e1e8846a784dfa40fda3432e763b40878efef2d01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H53" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅来源数值开发候选，未验证自然1→50或长期节奏；当前仅15EXP普通怪，不沿旧235天表。INI其它经验处理开关未自动移植；50级下级门槛仅供待用池及未来转生，显式cap禁止自动51。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="568" priority="1">
@@ -52463,7 +53543,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":19,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":20,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]},"progression":{"curve_version":"myf_exp_candidate_1_50_v1","operating_level_cap":50,"catalog_max_level":50,"pending_pool_policy":"one_next_level","new_overflow_policy":"reject_new_with_receipt","legacy_overflow_policy":"preserve_frozen","level_up_resources":"source_full_if_alive_original_birth","rebirth_enabled":false}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -53543,7 +53543,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":20,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]},"progression":{"curve_version":"myf_exp_candidate_1_50_v1","operating_level_cap":50,"catalog_max_level":50,"pending_pool_policy":"one_next_level","new_overflow_policy":"reject_new_with_receipt","legacy_overflow_policy":"preserve_frozen","level_up_resources":"source_full_if_alive_original_birth","rebirth_enabled":false}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":21,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]},"progression":{"curve_version":"myf_exp_candidate_1_50_v1","operating_level_cap":50,"catalog_max_level":50,"pending_pool_policy":"one_next_level","new_overflow_policy":"reject_new_with_receipt","legacy_overflow_policy":"preserve_frozen","level_up_resources":"source_full_if_alive_original_birth","rebirth_enabled":false}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -31524,8 +31524,10 @@
       <x:c r="G4" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H4" s="17" t="str">
-        <x:v>{"physical_attack_min":2,"physical_attack_max":5,"physical_defence_min":0,"physical_defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"attack_speed":0}</x:v>
+      <x:c r="H4" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"physical_attack_min":2,"physical_attack_max":5,"physical_defence_min":0,"physical_defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"attack_speed":0,"magic_attack_min":0,"magic_attack_max":0,"spirit_attack_min":0,"spirit_attack_max":0}</x:t>
+        </x:is>
       </x:c>
       <x:c r="I4" s="16" t="n">
         <x:v>4000</x:v>
@@ -31539,8 +31541,10 @@
       <x:c r="L4" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
-      <x:c r="M4" s="18" t="str">
-        <x:v>资料参考/myf/Mud2/DB/ApexM2_stditems.csv:220</x:v>
+      <x:c r="M4" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">资料参考/myf/Mud2/DB/ApexM2_stditems.csv:220；rule22基础装备属性：原表Mc/Mc2/Sc/Sc2逐列均为0，显式投影魔法攻击/道术攻击上下限；不证明完整词条/外观/持久系统</x:t>
+        </x:is>
       </x:c>
       <x:c r="N4" s="18" t="str">
         <x:v>仅显式development配置使用的跨来源候选；未通过目标1.80行为/数值/真机验收，不进入正式发布。 品质0、阶段0是开发夹具对接本项目枚举的工程选择；不把来源Color当品质。 首组开发装备未接额外攻速词条，本轮明确attack_speed=0适配；不证明源服全部词条。</x:v>
@@ -31568,8 +31572,10 @@
       <x:c r="G5" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H5" s="17" t="str">
-        <x:v>{"physical_attack_min":0,"physical_attack_max":0,"physical_defence_min":2,"physical_defence_max":2,"magic_defence_min":0,"magic_defence_max":1,"attack_speed":0}</x:v>
+      <x:c r="H5" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{"physical_attack_min":0,"physical_attack_max":0,"physical_defence_min":2,"physical_defence_max":2,"magic_defence_min":0,"magic_defence_max":1,"attack_speed":0,"magic_attack_min":0,"magic_attack_max":0,"spirit_attack_min":0,"spirit_attack_max":0}</x:t>
+        </x:is>
       </x:c>
       <x:c r="I5" s="16" t="n">
         <x:v>10000</x:v>
@@ -31583,8 +31589,10 @@
       <x:c r="L5" s="17" t="str">
         <x:v>candidate</x:v>
       </x:c>
-      <x:c r="M5" s="18" t="str">
-        <x:v>最终策划案.md:113-115、485-497（4.2、4.20）；资料参考/myf/Mud2/DB/ApexM2_stditems.csv:195</x:v>
+      <x:c r="M5" s="18" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最终策划案.md:113-115、485-497（4.2、4.20）；资料参考/myf/Mud2/DB/ApexM2_stditems.csv:195；rule22基础装备属性：原表Mc/Mc2/Sc/Sc2逐列均为0，显式投影魔法攻击/道术攻击上下限；不证明完整词条/外观/持久系统</x:t>
+        </x:is>
       </x:c>
       <x:c r="N5" s="18" t="str">
         <x:v>来源原名布衣(男)。本作无性别穿戴门槛，不新增男女装备分类，同itemID按职业固定外观；允许职业[0,1,2]是目标规则适配。女法师衣服外观映射仍待正式资源验收。仅development候选，未通过目标1.80行为或数值验收。 首组开发装备未接额外攻速词条，本轮明确attack_speed=0适配；不证明源服全部词条。</x:v>
@@ -53543,7 +53551,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":21,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]},"progression":{"curve_version":"myf_exp_candidate_1_50_v1","operating_level_cap":50,"catalog_max_level":50,"pending_pool_policy":"one_next_level","new_overflow_policy":"reject_new_with_receipt","legacy_overflow_policy":"preserve_frozen","level_up_resources":"source_full_if_alive_original_birth","rebirth_enabled":false}}</x:t>
+          <x:t xml:space="preserve">{"rule_version":22,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]},"progression":{"curve_version":"myf_exp_candidate_1_50_v1","operating_level_cap":50,"catalog_max_level":50,"pending_pool_policy":"one_next_level","new_overflow_policy":"reject_new_with_receipt","legacy_overflow_policy":"preserve_frozen","level_up_resources":"source_full_if_alive_original_birth","rebirth_enabled":false},"base_item_ids":[35,36,193,218]}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -53551,7 +53559,7 @@
       </x:c>
       <x:c r="E4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选；本任务rule16宠物驻留/身体/训练候选，数值由PetDefs/Growth及架构预算共同维护；rule17地图宠物政策与独立召唤候选，同源参数不激活主技能</x:t>
+          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选；本任务rule16宠物驻留/身体/训练候选，数值由PetDefs/Growth及架构预算共同维护；rule17地图宠物政策与独立召唤候选，同源参数不激活主技能；本任务rule22装备基础合同：base_item_ids只选择原4物品；MC/SC来自唯一装备行；装备阶段按floor((required_level−1)/10)校验；不选入乌木剑220，不新增回收价或外观</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="18" t="inlineStr">

--- a/outputs/development-prep-20261026/玩法配置.xlsx
+++ b/outputs/development-prep-20261026/玩法配置.xlsx
@@ -53551,7 +53551,7 @@
       </x:c>
       <x:c r="C4" s="17" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{"rule_version":22,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]},"progression":{"curve_version":"myf_exp_candidate_1_50_v1","operating_level_cap":50,"catalog_max_level":50,"pending_pool_policy":"one_next_level","new_overflow_policy":"reject_new_with_receipt","legacy_overflow_policy":"preserve_frozen","level_up_resources":"source_full_if_alive_original_birth","rebirth_enabled":false},"base_item_ids":[35,36,193,218]}</x:t>
+          <x:t xml:space="preserve">{"rule_version":23,"map_id":1,"monster_id":1,"pet_id":1,"players":[{"job_id":0,"definition_id":0,"hp":18,"mp":14,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":1,"definition_id":1,"hp":15,"mp":17,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":15,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true},{"job_id":2,"definition_id":2,"hp":16,"mp":13,"attack_min":0,"attack_max":0,"defence":0,"attack_ms":1386,"move_ms":600,"magic_min":0,"magic_max":0,"tao_min":0,"tao_max":0,"defence_min":0,"defence_max":0,"magic_defence_min":0,"magic_defence_max":0,"accuracy":5,"agility":18,"magic_resist":0,"magic_resist_weight":10,"attack_speed":0,"can_push":true}],"inventory_capacity":32,"initial_inventory":[218,218,193,35,36],"initial_bound_gold":0,"allow_free_dev_revive":true,"damage_formula":"development_source_combat","recycle_test_gold_by_item":{"35":0,"36":0,"193":400,"218":50},"technical_parameters_notice":"rule15仅开发来源瞬移：200ms延迟、完整绑定图随机、MP10+rank×3及Flux候选由对应唯一基础表维护。承接原streaming/旅行/导航受控参数；不改变事务/租约时限，不持久坐标/MP/CD/临时世界，不作容量或完整目标1.80认证。；rule16同owner保留身体/尸体有界；独立训练定义来自PetDefs/Growth，原免费bootstrap不训练，17与护符仍关闭，不认证容量。；rule17显式NoPets/RecallName与关闭的召唤独立候选，主仍22技能、legacy不训练、材料关闭；不认证17/购符业务。","player_stats_source":"Crystal Shared/BaseStats.cs 默认三职业成长与float32 Calculate；项目独立副本/摘要见docs/技能来源核验与实施清单.md；非目标1.80认证；HumanObject.cs:1766–1768攻击间隔随等级重算；2974–2975、3201普通前格时序。","damage_scope_notice":"开发来源候选：DC/MC/SC、AC/MAC区间、准确敏捷、基础剑术被动；火球延迟单体、治愈独立队列。元素、幸运、完整职业技能/升级仍未验收。 本轮补单体与3×3范围、雷电不死倍率、逐杀序号与原事件时刻；仍不包含幸运/元素/完整Buff。 本轮补攻杀/刺杀/半月/烈火及疾光/冰咆哮/地雷，binary32逐步运算；地狱火所有阶固定正前4格已由用户审定。仍非完整1.80核验。","revive_notice":"开发测试行为，不是已核验正式死亡/复活规则；不收费、不掉经验、不掉装；健康重连不回血，主动操作幂等恢复。","potions":{"tick_ms":200,"base_per_tick":5,"levels_per_step":10,"use_delay_ms":300,"queue_cap":65535,"effects":[{"item_id":35,"hp":20,"mp":0},{"item_id":36,"hp":0,"mp":30}]},"player_growth":[{"job_id":0,"hp_base":14,"mp_base":11,"hp_gain":4,"hp_gain_rate":4.5,"mp_gain":3.5,"mp_gain_rate":0,"attack_divisor":5,"defence_max_divisor":7,"magic_divisor":0,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":1,"hp_base":14,"mp_base":13,"hp_gain":15,"hp_gain_rate":1.8,"mp_gain":5,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":7,"tao_divisor":0,"magic_defence_min_divisor":0,"magic_defence_max_divisor":0},{"job_id":2,"hp_base":14,"mp_base":13,"hp_gain":6,"hp_gain_rate":2.5,"mp_gain":8,"mp_gain_rate":0,"attack_divisor":7,"defence_max_divisor":0,"magic_divisor":0,"tao_divisor":7,"magic_defence_min_divisor":12,"magic_defence_max_divisor":6}],"healing":{"tick_ms":600,"base_per_tick":5,"pet_base_per_tick":5,"levels_per_step":10,"queue_fraction_divisor":10,"queue_cap":65535},"initial_skill_books":[{"job_id":1,"item_id":7},{"job_id":2,"item_id":21},{"job_id":0,"item_id":1}],"skill_ids":[1,2,3,4,5,11,23,29,7,12,25,26,10,33,24,9,14,15,31,8,27,21],"skill_economy":{"page_item_id":900001,"preview_ttl_ms":120000,"preview_material_limit":32},"skill_shop_entries":[{"offer_id":6,"item_id":7,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":7,"item_id":21,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":8,"item_id":1,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":3,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":4,"item_id":900001,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":9,"item_id":22,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":10,"item_id":12,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":11,"item_id":11,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":12,"item_id":14,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":13,"item_id":32,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":14,"item_id":2,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":15,"item_id":3,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":16,"item_id":4,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":17,"item_id":6,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":18,"item_id":16,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":19,"item_id":20,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":20,"item_id":17,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":21,"item_id":10,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":22,"item_id":28,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":23,"item_id":29,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":24,"item_id":18,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":25,"item_id":8,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":26,"item_id":5,"required_role_level":1,"max_purchase_quantity":32},{"offer_id":27,"item_id":13,"required_role_level":1,"max_purchase_quantity":32}],"recyclable_book_ids":[7,21,1,22,12,11,14,32,2,3,4,6,16,20,17,10,28,29,18,8,5,13],"recycle_source_kinds":["monster_drop"],"skill_book_drop_quality":1,"combat_timing":{"player_attack_base_ms":1400,"player_attack_speed_step_ms":60,"player_attack_level_step_ms":14,"player_attack_level_cap_ms":370,"player_attack_min_ms":550,"player_attack_action_ms":550,"player_attack_impact_ms":300,"event_capacity":128,"kill_queue_capacity":16,"player_push_action_ms":500,"monster_push_action_ms_per_step":300,"monster_push_move_ms_per_step":500,"pushed_step_display_ms":300},"pet_spawn":{"x":8,"y":7},"casting_supply":{"enabled":false,"slot":100,"item_ids":[187]},"map_catalog_ids":[2],"binding":{"enabled":false,"start_points":[],"safe_zone_enabled":true},"source_map_streaming":{"load_concurrency":4,"cache_capacity":49},"town_travel":{"enabled":true,"town_map_id":2,"plan_ttl_ms":120000,"quiesce_ttl_ms":10000,"ack_ttl_ms":120000,"max_plans_per_scene":256},"town_navigation":{"enabled":true,"work_per_task":1024,"work_per_worker_tick":8192,"workspaces_per_worker":1,"queue_per_worker":64,"max_expanded":490000,"max_frontier":65536,"max_route_cells":4096,"max_replans":3,"max_dynamic_cells":2,"max_memory_bytes_per_worker":33554432},"pet_runtime":{"enabled":true,"bootstrap_mode":"legacy_untrained_pet","definition_ids":[1]},"equipment_recycling":{"mode":"development_gold_only","outputs":[]},"progression":{"curve_version":"myf_exp_candidate_1_50_v1","operating_level_cap":50,"catalog_max_level":50,"pending_pool_policy":"one_next_level","new_overflow_policy":"reject_new_with_receipt","legacy_overflow_policy":"preserve_frozen","level_up_resources":"source_full_if_alive_original_birth","rebirth_enabled":false},"base_item_ids":[35,36,193,218],"warehouses":{"enabled":true,"query_page_limit":30}}</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -53559,7 +53559,7 @@
       </x:c>
       <x:c r="E4" s="18" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选；本任务rule16宠物驻留/身体/训练候选，数值由PetDefs/Growth及架构预算共同维护；rule17地图宠物政策与独立召唤候选，同源参数不激活主技能；本任务rule22装备基础合同：base_item_ids只选择原4物品；MC/SC来自唯一装备行；装备阶段按floor((required_level−1)/10)校验；不选入乌木剑220，不新增回收价或外观</x:t>
+          <x:t xml:space="preserve">rule15源码开发候选；Crystal Server/MirEnvir/Envir.cs:654–656、MirDatabase/MagicInfo.cs:18,219–221、MirObjects/HumanObject.cs:186,3375–3397,3424–3451,3537–3540,6096–6107、MirObjects/PlayerObject.cs:4633–4647；非目标1.80完整认证；既有首循环、状态、绑定及城镇来源继续按各基础表来源；本任务rule15原World执行与连接scene解耦技术开发候选；本任务rule16宠物驻留/身体/训练候选，数值由PetDefs/Growth及架构预算共同维护；rule17地图宠物政策与独立召唤候选，同源参数不激活主技能；本任务rule22装备基础合同：base_item_ids只选择原4物品；MC/SC来自唯一装备行；装备阶段按floor((required_level−1)/10)校验；不选入乌木剑220，不新增回收价或外观；本任务rule23双仓储：容量与个人扩页价格只读取角色与仓库规则的已定原行；query_page_limit=30仅为有界查询技术候选，不限制个人总页数；共享按本角色当前特权及永久account+origin校验；不赠特权或新增非绑元宝</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="18" t="inlineStr">
